--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>113.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-53.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.2%</t>
+          <t>445.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.8%</t>
+          <t>-591.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.7%</t>
+          <t>-279.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.6%</t>
+          <t>-269.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-201.6%</t>
+          <t>-204.3%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760745</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.805233830019551</v>
+        <v>-7.894867041079634</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1589183645136409</v>
+        <v>-0.1947716489376741</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.704215865268731</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.742004458251203</v>
+        <v>-7.831637669311285</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1390944953471065</v>
+        <v>-0.1749477797711396</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.704215865268731</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.618713323434072</v>
+        <v>-7.708346534494154</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.09227994740967738</v>
+        <v>-0.1281332318337105</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.580924730451601</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.597564124530629</v>
+        <v>-7.687197335590711</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.07611928961097503</v>
+        <v>-0.1119725740350077</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.559775531548158</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.353798682547184</v>
+        <v>-7.443431893607267</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.01716759552945346</v>
+        <v>-0.01868568889457967</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.559775531548158</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.089770615353924</v>
+        <v>-7.179403826414006</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1249031363267736</v>
+        <v>0.08904985190274051</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.357910132732204</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.839920221404849</v>
+        <v>-6.929553432464932</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2175853688901057</v>
+        <v>0.1817320844660726</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.357910132732204</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.664028128937417</v>
+        <v>-6.7536613399975</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2915413293977274</v>
+        <v>0.2556880449736942</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.357910132732204</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.492581665914954</v>
+        <v>-6.582214876975036</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3734474206612663</v>
+        <v>0.3375941362372332</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.186463669709741</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.267548666246131</v>
+        <v>-6.357181877306213</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4624810981450924</v>
+        <v>0.4266278137210593</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.961430670040918</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.052914288609724</v>
+        <v>-6.142547499669806</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5530296502539724</v>
+        <v>0.5171763658299393</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7467962924045112</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.959914247403826</v>
+        <v>-6.049547458463908</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5714239255201274</v>
+        <v>0.5355706410960943</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7467962924045112</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.719483750598966</v>
+        <v>-5.809116961659048</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6693392008669488</v>
+        <v>0.6334859164429161</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5063657955996509</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.647241182427771</v>
+        <v>-5.736874393487853</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7021655419702468</v>
+        <v>0.6663122575462141</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5063657955996509</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.531301332802586</v>
+        <v>-5.620934543862668</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7492200657376613</v>
+        <v>0.7133667813136282</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.429544064583527</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288645744379423</v>
+        <v>-5.378278955439505</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8432803723269195</v>
+        <v>0.8074270879028869</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.429544064583527</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068624946342412</v>
+        <v>-5.158258157402495</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9328677285523379</v>
+        <v>0.8970144441283052</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2883242195155468</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935757257279135</v>
+        <v>-5.025390468339217</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001908986979472</v>
+        <v>0.9660557025554395</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2883242195155468</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.776242153759765</v>
+        <v>-4.865875364819847</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.066860872827522</v>
+        <v>1.031007588403489</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1288091159961768</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.631570008660027</v>
+        <v>-4.72120321972011</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.134817833428857</v>
+        <v>1.098964549004824</v>
       </c>
       <c r="F1932" t="n">
         <v>0.01586302910356058</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412105</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.69144483601772</v>
+        <v>-4.781078047077802</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.096905393887206</v>
+        <v>1.061052109463173</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.04401179825413154</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.604645338238711</v>
+        <v>-4.694278549298794</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.154025686321375</v>
+        <v>1.118172401897342</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.04401179825413154</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.607115044700517</v>
+        <v>-4.6967482557606</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.153110205110065</v>
+        <v>1.117256920686032</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.0464815047159377</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.675485231024528</v>
+        <v>-4.76511844208461</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.136769053055163</v>
+        <v>1.10091576863113</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.03720580567972276</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.554068801398051</v>
+        <v>-4.643702012458133</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.175772333537645</v>
+        <v>1.139919049113612</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.03720580567972276</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.585061960726756</v>
+        <v>-4.674695171786839</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9880846348465497</v>
+        <v>0.9522313504225166</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.03720580567972276</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.409587700934287</v>
+        <v>-4.499220911994369</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.062841570755325</v>
+        <v>1.026988286331292</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.03720580567972276</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.520523953575536</v>
+        <v>-4.610157164635618</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9942090984600327</v>
+        <v>0.9583558140359998</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.03720580567972276</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.723550531118769</v>
+        <v>-4.813183742178851</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9161298526626451</v>
+        <v>0.880276568238612</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2402323832229561</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.565624932183476</v>
+        <v>-4.655258143243558</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9894724786688947</v>
+        <v>0.9536191942448617</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2402323832229561</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.479381469157098</v>
+        <v>-4.56901468021718</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.018916134453306</v>
+        <v>0.9830628500292731</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2402323832229561</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.48056455380816</v>
+        <v>-4.570197764868242</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.010218676037407</v>
+        <v>0.9743653916133741</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2458754316894677</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.357436846814077</v>
+        <v>-4.447070057874159</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.060021631868142</v>
+        <v>1.024168347444109</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2458754316894677</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.264626365363217</v>
+        <v>-4.354259576423299</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.026418516339851</v>
+        <v>0.9905652319158182</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1530649502386083</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.216063313142187</v>
+        <v>-4.305696524202269</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.047717213152864</v>
+        <v>1.011863928728831</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1045018980175781</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.103392094905937</v>
+        <v>-4.193025305966019</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.087861408959087</v>
+        <v>1.052008124535054</v>
       </c>
       <c r="F1948" t="n">
         <v>0.00816932021867206</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.991015093723264</v>
+        <v>-4.080648304783346</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.138303505262823</v>
+        <v>1.102450220838791</v>
       </c>
       <c r="F1949" t="n">
         <v>0.00816932021867206</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.189249662609995</v>
+        <v>-4.278882873670077</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.07050687947667</v>
+        <v>1.034653595052637</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1900652486680585</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.272250943635274</v>
+        <v>-4.361884154695356</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.875662087067212</v>
+        <v>0.8398088026431791</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2086361331952323</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.113056671578697</v>
+        <v>-4.202689882638779</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.059489456609048</v>
+        <v>1.023636172185015</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2086361331952323</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.1996552545598</v>
+        <v>-4.289288465619882</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.03936304951893</v>
+        <v>1.003509765094897</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2086361331952323</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.161271592001649</v>
+        <v>-4.250904803061731</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.052135955884559</v>
+        <v>1.016282671460526</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1702524706370811</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.984155261966483</v>
+        <v>-4.073788473026565</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.119711516743928</v>
+        <v>1.083858232319895</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1702524706370811</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.954453137990189</v>
+        <v>-4.044086349050271</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.132275758096358</v>
+        <v>1.096422473672325</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1747225958523945</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.775077716751421</v>
+        <v>-3.864710927811504</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.197812901898279</v>
+        <v>1.161959617474247</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.01794583768167579</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.820091930272028</v>
+        <v>-3.90972514133211</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.160614671821627</v>
+        <v>1.124761387397594</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0482947329962804</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.087096440544463</v>
+        <v>-4.176729651604545</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.059504430051598</v>
+        <v>1.023651145627565</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.242657771039229</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.375883661003378</v>
+        <v>-4.465516872063461</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9431934637645338</v>
+        <v>0.9073401793405007</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3437438911382293</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.343408074832606</v>
+        <v>-4.433041285892688</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9537836597871594</v>
+        <v>0.9179303753631265</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3437438911382293</v>
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.56325414279521</v>
+        <v>3.426543021296952</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.332131752807859</v>
+        <v>-4.303225455426153</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9548189078053031</v>
+        <v>0.9663814267579856</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4057544348760804</v>
+        <v>-0.4518834631704997</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.444575372316546</v>
+        <v>2.416897955339894</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>133.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,22 +977,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-698.4%</t>
+          <t>-688.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.6%</t>
+          <t>440.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-591.9%</t>
+          <t>-583.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-279.7%</t>
+          <t>-275.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.6%</t>
+          <t>-276.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-296.8%</t>
+          <t>-286.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-269.2%</t>
+          <t>-264.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-204.3%</t>
+          <t>-201.3%</t>
         </is>
       </c>
     </row>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.3190743501726734</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.245763505246598</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.2708520833255899</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.230554581129431</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>0.03372059147579481</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.170643068887055</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>0.03875818220338134</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.171235545363428</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.1238678977612572</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>3.084931495001309</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.1896352878106693</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>3.059642148112015</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5079986410624522</v>
+        <v>-0.4066441104784234</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.922924838799057</v>
+        <v>2.963466651032669</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5897705414902039</v>
+        <v>-0.4884160109061751</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.880298804583195</v>
+        <v>2.920840616816806</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6569796493620816</v>
+        <v>-0.5556251187780528</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.858180478268146</v>
+        <v>2.898722290501758</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8645454337536935</v>
+        <v>-0.7631909031696646</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.772978960630741</v>
+        <v>2.813520772864353</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.282299457300531</v>
+        <v>-1.180944926716502</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.60380424271707</v>
+        <v>2.644346054950681</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.503921390858648</v>
+        <v>-1.402566860274619</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.515021685892745</v>
+        <v>2.555563498126356</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.711925449211725</v>
+        <v>-1.610570918627696</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.436712207105439</v>
+        <v>2.477254019339051</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.9233378700997</v>
+        <v>-1.821983339515671</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.347228695088237</v>
+        <v>2.387770507321849</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.262496247688222</v>
+        <v>-2.161141717104194</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.204649643359277</v>
+        <v>2.245191455592889</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.470987029139907</v>
+        <v>-2.369632498555878</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.141591620517372</v>
+        <v>2.182133432750983</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.964311900675085</v>
+        <v>-2.862957370091056</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.952360422311869</v>
+        <v>1.992902234545481</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.456696928699182</v>
+        <v>-3.355342398115153</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.756512803145962</v>
+        <v>1.797054615379574</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.841877319629254</v>
+        <v>-3.740522789045226</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.600983185586797</v>
+        <v>1.641524997820409</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.185560092855917</v>
+        <v>-4.084205562271888</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.465279199750748</v>
+        <v>1.505821011984359</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.392071869742939</v>
+        <v>-4.29071733915891</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.378780547652197</v>
+        <v>1.419322359885809</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.701305972738989</v>
+        <v>-4.599951442154961</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.256859833154036</v>
+        <v>1.297401645387648</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.133111765888777</v>
+        <v>-5.031757235304748</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.070470403361526</v>
+        <v>1.111012215595137</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.367805760021329</v>
+        <v>-5.2664512294373</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9648775807105956</v>
+        <v>1.005419392944207</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.703468407251782</v>
+        <v>-5.602113876667753</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8291931134743797</v>
+        <v>0.8697349257079914</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.067094652152095</v>
+        <v>-5.965740121568066</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6902301757484959</v>
+        <v>0.7307719879821075</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.432222034790842</v>
+        <v>-6.330867504206813</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5434337376988285</v>
+        <v>0.5839755499324402</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.840810811971521</v>
+        <v>-6.739456281387492</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3787597708413162</v>
+        <v>0.4193015830749278</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.253793296112614</v>
+        <v>-7.152438765528585</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.208752209656339</v>
+        <v>0.2492940218899506</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.670185170399612</v>
+        <v>-7.568830639815583</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.04018951055041775</v>
+        <v>0.08073132278402895</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.046862180929455</v>
+        <v>-7.945507650345427</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.100222602992841</v>
+        <v>-0.05968079075922983</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.392737002914265</v>
+        <v>-8.291382472330236</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2424729666410692</v>
+        <v>-0.201931154407458</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.556316881098649</v>
+        <v>-8.45496235051462</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3094999978598221</v>
+        <v>-0.2689581856262104</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.852978222908847</v>
+        <v>-8.751623692324818</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4243855586546932</v>
+        <v>-0.3838437464210815</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.976222612124277</v>
+        <v>-8.874868081540248</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4777096188752683</v>
+        <v>-0.4371678066416567</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.359224000866908</v>
+        <v>-9.257869470282879</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6310122756939047</v>
+        <v>-0.5904704634602931</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.516622881080028</v>
+        <v>-9.415268350496</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.691400311807723</v>
+        <v>-0.6508584995741113</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.87615320358403</v>
+        <v>-9.774798673000001</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8298621375112734</v>
+        <v>-0.7893203252776617</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.926502267038252</v>
+        <v>-9.825147736454223</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8420857429357844</v>
+        <v>-0.8015439307021732</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.14565123511245</v>
+        <v>-10.04429670452842</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9267035795436951</v>
+        <v>-0.886161767310083</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.14196031015604</v>
+        <v>-10.04060577957201</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9252272095611302</v>
+        <v>-0.8846853973275191</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.3462184854859</v>
+        <v>-10.24486395490187</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.001417282574433</v>
+        <v>-0.960875470340822</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.56425625711708</v>
+        <v>-10.46290172653305</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.084149836742469</v>
+        <v>-1.043608024508857</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.49078642544963</v>
+        <v>-10.3894318948656</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.039390202582068</v>
+        <v>-0.9988483903484564</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.66591084283617</v>
+        <v>-10.56455631225215</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.094884748789168</v>
+        <v>-1.054342936555557</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.90036293685066</v>
+        <v>-10.79900840626664</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.19588475129656</v>
+        <v>-1.155342939062949</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.1881667813879</v>
+        <v>-11.08681225080387</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.317678479885432</v>
+        <v>-1.27713666765182</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.877190163033957</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.41799122855173</v>
+        <v>-11.3166366979677</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.408492468912406</v>
+        <v>-1.367950656678794</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.039837700104118</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.65002014828799</v>
+        <v>-11.54866561770396</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.498610308177796</v>
+        <v>-1.458068495944184</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.101850397292541</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.59800463431918</v>
+        <v>-11.49665010373515</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.473813766903869</v>
+        <v>-1.433271954670258</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.101850397292541</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.7396764760433</v>
+        <v>-11.63832194545927</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.531957730492259</v>
+        <v>-1.491415918258648</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.101850397292541</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.69008563161846</v>
+        <v>-11.58873110103443</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.497067982557453</v>
+        <v>-1.456526170323842</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.052259552867707</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.49093352438136</v>
+        <v>-11.38957899379733</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.430458273309296</v>
+        <v>-1.389916461075685</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.886937026917894</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.26508837166195</v>
+        <v>-11.16373384107792</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.330541139185324</v>
+        <v>-1.289999326951712</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.84501035133073</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.14050971532436</v>
+        <v>-11.03915518474033</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.279570532094228</v>
+        <v>-1.239028719860617</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.84501035133073</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.19340500336865</v>
+        <v>-11.09205047278462</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.298094873149835</v>
+        <v>-1.257553060916224</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.840055005242284</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.9094962724399</v>
+        <v>-10.80814174185587</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.178797676539699</v>
+        <v>-1.138255864306088</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.840055005242284</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.83812987983025</v>
+        <v>-10.73677534924622</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.159988381889706</v>
+        <v>-1.119446569656094</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.768688612632636</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.57429301262618</v>
+        <v>-10.47293848204215</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.064337116320985</v>
+        <v>-1.023795304087373</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.768688612632636</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.30705121175778</v>
+        <v>-10.20569668117376</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9592749564729997</v>
+        <v>-0.9187331442393885</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.768688612632636</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.20914417308129</v>
+        <v>-10.10778964249726</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9204124559758644</v>
+        <v>-0.8798706437422532</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.700702862772079</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.18519063210534</v>
+        <v>-10.08383610152131</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9101625334399874</v>
+        <v>-0.8696207212063762</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.676749321796122</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.921130693782539</v>
+        <v>-9.81977616319851</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8177988742726212</v>
+        <v>-0.7772570620390096</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.412689383473326</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.214051070277701</v>
+        <v>-9.112696539693673</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5377540585309868</v>
+        <v>-0.4972122462973756</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.412689383473326</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.173866771911511</v>
+        <v>-9.072512241327482</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5213367152966693</v>
+        <v>-0.4807949030630581</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.372505085107135</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.093796976373707</v>
+        <v>-8.992442445789678</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4899419758607908</v>
+        <v>-0.4494001636271792</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.292435289569331</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.860315754144107</v>
+        <v>-8.758961223560078</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3886250581310984</v>
+        <v>-0.3480832458974872</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.058954067339732</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.710649363136593</v>
+        <v>-8.609294832552564</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3316507120410521</v>
+        <v>-0.2911088998074405</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.966050576097196</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.578373889505706</v>
+        <v>-8.477019358921677</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2833730358416702</v>
+        <v>-0.2428312236080585</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.83377510246631</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.387774214832552</v>
+        <v>-8.286419684248523</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2043181052847718</v>
+        <v>-0.1637762930511606</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.643175427793157</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.138774416148971</v>
+        <v>-8.037419885564942</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.09181184458768099</v>
+        <v>-0.05127003235406935</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.643175427793157</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.244364405922076</v>
+        <v>-8.143009875338047</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2620237700961412</v>
+        <v>-0.2214819578625296</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.748765417566261</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.263099308040672</v>
+        <v>-8.161744777456644</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2209733890664936</v>
+        <v>-0.1804315768328824</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.748765417566261</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.115159266633073</v>
+        <v>-8.013804736049044</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2816762951916214</v>
+        <v>-0.2411344829580102</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.728444501657704</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.090930630244101</v>
+        <v>-7.989576099660072</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2806988268895108</v>
+        <v>-0.2401570146558991</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.704215865268731</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.047382223473409</v>
+        <v>-7.946027692889381</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2702400762763273</v>
+        <v>-0.2296982640427161</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.704215865268731</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.894867041079634</v>
+        <v>-7.703879299435523</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1947716489376741</v>
+        <v>-0.1183765522800297</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.704215865268731</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.831637669311285</v>
+        <v>-7.640649927667175</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1749477797711396</v>
+        <v>-0.0985526831134953</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.704215865268731</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262046</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.708346534494154</v>
+        <v>-7.517358792850044</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1281332318337105</v>
+        <v>-0.05173813517606618</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.580924730451601</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.687197335590711</v>
+        <v>-7.496209593946601</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1119725740350077</v>
+        <v>-0.03557747737736383</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.559775531548158</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.443431893607267</v>
+        <v>-7.252444151963156</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.01868568889457967</v>
+        <v>0.05770940776306466</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.559775531548158</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.179403826414006</v>
+        <v>-6.988416084769897</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.08904985190274051</v>
+        <v>0.1654449485603844</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.357910132732204</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.929553432464932</v>
+        <v>-6.738565690820822</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1817320844660726</v>
+        <v>0.2581271811237165</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.357910132732204</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.7536613399975</v>
+        <v>-6.56267359835339</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2556880449736942</v>
+        <v>0.3320831416313381</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.357910132732204</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.582214876975036</v>
+        <v>-6.391227135330927</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3375941362372332</v>
+        <v>0.4139892328948771</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.186463669709741</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.357181877306213</v>
+        <v>-6.166194135662104</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4266278137210593</v>
+        <v>0.5030229103787032</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.961430670040918</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.142547499669806</v>
+        <v>-5.951559758025697</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5171763658299393</v>
+        <v>0.5935714624875832</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7467962924045112</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.049547458463908</v>
+        <v>-5.858559716819799</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5355706410960943</v>
+        <v>0.6119657377537382</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7467962924045112</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.809116961659048</v>
+        <v>-5.618129220014938</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6334859164429161</v>
+        <v>0.70988101310056</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5063657955996509</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.736874393487853</v>
+        <v>-5.545886651843744</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6663122575462141</v>
+        <v>0.742707354203858</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5063657955996509</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.620934543862668</v>
+        <v>-5.429946802218558</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7133667813136282</v>
+        <v>0.7897618779712721</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.429544064583527</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.378278955439505</v>
+        <v>-5.187291213795396</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8074270879028869</v>
+        <v>0.8838221845605307</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.429544064583527</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.158258157402495</v>
+        <v>-4.967270415758385</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8970144441283052</v>
+        <v>0.9734095407859489</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2883242195155468</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.025390468339217</v>
+        <v>-4.834402726695108</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9660557025554395</v>
+        <v>1.042450799213083</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2883242195155468</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.865875364819847</v>
+        <v>-4.674887623175738</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.031007588403489</v>
+        <v>1.107402685061133</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1288091159961768</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.72120321972011</v>
+        <v>-4.530215478076</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.098964549004824</v>
+        <v>1.175359645662468</v>
       </c>
       <c r="F1932" t="n">
         <v>0.01586302910356058</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.781078047077802</v>
+        <v>-4.590090305433693</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.061052109463173</v>
+        <v>1.137447206120817</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.04401179825413154</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.694278549298794</v>
+        <v>-4.503290807654684</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.118172401897342</v>
+        <v>1.194567498554986</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.04401179825413154</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.6967482557606</v>
+        <v>-4.50576051411649</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.117256920686032</v>
+        <v>1.193652017343676</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.0464815047159377</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.76511844208461</v>
+        <v>-4.574130700440501</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10091576863113</v>
+        <v>1.177310865288774</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.03720580567972276</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.643702012458133</v>
+        <v>-4.452714270814024</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.139919049113612</v>
+        <v>1.216314145771256</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.03720580567972276</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.674695171786839</v>
+        <v>-4.483707430142729</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9522313504225166</v>
+        <v>1.02862644708016</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.03720580567972276</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.499220911994369</v>
+        <v>-4.30823317035026</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.026988286331292</v>
+        <v>1.103383382988936</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.03720580567972276</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.610157164635618</v>
+        <v>-4.419169422991509</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9583558140359998</v>
+        <v>1.034750910693644</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.03720580567972276</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.813183742178851</v>
+        <v>-4.622196000534742</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.880276568238612</v>
+        <v>0.9566716648962559</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2402323832229561</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.655258143243558</v>
+        <v>-4.464270401599449</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9536191942448617</v>
+        <v>1.030014290902505</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2402323832229561</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.56901468021718</v>
+        <v>-4.378026938573071</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9830628500292731</v>
+        <v>1.059457946686917</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2402323832229561</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.570197764868242</v>
+        <v>-4.379210023224132</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9743653916133741</v>
+        <v>1.050760488271018</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2458754316894677</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273188</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.447070057874159</v>
+        <v>-4.256082316230049</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.024168347444109</v>
+        <v>1.100563444101753</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2458754316894677</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279497</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.354259576423299</v>
+        <v>-4.16327183477919</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9905652319158182</v>
+        <v>1.066960328573462</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1530649502386083</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.305696524202269</v>
+        <v>-4.11470878255816</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.011863928728831</v>
+        <v>1.088259025386475</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1045018980175781</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.193025305966019</v>
+        <v>-4.00203756432191</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.052008124535054</v>
+        <v>1.128403221192698</v>
       </c>
       <c r="F1948" t="n">
         <v>0.00816932021867206</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.080648304783346</v>
+        <v>-3.889660563139237</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.102450220838791</v>
+        <v>1.178845317496434</v>
       </c>
       <c r="F1949" t="n">
         <v>0.00816932021867206</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.278882873670077</v>
+        <v>-4.087895132025968</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.034653595052637</v>
+        <v>1.111048691710281</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1900652486680585</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.361884154695356</v>
+        <v>-4.170896413051246</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8398088026431791</v>
+        <v>0.9162038993008228</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2086361331952323</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.202689882638779</v>
+        <v>-4.01170214099467</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.023636172185015</v>
+        <v>1.100031268842659</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2086361331952323</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.289288465619882</v>
+        <v>-4.098300723975773</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.003509765094897</v>
+        <v>1.079904861752541</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2086361331952323</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.250904803061731</v>
+        <v>-4.059917061417622</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.016282671460526</v>
+        <v>1.09267776811817</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1702524706370811</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.073788473026565</v>
+        <v>-3.882800731382456</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.083858232319895</v>
+        <v>1.160253328977539</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1702524706370811</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.044086349050271</v>
+        <v>-3.853098607406162</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.096422473672325</v>
+        <v>1.172817570329969</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1747225958523945</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.864710927811504</v>
+        <v>-3.673723186167394</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.161959617474247</v>
+        <v>1.23835471413189</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.01794583768167579</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.90972514133211</v>
+        <v>-3.718737399688</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.124761387397594</v>
+        <v>1.201156484055238</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0482947329962804</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.176729651604545</v>
+        <v>-3.985741909960436</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.023651145627565</v>
+        <v>1.100046242285209</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.242657771039229</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.465516872063461</v>
+        <v>-4.274529130419351</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9073401793405007</v>
+        <v>0.9837352759981446</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3437438911382293</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.433041285892688</v>
+        <v>-4.242053544248579</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9179303753631265</v>
+        <v>0.9943254720207702</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3437438911382293</v>
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.426543021296952</v>
+        <v>3.807102781585847</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.303225455426153</v>
+        <v>-4.223015416541282</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9663814267579856</v>
+        <v>0.9984654423119341</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4518834631704997</v>
+        <v>-0.4019275024694239</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.416897955339894</v>
+        <v>2.44687153176054</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.3%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.1%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-688.2%</t>
+          <t>-698.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.0%</t>
+          <t>-53.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.5%</t>
+          <t>446.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.9%</t>
+          <t>-598.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-275.7%</t>
+          <t>-279.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.4%</t>
+          <t>-282.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-286.0%</t>
+          <t>-84.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.2%</t>
+          <t>-268.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-201.3%</t>
+          <t>-203.7%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3190743501726734</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.245763505246598</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.2708520833255899</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.230554581129431</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.03372059147579481</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.170643068887055</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.03875818220338134</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.171235545363428</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1238678977612572</v>
+        <v>-0.2252224283452861</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.084931495001309</v>
+        <v>3.044389682767698</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1896352878106693</v>
+        <v>-0.2909898183946981</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.059642148112015</v>
+        <v>3.019100335878403</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760745</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4066441104784234</v>
+        <v>-0.5079986410624522</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.963466651032669</v>
+        <v>2.922924838799057</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4884160109061751</v>
+        <v>-0.5897705414902039</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.920840616816806</v>
+        <v>2.880298804583195</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5556251187780528</v>
+        <v>-0.6569796493620816</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.898722290501758</v>
+        <v>2.858180478268146</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7631909031696646</v>
+        <v>-0.8645454337536935</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.813520772864353</v>
+        <v>2.772978960630741</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.180944926716502</v>
+        <v>-1.282299457300531</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.644346054950681</v>
+        <v>2.60380424271707</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.402566860274619</v>
+        <v>-1.503921390858648</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.555563498126356</v>
+        <v>2.515021685892745</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.610570918627696</v>
+        <v>-1.711925449211725</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.477254019339051</v>
+        <v>2.436712207105439</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.821983339515671</v>
+        <v>-1.9233378700997</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.387770507321849</v>
+        <v>2.347228695088237</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.161141717104194</v>
+        <v>-2.262496247688222</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.245191455592889</v>
+        <v>2.204649643359277</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.369632498555878</v>
+        <v>-2.470987029139907</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.182133432750983</v>
+        <v>2.141591620517372</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.862957370091056</v>
+        <v>-2.964311900675085</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.992902234545481</v>
+        <v>1.952360422311869</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.355342398115153</v>
+        <v>-3.456696928699182</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.797054615379574</v>
+        <v>1.756512803145962</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.740522789045226</v>
+        <v>-3.841877319629254</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.641524997820409</v>
+        <v>1.600983185586797</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.084205562271888</v>
+        <v>-4.185560092855917</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.505821011984359</v>
+        <v>1.465279199750748</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.29071733915891</v>
+        <v>-4.392071869742939</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.419322359885809</v>
+        <v>1.378780547652197</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.599951442154961</v>
+        <v>-4.701305972738989</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.297401645387648</v>
+        <v>1.256859833154036</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.031757235304748</v>
+        <v>-5.133111765888777</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.111012215595137</v>
+        <v>1.070470403361526</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.2664512294373</v>
+        <v>-5.367805760021329</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.005419392944207</v>
+        <v>0.9648775807105956</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.602113876667753</v>
+        <v>-5.703468407251782</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8697349257079914</v>
+        <v>0.8291931134743797</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.965740121568066</v>
+        <v>-6.067094652152095</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7307719879821075</v>
+        <v>0.6902301757484959</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.330867504206813</v>
+        <v>-6.432222034790842</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5839755499324402</v>
+        <v>0.5434337376988285</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.739456281387492</v>
+        <v>-6.840810811971521</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4193015830749278</v>
+        <v>0.3787597708413162</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.152438765528585</v>
+        <v>-7.253793296112614</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2492940218899506</v>
+        <v>0.208752209656339</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.568830639815583</v>
+        <v>-7.670185170399612</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.08073132278402895</v>
+        <v>0.04018951055041775</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.945507650345427</v>
+        <v>-8.046862180929455</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.05968079075922983</v>
+        <v>-0.100222602992841</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.291382472330236</v>
+        <v>-8.392737002914265</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.201931154407458</v>
+        <v>-0.2424729666410692</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.45496235051462</v>
+        <v>-8.556316881098649</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2689581856262104</v>
+        <v>-0.3094999978598221</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.751623692324818</v>
+        <v>-8.852978222908847</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3838437464210815</v>
+        <v>-0.4243855586546932</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.874868081540248</v>
+        <v>-8.976222612124277</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4371678066416567</v>
+        <v>-0.4777096188752683</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.257869470282879</v>
+        <v>-9.359224000866908</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5904704634602931</v>
+        <v>-0.6310122756939047</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.415268350496</v>
+        <v>-9.516622881080028</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6508584995741113</v>
+        <v>-0.691400311807723</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.774798673000001</v>
+        <v>-9.87615320358403</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7893203252776617</v>
+        <v>-0.8298621375112734</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.825147736454223</v>
+        <v>-9.926502267038252</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8015439307021732</v>
+        <v>-0.8420857429357844</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.04429670452842</v>
+        <v>-10.14565123511245</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.886161767310083</v>
+        <v>-0.9267035795436951</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.04060577957201</v>
+        <v>-10.14196031015604</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8846853973275191</v>
+        <v>-0.9252272095611302</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.24486395490187</v>
+        <v>-10.3462184854859</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.960875470340822</v>
+        <v>-1.001417282574433</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.46290172653305</v>
+        <v>-10.56425625711708</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.043608024508857</v>
+        <v>-1.084149836742469</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.3894318948656</v>
+        <v>-10.49078642544963</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9988483903484564</v>
+        <v>-1.039390202582068</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.56455631225215</v>
+        <v>-10.66591084283617</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.054342936555557</v>
+        <v>-1.094884748789168</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.79900840626664</v>
+        <v>-10.90036293685066</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.155342939062949</v>
+        <v>-1.19588475129656</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.08681225080387</v>
+        <v>-11.1881667813879</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.27713666765182</v>
+        <v>-1.317678479885432</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.877190163033957</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.3166366979677</v>
+        <v>-11.41799122855173</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.367950656678794</v>
+        <v>-1.408492468912406</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.039837700104118</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.54866561770396</v>
+        <v>-11.65002014828799</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.458068495944184</v>
+        <v>-1.498610308177796</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.101850397292541</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.49665010373515</v>
+        <v>-11.59800463431918</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.433271954670258</v>
+        <v>-1.473813766903869</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.101850397292541</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.63832194545927</v>
+        <v>-11.7396764760433</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.491415918258648</v>
+        <v>-1.531957730492259</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.101850397292541</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.58873110103443</v>
+        <v>-11.69008563161846</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.456526170323842</v>
+        <v>-1.497067982557453</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.052259552867707</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.38957899379733</v>
+        <v>-11.49093352438136</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.389916461075685</v>
+        <v>-1.430458273309296</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.886937026917894</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.16373384107792</v>
+        <v>-11.26508837166195</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.289999326951712</v>
+        <v>-1.330541139185324</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.84501035133073</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.03915518474033</v>
+        <v>-11.14050971532436</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.239028719860617</v>
+        <v>-1.279570532094228</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.84501035133073</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.09205047278462</v>
+        <v>-11.19340500336865</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.257553060916224</v>
+        <v>-1.298094873149835</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.840055005242284</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.80814174185587</v>
+        <v>-10.9094962724399</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.138255864306088</v>
+        <v>-1.178797676539699</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.840055005242284</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.73677534924622</v>
+        <v>-10.83812987983025</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.119446569656094</v>
+        <v>-1.159988381889706</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.768688612632636</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.47293848204215</v>
+        <v>-10.57429301262618</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.023795304087373</v>
+        <v>-1.064337116320985</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.768688612632636</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.20569668117376</v>
+        <v>-10.30705121175778</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9187331442393885</v>
+        <v>-0.9592749564729997</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.768688612632636</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.10778964249726</v>
+        <v>-10.20914417308129</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8798706437422532</v>
+        <v>-0.9204124559758644</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.700702862772079</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.08383610152131</v>
+        <v>-10.18519063210534</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8696207212063762</v>
+        <v>-0.9101625334399874</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.676749321796122</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.81977616319851</v>
+        <v>-9.921130693782539</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7772570620390096</v>
+        <v>-0.8177988742726212</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.412689383473326</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.112696539693673</v>
+        <v>-9.214051070277701</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4972122462973756</v>
+        <v>-0.5377540585309868</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.412689383473326</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.072512241327482</v>
+        <v>-9.173866771911511</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4807949030630581</v>
+        <v>-0.5213367152966693</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.372505085107135</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.992442445789678</v>
+        <v>-9.093796976373707</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4494001636271792</v>
+        <v>-0.4899419758607908</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.292435289569331</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.758961223560078</v>
+        <v>-8.860315754144107</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3480832458974872</v>
+        <v>-0.3886250581310984</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.058954067339732</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.609294832552564</v>
+        <v>-8.710649363136593</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2911088998074405</v>
+        <v>-0.3316507120410521</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.966050576097196</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.477019358921677</v>
+        <v>-8.578373889505706</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2428312236080585</v>
+        <v>-0.2833730358416702</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.83377510246631</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.286419684248523</v>
+        <v>-8.387774214832552</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1637762930511606</v>
+        <v>-0.2043181052847718</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.643175427793157</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.037419885564942</v>
+        <v>-8.138774416148971</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05127003235406935</v>
+        <v>-0.09181184458768099</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.643175427793157</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.143009875338047</v>
+        <v>-8.244364405922076</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2214819578625296</v>
+        <v>-0.2620237700961412</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.748765417566261</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.161744777456644</v>
+        <v>-8.263099308040672</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1804315768328824</v>
+        <v>-0.2209733890664936</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.748765417566261</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.013804736049044</v>
+        <v>-8.115159266633073</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2411344829580102</v>
+        <v>-0.2816762951916214</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.728444501657704</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.989576099660072</v>
+        <v>-8.090930630244101</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2401570146558991</v>
+        <v>-0.2806988268895108</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.704215865268731</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.946027692889381</v>
+        <v>-8.047382223473409</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2296982640427161</v>
+        <v>-0.2702400762763273</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.704215865268731</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.703879299435523</v>
+        <v>-7.805233830019551</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1183765522800297</v>
+        <v>-0.1589183645136409</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.704215865268731</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.640649927667175</v>
+        <v>-7.742004458251203</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.0985526831134953</v>
+        <v>-0.1390944953471065</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.704215865268731</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.517358792850044</v>
+        <v>-7.618713323434072</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05173813517606618</v>
+        <v>-0.09227994740967738</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.580924730451601</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.496209593946601</v>
+        <v>-7.597564124530629</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03557747737736383</v>
+        <v>-0.07611928961097503</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.559775531548158</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.252444151963156</v>
+        <v>-7.353798682547184</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.05770940776306466</v>
+        <v>0.01716759552945346</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.559775531548158</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.988416084769897</v>
+        <v>-7.089770615353924</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1654449485603844</v>
+        <v>0.1249031363267736</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.357910132732204</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.738565690820822</v>
+        <v>-6.839920221404849</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2581271811237165</v>
+        <v>0.2175853688901057</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.357910132732204</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.56267359835339</v>
+        <v>-6.664028128937417</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3320831416313381</v>
+        <v>0.2915413293977274</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.357910132732204</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.391227135330927</v>
+        <v>-6.492581665914954</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4139892328948771</v>
+        <v>0.3734474206612663</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.186463669709741</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.166194135662104</v>
+        <v>-6.267548666246131</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5030229103787032</v>
+        <v>0.4624810981450924</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.961430670040918</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.951559758025697</v>
+        <v>-6.052914288609724</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5935714624875832</v>
+        <v>0.5530296502539724</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7467962924045112</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.858559716819799</v>
+        <v>-5.959914247403826</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6119657377537382</v>
+        <v>0.5714239255201274</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7467962924045112</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.618129220014938</v>
+        <v>-5.719483750598966</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.70988101310056</v>
+        <v>0.6693392008669488</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5063657955996509</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.545886651843744</v>
+        <v>-5.647241182427771</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.742707354203858</v>
+        <v>0.7021655419702468</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5063657955996509</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.429946802218558</v>
+        <v>-5.531301332802586</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7897618779712721</v>
+        <v>0.7492200657376613</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.429544064583527</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.187291213795396</v>
+        <v>-5.288645744379423</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8838221845605307</v>
+        <v>0.8432803723269195</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.429544064583527</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.967270415758385</v>
+        <v>-5.068624946342412</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9734095407859489</v>
+        <v>0.9328677285523379</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2883242195155468</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.834402726695108</v>
+        <v>-4.935757257279135</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.042450799213083</v>
+        <v>1.001908986979472</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2883242195155468</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.674887623175738</v>
+        <v>-4.776242153759765</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.107402685061133</v>
+        <v>1.066860872827522</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1288091159961768</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.530215478076</v>
+        <v>-4.631570008660027</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.175359645662468</v>
+        <v>1.134817833428857</v>
       </c>
       <c r="F1932" t="n">
         <v>0.01586302910356058</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.590090305433693</v>
+        <v>-4.69144483601772</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.137447206120817</v>
+        <v>1.096905393887206</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.04401179825413154</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.503290807654684</v>
+        <v>-4.604645338238711</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.194567498554986</v>
+        <v>1.154025686321375</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.04401179825413154</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.50576051411649</v>
+        <v>-4.607115044700517</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.193652017343676</v>
+        <v>1.153110205110065</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.0464815047159377</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.574130700440501</v>
+        <v>-4.675485231024528</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.177310865288774</v>
+        <v>1.136769053055163</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.03720580567972276</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.452714270814024</v>
+        <v>-4.554068801398051</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.216314145771256</v>
+        <v>1.175772333537645</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.03720580567972276</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.483707430142729</v>
+        <v>-4.585061960726756</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.02862644708016</v>
+        <v>0.9880846348465497</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.03720580567972276</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.30823317035026</v>
+        <v>-4.409587700934287</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.103383382988936</v>
+        <v>1.062841570755325</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.03720580567972276</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.419169422991509</v>
+        <v>-4.520523953575536</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.034750910693644</v>
+        <v>0.9942090984600327</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.03720580567972276</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.622196000534742</v>
+        <v>-4.723550531118769</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9566716648962559</v>
+        <v>0.9161298526626451</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2402323832229561</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.464270401599449</v>
+        <v>-4.565624932183476</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.030014290902505</v>
+        <v>0.9894724786688947</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2402323832229561</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.378026938573071</v>
+        <v>-4.479381469157098</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.059457946686917</v>
+        <v>1.018916134453306</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2402323832229561</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.379210023224132</v>
+        <v>-4.48056455380816</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.050760488271018</v>
+        <v>1.010218676037407</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2458754316894677</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.256082316230049</v>
+        <v>-4.357436846814077</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.100563444101753</v>
+        <v>1.060021631868142</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2458754316894677</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.16327183477919</v>
+        <v>-4.304257644743862</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.066960328573462</v>
+        <v>1.010566004587593</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1530649502386083</v>
+        <v>-0.1926962296192527</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.640786516655721</v>
+        <v>2.617007749027334</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.11470878255816</v>
+        <v>-4.255694592522832</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.088259025386475</v>
+        <v>1.031864701400606</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1045018980175781</v>
+        <v>-0.1441331773982225</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.671797823912939</v>
+        <v>2.648019056284553</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.00203756432191</v>
+        <v>-4.143023374286582</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.128403221192698</v>
+        <v>1.072008897206829</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.00816932021867206</v>
+        <v>-0.03146195916197231</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.734476263366413</v>
+        <v>2.710697495738026</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.889660563139237</v>
+        <v>-4.030646373103909</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.178845317496434</v>
+        <v>1.122450993510566</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.00816932021867206</v>
+        <v>-0.03146195916197231</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.73996755919708</v>
+        <v>2.716188791568693</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.087895132025968</v>
+        <v>-4.228880941990639</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.111048691710281</v>
+        <v>1.054654367724412</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1900652486680585</v>
+        <v>-0.2296965280487029</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.632524019633581</v>
+        <v>2.608745252005194</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.170896413051246</v>
+        <v>-4.311882223015918</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9162038993008228</v>
+        <v>0.8598095753149542</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2086361331952323</v>
+        <v>-0.2482674125758766</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.45973720891793</v>
+        <v>2.435958441289543</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.01170214099467</v>
+        <v>-4.152687950959342</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.100031268842659</v>
+        <v>1.04363694485679</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2086361331952323</v>
+        <v>-0.2482674125758766</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.579886869637135</v>
+        <v>2.556108102008749</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.098300723975773</v>
+        <v>-4.239286533940445</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.079904861752541</v>
+        <v>1.023510537766672</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2086361331952323</v>
+        <v>-0.2482674125758766</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.594399895739458</v>
+        <v>2.570621128111072</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.059917061417622</v>
+        <v>-4.200902871382294</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.09267776811817</v>
+        <v>1.036283444132301</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1702524706370811</v>
+        <v>-0.2098837500177255</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.614849534616718</v>
+        <v>2.591070766988331</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.882800731382456</v>
+        <v>-4.023786541347127</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.160253328977539</v>
+        <v>1.10385900499167</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1702524706370811</v>
+        <v>-0.2098837500177255</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.611578563462019</v>
+        <v>2.587799795833633</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.853098607406162</v>
+        <v>-3.994084417370834</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.172817570329969</v>
+        <v>1.1164232463441</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1747225958523945</v>
+        <v>-0.2143538752330388</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.609579880094745</v>
+        <v>2.585801112466358</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.673723186167394</v>
+        <v>-3.814708996132066</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.23835471413189</v>
+        <v>1.181960390146022</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01794583768167579</v>
+        <v>-0.05757711706232016</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.69743291030359</v>
+        <v>2.673654142675204</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.718737399688</v>
+        <v>-3.859723209652672</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.201156484055238</v>
+        <v>1.144762160069369</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0482947329962804</v>
+        <v>-0.08792601237692477</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.660031028446417</v>
+        <v>2.636252260818031</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.985741909960436</v>
+        <v>-4.126727719925108</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.100046242285209</v>
+        <v>1.04365191829934</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.242657771039229</v>
+        <v>-0.2822890504198733</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.549104767959594</v>
+        <v>2.525326000331207</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.274529130419351</v>
+        <v>-4.415514940384023</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9837352759981446</v>
+        <v>0.9273409520122757</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3437438911382293</v>
+        <v>-0.3833751705188737</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.487657017796695</v>
+        <v>2.463878250168309</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.242053544248579</v>
+        <v>-4.383039354213251</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9943254720207702</v>
+        <v>0.9379311480349015</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3437438911382293</v>
+        <v>-0.3833751705188737</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.485256979351012</v>
+        <v>2.461478211722625</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.807102781585847</v>
+        <v>3.476141404753644</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.223015416541282</v>
+        <v>-4.364001226505954</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9984654423119341</v>
+        <v>0.9420711183260653</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4019275024694239</v>
+        <v>-0.4415587818500682</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.44687153176054</v>
+        <v>2.423092764132153</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>-34.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>133.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-698.4%</t>
+          <t>-691.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.0%</t>
+          <t>442.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-598.0%</t>
+          <t>-595.6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-279.7%</t>
+          <t>-276.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.0%</t>
+          <t>-281.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-84.4%</t>
+          <t>-296.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.1%</t>
+          <t>-264.2%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-203.7%</t>
+          <t>-169.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1962"/>
+  <dimension ref="A1:G1963"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.2910965925453626</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.234572402195674</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.242874325698279</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.219363478078507</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>0.005742833848483953</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.159451965836131</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>0.01078042457607048</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.160044442312503</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.1518456553885681</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>3.073740391950385</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.2176130454379802</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>3.04845104506109</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760745</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5079986410624522</v>
+        <v>-0.4346218681057343</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.922924838799057</v>
+        <v>2.952275547981744</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5897705414902039</v>
+        <v>-0.516393768533486</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.880298804583195</v>
+        <v>2.909649513765882</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6569796493620816</v>
+        <v>-0.5836028764053636</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.858180478268146</v>
+        <v>2.887531187450833</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8645454337536935</v>
+        <v>-0.7911686607969755</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.772978960630741</v>
+        <v>2.802329669813429</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.282299457300531</v>
+        <v>-1.208922684343812</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.60380424271707</v>
+        <v>2.633154951899757</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.503921390858648</v>
+        <v>-1.43054461790193</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.515021685892745</v>
+        <v>2.544372395075432</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.711925449211725</v>
+        <v>-1.638548676255007</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.436712207105439</v>
+        <v>2.466062916288126</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.9233378700997</v>
+        <v>-1.849961097142982</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.347228695088237</v>
+        <v>2.376579404270924</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.262496247688222</v>
+        <v>-2.189119474731505</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.204649643359277</v>
+        <v>2.234000352541964</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.470987029139907</v>
+        <v>-2.397610256183189</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.141591620517372</v>
+        <v>2.170942329700059</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.964311900675085</v>
+        <v>-2.890935127718367</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.952360422311869</v>
+        <v>1.981711131494556</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.456696928699182</v>
+        <v>-3.383320155742464</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.756512803145962</v>
+        <v>1.78586351232865</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.841877319629254</v>
+        <v>-3.768500546672537</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.600983185586797</v>
+        <v>1.630333894769484</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.185560092855917</v>
+        <v>-4.112183319899199</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.465279199750748</v>
+        <v>1.494629908933435</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.392071869742939</v>
+        <v>-4.318695096786221</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.378780547652197</v>
+        <v>1.408131256834884</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.701305972738989</v>
+        <v>-4.627929199782272</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.256859833154036</v>
+        <v>1.286210542336724</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.133111765888777</v>
+        <v>-5.059734992932059</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.070470403361526</v>
+        <v>1.099821112544213</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.367805760021329</v>
+        <v>-5.294428987064611</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9648775807105956</v>
+        <v>0.9942282898932828</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.703468407251782</v>
+        <v>-5.630091634295064</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8291931134743797</v>
+        <v>0.858543822657067</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.067094652152095</v>
+        <v>-5.993717879195377</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6902301757484959</v>
+        <v>0.7195808849311831</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.432222034790842</v>
+        <v>-6.358845261834124</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5434337376988285</v>
+        <v>0.5727844468815158</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.840810811971521</v>
+        <v>-6.767434039014802</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3787597708413162</v>
+        <v>0.4081104800240034</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.253793296112614</v>
+        <v>-7.180416523155896</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.208752209656339</v>
+        <v>0.2381029188390267</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.670185170399612</v>
+        <v>-7.596808397442893</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.04018951055041775</v>
+        <v>0.06954021973310498</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.046862180929455</v>
+        <v>-7.973485407972738</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.100222602992841</v>
+        <v>-0.0708718938101538</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.392737002914265</v>
+        <v>-8.319360229957546</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2424729666410692</v>
+        <v>-0.213122257458382</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.556316881098649</v>
+        <v>-8.48294010814193</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3094999978598221</v>
+        <v>-0.2801492886771348</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.852978222908847</v>
+        <v>-8.779601449952128</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4243855586546932</v>
+        <v>-0.395034849472006</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.976222612124277</v>
+        <v>-8.902845839167558</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4777096188752683</v>
+        <v>-0.4483589096925806</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.359224000866908</v>
+        <v>-9.285847227910189</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6310122756939047</v>
+        <v>-0.601661566511217</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.516622881080028</v>
+        <v>-9.44324610812331</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.691400311807723</v>
+        <v>-0.6620496026250353</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.87615320358403</v>
+        <v>-9.802776430627311</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8298621375112734</v>
+        <v>-0.8005114283285857</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.926502267038252</v>
+        <v>-9.853125494081533</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8420857429357844</v>
+        <v>-0.8127350337530972</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.14565123511245</v>
+        <v>-10.07227446215573</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9267035795436951</v>
+        <v>-0.8973528703610074</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.14196031015604</v>
+        <v>-10.06858353719932</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9252272095611302</v>
+        <v>-0.8958765003784426</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.3462184854859</v>
+        <v>-10.27284171252918</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.001417282574433</v>
+        <v>-0.9720665733917464</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.56425625711708</v>
+        <v>-10.49087948416036</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.084149836742469</v>
+        <v>-1.054799127559781</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.49078642544963</v>
+        <v>-10.41740965249291</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.039390202582068</v>
+        <v>-1.01003949339938</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.66591084283617</v>
+        <v>-10.59253406987946</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.094884748789168</v>
+        <v>-1.065534039606481</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.90036293685066</v>
+        <v>-10.82698616389395</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.19588475129656</v>
+        <v>-1.166534042113872</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.1881667813879</v>
+        <v>-11.11479000843118</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.317678479885432</v>
+        <v>-1.288327770702745</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.877190163033957</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.41799122855173</v>
+        <v>-11.34461445559501</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.408492468912406</v>
+        <v>-1.379141759729718</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.039837700104118</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.65002014828799</v>
+        <v>-11.57664337533127</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.498610308177796</v>
+        <v>-1.469259598995108</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.101850397292541</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.59800463431918</v>
+        <v>-11.52462786136246</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.473813766903869</v>
+        <v>-1.444463057721182</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.101850397292541</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.7396764760433</v>
+        <v>-11.66629970308658</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.531957730492259</v>
+        <v>-1.502607021309572</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.101850397292541</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.69008563161846</v>
+        <v>-11.61670885866174</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.497067982557453</v>
+        <v>-1.467717273374765</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.052259552867707</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.49093352438136</v>
+        <v>-11.41755675142464</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.430458273309296</v>
+        <v>-1.40110756412661</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.886937026917894</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.26508837166195</v>
+        <v>-11.19171159870523</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.330541139185324</v>
+        <v>-1.301190430002636</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.84501035133073</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.14050971532436</v>
+        <v>-11.06713294236764</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.279570532094228</v>
+        <v>-1.25021982291154</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.84501035133073</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.19340500336865</v>
+        <v>-11.12002823041193</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.298094873149835</v>
+        <v>-1.268744163967147</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.840055005242284</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.9094962724399</v>
+        <v>-10.83611949948318</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.178797676539699</v>
+        <v>-1.149446967357011</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.840055005242284</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.83812987983025</v>
+        <v>-10.76475310687353</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.159988381889706</v>
+        <v>-1.130637672707017</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.768688612632636</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.57429301262618</v>
+        <v>-10.50091623966946</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.064337116320985</v>
+        <v>-1.034986407138297</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.768688612632636</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.30705121175778</v>
+        <v>-10.23367443880106</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9592749564729997</v>
+        <v>-0.929924247290312</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.768688612632636</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.20914417308129</v>
+        <v>-10.13576740012457</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9204124559758644</v>
+        <v>-0.8910617467931758</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.700702862772079</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.18519063210534</v>
+        <v>-10.11181385914862</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9101625334399874</v>
+        <v>-0.8808118242572998</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.676749321796122</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.921130693782539</v>
+        <v>-9.847753920825818</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8177988742726212</v>
+        <v>-0.7884481650899327</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.412689383473326</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.214051070277701</v>
+        <v>-9.140674297320981</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5377540585309868</v>
+        <v>-0.5084033493482987</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.412689383473326</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.173866771911511</v>
+        <v>-9.10048999895479</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5213367152966693</v>
+        <v>-0.4919860061139811</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.372505085107135</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.093796976373707</v>
+        <v>-9.020420203416986</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4899419758607908</v>
+        <v>-0.4605912666781027</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.292435289569331</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.860315754144107</v>
+        <v>-8.786938981187387</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3886250581310984</v>
+        <v>-0.3592743489484103</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.058954067339732</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.710649363136593</v>
+        <v>-8.637272590179872</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3316507120410521</v>
+        <v>-0.302300002858364</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.966050576097196</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.578373889505706</v>
+        <v>-8.504997116548985</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2833730358416702</v>
+        <v>-0.2540223266589821</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.83377510246631</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.387774214832552</v>
+        <v>-8.314397441875832</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2043181052847718</v>
+        <v>-0.1749673961020837</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.643175427793157</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.138774416148971</v>
+        <v>-8.06539764319225</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.09181184458768099</v>
+        <v>-0.06246113540499243</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.643175427793157</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.244364405922076</v>
+        <v>-8.170987632965355</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2620237700961412</v>
+        <v>-0.2326730609134531</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.748765417566261</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.263099308040672</v>
+        <v>-8.189722535083952</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2209733890664936</v>
+        <v>-0.1916226798838054</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.748765417566261</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.115159266633073</v>
+        <v>-8.041782493676353</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2816762951916214</v>
+        <v>-0.2523255860089333</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.728444501657704</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.090930630244101</v>
+        <v>-8.01755385728738</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2806988268895108</v>
+        <v>-0.2513481177068226</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.704215865268731</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.047382223473409</v>
+        <v>-7.97400545051669</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2702400762763273</v>
+        <v>-0.2408893670936396</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.704215865268731</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.805233830019551</v>
+        <v>-7.821490268122914</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1589183645136409</v>
+        <v>-0.165420939754986</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.704215865268731</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.742004458251203</v>
+        <v>-7.758260896354566</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1390944953471065</v>
+        <v>-0.1455970705884519</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.704215865268731</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.618713323434072</v>
+        <v>-7.634969761537435</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.09227994740967738</v>
+        <v>-0.09878252265102239</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.580924730451601</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.597564124530629</v>
+        <v>-7.613820562633991</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.07611928961097503</v>
+        <v>-0.08262186485232004</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.559775531548158</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.353798682547184</v>
+        <v>-7.370055120650547</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.01716759552945346</v>
+        <v>0.01066502028810845</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.559775531548158</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.089770615353924</v>
+        <v>-7.106027053457288</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1249031363267736</v>
+        <v>0.1184005610854282</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.357910132732204</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.839920221404849</v>
+        <v>-6.856176659508213</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2175853688901057</v>
+        <v>0.2110827936487603</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.357910132732204</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.664028128937417</v>
+        <v>-6.680284567040781</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2915413293977274</v>
+        <v>0.2850387541563819</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.357910132732204</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.492581665914954</v>
+        <v>-6.508838104018317</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3734474206612663</v>
+        <v>0.3669448454199209</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.186463669709741</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.267548666246131</v>
+        <v>-6.283805104349494</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4624810981450924</v>
+        <v>0.455978522903747</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.961430670040918</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.052914288609724</v>
+        <v>-6.069170726713088</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5530296502539724</v>
+        <v>0.546527075012627</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7467962924045112</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.959914247403826</v>
+        <v>-5.976170685507189</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5714239255201274</v>
+        <v>0.564921350278782</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7467962924045112</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.719483750598966</v>
+        <v>-5.735740188702329</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6693392008669488</v>
+        <v>0.6628366256256033</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5063657955996509</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.647241182427771</v>
+        <v>-5.663497620531134</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7021655419702468</v>
+        <v>0.6956629667289014</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5063657955996509</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.531301332802586</v>
+        <v>-5.547557770905949</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7492200657376613</v>
+        <v>0.7427174904963159</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.429544064583527</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288645744379423</v>
+        <v>-5.304902182482786</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8432803723269195</v>
+        <v>0.8367777970855741</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.429544064583527</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068624946342412</v>
+        <v>-5.084881384445776</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9328677285523379</v>
+        <v>0.9263651533109925</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2883242195155468</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935757257279135</v>
+        <v>-4.952013695382498</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001908986979472</v>
+        <v>0.9954064117381269</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2883242195155468</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.776242153759765</v>
+        <v>-4.792498591863128</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.066860872827522</v>
+        <v>1.060358297586177</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1288091159961768</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.631570008660027</v>
+        <v>-4.647826446763391</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.134817833428857</v>
+        <v>1.128315258187512</v>
       </c>
       <c r="F1932" t="n">
         <v>0.01586302910356058</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412105</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.69144483601772</v>
+        <v>-4.707701274121083</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.096905393887206</v>
+        <v>1.090402818645861</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.04401179825413154</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.604645338238711</v>
+        <v>-4.620901776342075</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.154025686321375</v>
+        <v>1.14752311108003</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.04401179825413154</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.607115044700517</v>
+        <v>-4.623371482803881</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.153110205110065</v>
+        <v>1.14660762986872</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.0464815047159377</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.675485231024528</v>
+        <v>-4.691741669127891</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.136769053055163</v>
+        <v>1.130266477813818</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.03720580567972276</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.554068801398051</v>
+        <v>-4.570325239501415</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.175772333537645</v>
+        <v>1.169269758296299</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.03720580567972276</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.585061960726756</v>
+        <v>-4.60131839883012</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9880846348465497</v>
+        <v>0.9815820596052043</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.03720580567972276</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.409587700934287</v>
+        <v>-4.42584413903765</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.062841570755325</v>
+        <v>1.05633899551398</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.03720580567972276</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.520523953575536</v>
+        <v>-4.536780391678899</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9942090984600327</v>
+        <v>0.9877065232186872</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.03720580567972276</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.723550531118769</v>
+        <v>-4.739806969222133</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9161298526626451</v>
+        <v>0.9096272774212997</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2402323832229561</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.565624932183476</v>
+        <v>-4.58188137028684</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9894724786688947</v>
+        <v>0.9829699034275492</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2402323832229561</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.479381469157098</v>
+        <v>-4.495637907260462</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.018916134453306</v>
+        <v>1.012413559211961</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2402323832229561</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.48056455380816</v>
+        <v>-4.496820991911523</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.010218676037407</v>
+        <v>1.003716100796062</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2458754316894677</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.357436846814077</v>
+        <v>-4.37369328491744</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.060021631868142</v>
+        <v>1.053519056626796</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2458754316894677</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.304257644743862</v>
+        <v>-4.28088280346658</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.010566004587593</v>
+        <v>1.019915941098506</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1926962296192527</v>
+        <v>-0.1530649502386083</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.617007749027334</v>
+        <v>2.640786516655721</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.255694592522832</v>
+        <v>-4.232319751245551</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.031864701400606</v>
+        <v>1.041214637911519</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1441331773982225</v>
+        <v>-0.1045018980175781</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.648019056284553</v>
+        <v>2.671797823912939</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.143023374286582</v>
+        <v>-4.1196485330093</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.072008897206829</v>
+        <v>1.081358833717742</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03146195916197231</v>
+        <v>0.00816932021867206</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.710697495738026</v>
+        <v>2.734476263366413</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.030646373103909</v>
+        <v>-4.007271531826628</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.122450993510566</v>
+        <v>1.131800930021478</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03146195916197231</v>
+        <v>0.00816932021867206</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.716188791568693</v>
+        <v>2.73996755919708</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.228880941990639</v>
+        <v>-4.205506100713359</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.054654367724412</v>
+        <v>1.064004304235325</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2296965280487029</v>
+        <v>-0.1900652486680585</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608745252005194</v>
+        <v>2.632524019633581</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.311882223015918</v>
+        <v>-4.288507381738638</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8598095753149542</v>
+        <v>0.8691595118258666</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2482674125758766</v>
+        <v>-0.2086361331952323</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.435958441289543</v>
+        <v>2.45973720891793</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.152687950959342</v>
+        <v>-4.129313109682061</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.04363694485679</v>
+        <v>1.052986881367703</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2482674125758766</v>
+        <v>-0.2086361331952323</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556108102008749</v>
+        <v>2.579886869637135</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.239286533940445</v>
+        <v>-4.215911692663164</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.023510537766672</v>
+        <v>1.032860474277585</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2482674125758766</v>
+        <v>-0.2086361331952323</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570621128111072</v>
+        <v>2.594399895739458</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.200902871382294</v>
+        <v>-4.177528030105013</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.036283444132301</v>
+        <v>1.045633380643214</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2098837500177255</v>
+        <v>-0.1702524706370811</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.591070766988331</v>
+        <v>2.614849534616718</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.023786541347127</v>
+        <v>-4.000411700069847</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.10385900499167</v>
+        <v>1.113208941502582</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2098837500177255</v>
+        <v>-0.1702524706370811</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587799795833633</v>
+        <v>2.611578563462019</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.994084417370834</v>
+        <v>-3.970709576093554</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.1164232463441</v>
+        <v>1.125773182855013</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2143538752330388</v>
+        <v>-0.1747225958523945</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.585801112466358</v>
+        <v>2.609579880094745</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.814708996132066</v>
+        <v>-3.791334154854786</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.181960390146022</v>
+        <v>1.191310326656934</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05757711706232016</v>
+        <v>-0.01794583768167579</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.673654142675204</v>
+        <v>2.69743291030359</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.859723209652672</v>
+        <v>-3.836348368375392</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.144762160069369</v>
+        <v>1.154112096580281</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08792601237692477</v>
+        <v>-0.0482947329962804</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.636252260818031</v>
+        <v>2.660031028446417</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.126727719925108</v>
+        <v>-4.103352878647827</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.04365191829934</v>
+        <v>1.053001854810253</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2822890504198733</v>
+        <v>-0.242657771039229</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.525326000331207</v>
+        <v>2.549104767959594</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.415514940384023</v>
+        <v>-4.392140099106743</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9273409520122757</v>
+        <v>0.9366908885231884</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3833751705188737</v>
+        <v>-0.3437438911382293</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.463878250168309</v>
+        <v>2.487657017796695</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.383039354213251</v>
+        <v>-4.359664512935971</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9379311480349015</v>
+        <v>0.9472810845458139</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3833751705188737</v>
+        <v>-0.3437438911382293</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.461478211722625</v>
+        <v>2.485256979351012</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,45 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.476141404753644</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.364001226505954</v>
+        <v>-4.340626385228673</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9420711183260653</v>
+        <v>0.9514210548369777</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4415587818500682</v>
+        <v>-0.4019275024694239</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.423092764132153</v>
+        <v>2.44687153176054</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="2" t="n">
+        <v>45425</v>
+      </c>
+      <c r="B1963" t="n">
+        <v>3.806719880762929</v>
+      </c>
+      <c r="C1963" t="n">
+        <v>2.773465375508851</v>
+      </c>
+      <c r="D1963" t="n">
+        <v>-4.340626385228673</v>
+      </c>
+      <c r="E1963" t="n">
+        <v>0.9514210548369777</v>
+      </c>
+      <c r="F1963" t="n">
+        <v>-0.4019275024694239</v>
+      </c>
+      <c r="G1963" t="n">
+        <v>2.766529172495218</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-53.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.1%</t>
+          <t>133.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-691.0%</t>
+          <t>-698.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-53.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>442.0%</t>
+          <t>446.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.6%</t>
+          <t>-598.0%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-276.8%</t>
+          <t>-279.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.1%</t>
+          <t>-282.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-296.2%</t>
+          <t>-84.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.2%</t>
+          <t>-268.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.4%</t>
+          <t>-188.4%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2910965925453626</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.234572402195674</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.242874325698279</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.219363478078507</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.005742833848483953</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.159451965836131</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.01078042457607048</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.160044442312503</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1518456553885681</v>
+        <v>-0.2252224283452861</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.073740391950385</v>
+        <v>3.044389682767698</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2176130454379802</v>
+        <v>-0.2909898183946981</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.04845104506109</v>
+        <v>3.019100335878403</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4346218681057343</v>
+        <v>-0.5079986410624522</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.952275547981744</v>
+        <v>2.922924838799057</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.516393768533486</v>
+        <v>-0.5897705414902039</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.909649513765882</v>
+        <v>2.880298804583195</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5836028764053636</v>
+        <v>-0.6569796493620816</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.887531187450833</v>
+        <v>2.858180478268146</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7911686607969755</v>
+        <v>-0.8645454337536935</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.802329669813429</v>
+        <v>2.772978960630741</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.208922684343812</v>
+        <v>-1.282299457300531</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.633154951899757</v>
+        <v>2.60380424271707</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.43054461790193</v>
+        <v>-1.503921390858648</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.544372395075432</v>
+        <v>2.515021685892745</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.638548676255007</v>
+        <v>-1.711925449211725</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.466062916288126</v>
+        <v>2.436712207105439</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.849961097142982</v>
+        <v>-1.9233378700997</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.376579404270924</v>
+        <v>2.347228695088237</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.189119474731505</v>
+        <v>-2.262496247688222</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.234000352541964</v>
+        <v>2.204649643359277</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.397610256183189</v>
+        <v>-2.470987029139907</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.170942329700059</v>
+        <v>2.141591620517372</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.890935127718367</v>
+        <v>-2.964311900675085</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.981711131494556</v>
+        <v>1.952360422311869</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.383320155742464</v>
+        <v>-3.456696928699182</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.78586351232865</v>
+        <v>1.756512803145962</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.768500546672537</v>
+        <v>-3.841877319629254</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.630333894769484</v>
+        <v>1.600983185586797</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.112183319899199</v>
+        <v>-4.185560092855917</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.494629908933435</v>
+        <v>1.465279199750748</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.318695096786221</v>
+        <v>-4.392071869742939</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.408131256834884</v>
+        <v>1.378780547652197</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.627929199782272</v>
+        <v>-4.701305972738989</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.286210542336724</v>
+        <v>1.256859833154036</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.059734992932059</v>
+        <v>-5.133111765888777</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.099821112544213</v>
+        <v>1.070470403361526</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.294428987064611</v>
+        <v>-5.367805760021329</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9942282898932828</v>
+        <v>0.9648775807105956</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.630091634295064</v>
+        <v>-5.703468407251782</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.858543822657067</v>
+        <v>0.8291931134743797</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.993717879195377</v>
+        <v>-6.067094652152095</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7195808849311831</v>
+        <v>0.6902301757484959</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.358845261834124</v>
+        <v>-6.432222034790842</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5727844468815158</v>
+        <v>0.5434337376988285</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.767434039014802</v>
+        <v>-6.840810811971521</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4081104800240034</v>
+        <v>0.3787597708413162</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.180416523155896</v>
+        <v>-7.253793296112614</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2381029188390267</v>
+        <v>0.208752209656339</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.596808397442893</v>
+        <v>-7.670185170399612</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.06954021973310498</v>
+        <v>0.04018951055041775</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.973485407972738</v>
+        <v>-8.046862180929455</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0708718938101538</v>
+        <v>-0.100222602992841</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.319360229957546</v>
+        <v>-8.392737002914265</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.213122257458382</v>
+        <v>-0.2424729666410692</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.48294010814193</v>
+        <v>-8.556316881098649</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2801492886771348</v>
+        <v>-0.3094999978598221</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.779601449952128</v>
+        <v>-8.852978222908847</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.395034849472006</v>
+        <v>-0.4243855586546932</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.902845839167558</v>
+        <v>-8.976222612124277</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4483589096925806</v>
+        <v>-0.4777096188752683</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.285847227910189</v>
+        <v>-9.359224000866908</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.601661566511217</v>
+        <v>-0.6310122756939047</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.44324610812331</v>
+        <v>-9.516622881080028</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6620496026250353</v>
+        <v>-0.691400311807723</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.802776430627311</v>
+        <v>-9.87615320358403</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8005114283285857</v>
+        <v>-0.8298621375112734</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.853125494081533</v>
+        <v>-9.926502267038252</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8127350337530972</v>
+        <v>-0.8420857429357844</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.07227446215573</v>
+        <v>-10.14565123511245</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8973528703610074</v>
+        <v>-0.9267035795436951</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.06858353719932</v>
+        <v>-10.14196031015604</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8958765003784426</v>
+        <v>-0.9252272095611302</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.27284171252918</v>
+        <v>-10.3462184854859</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9720665733917464</v>
+        <v>-1.001417282574433</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.49087948416036</v>
+        <v>-10.56425625711708</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.054799127559781</v>
+        <v>-1.084149836742469</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.41740965249291</v>
+        <v>-10.49078642544963</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.01003949339938</v>
+        <v>-1.039390202582068</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.59253406987946</v>
+        <v>-10.66591084283617</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.065534039606481</v>
+        <v>-1.094884748789168</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.82698616389395</v>
+        <v>-10.90036293685066</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.166534042113872</v>
+        <v>-1.19588475129656</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.11479000843118</v>
+        <v>-11.1881667813879</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.288327770702745</v>
+        <v>-1.317678479885432</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.877190163033957</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.34461445559501</v>
+        <v>-11.41799122855173</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.379141759729718</v>
+        <v>-1.408492468912406</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.039837700104118</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.57664337533127</v>
+        <v>-11.65002014828799</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.469259598995108</v>
+        <v>-1.498610308177796</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.101850397292541</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.52462786136246</v>
+        <v>-11.59800463431918</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.444463057721182</v>
+        <v>-1.473813766903869</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.101850397292541</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.66629970308658</v>
+        <v>-11.7396764760433</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.502607021309572</v>
+        <v>-1.531957730492259</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.101850397292541</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.61670885866174</v>
+        <v>-11.69008563161846</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.467717273374765</v>
+        <v>-1.497067982557453</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.052259552867707</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.41755675142464</v>
+        <v>-11.49093352438136</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.40110756412661</v>
+        <v>-1.430458273309296</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.886937026917894</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.19171159870523</v>
+        <v>-11.26508837166195</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.301190430002636</v>
+        <v>-1.330541139185324</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.84501035133073</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.06713294236764</v>
+        <v>-11.14050971532436</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.25021982291154</v>
+        <v>-1.279570532094228</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.84501035133073</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.12002823041193</v>
+        <v>-11.19340500336865</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.268744163967147</v>
+        <v>-1.298094873149835</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.840055005242284</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83611949948318</v>
+        <v>-10.9094962724399</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.149446967357011</v>
+        <v>-1.178797676539699</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.840055005242284</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.76475310687353</v>
+        <v>-10.83812987983025</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.130637672707017</v>
+        <v>-1.159988381889706</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.768688612632636</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.50091623966946</v>
+        <v>-10.57429301262618</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.034986407138297</v>
+        <v>-1.064337116320985</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.768688612632636</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.23367443880106</v>
+        <v>-10.30705121175778</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.929924247290312</v>
+        <v>-0.9592749564729997</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.768688612632636</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.13576740012457</v>
+        <v>-10.20914417308129</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8910617467931758</v>
+        <v>-0.9204124559758644</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.700702862772079</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.11181385914862</v>
+        <v>-10.18519063210534</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8808118242572998</v>
+        <v>-0.9101625334399874</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.676749321796122</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.847753920825818</v>
+        <v>-9.921130693782539</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7884481650899327</v>
+        <v>-0.8177988742726212</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.412689383473326</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.140674297320981</v>
+        <v>-9.214051070277701</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5084033493482987</v>
+        <v>-0.5377540585309868</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.412689383473326</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.10048999895479</v>
+        <v>-9.173866771911511</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4919860061139811</v>
+        <v>-0.5213367152966693</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.372505085107135</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.020420203416986</v>
+        <v>-9.093796976373707</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4605912666781027</v>
+        <v>-0.4899419758607908</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.292435289569331</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.786938981187387</v>
+        <v>-8.860315754144107</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3592743489484103</v>
+        <v>-0.3886250581310984</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.058954067339732</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.637272590179872</v>
+        <v>-8.710649363136593</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.302300002858364</v>
+        <v>-0.3316507120410521</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.966050576097196</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.504997116548985</v>
+        <v>-8.578373889505706</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2540223266589821</v>
+        <v>-0.2833730358416702</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.83377510246631</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.314397441875832</v>
+        <v>-8.387774214832552</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1749673961020837</v>
+        <v>-0.2043181052847718</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.643175427793157</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.06539764319225</v>
+        <v>-8.138774416148971</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.06246113540499243</v>
+        <v>-0.09181184458768099</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.643175427793157</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.170987632965355</v>
+        <v>-8.244364405922076</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2326730609134531</v>
+        <v>-0.2620237700961412</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.748765417566261</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.189722535083952</v>
+        <v>-8.263099308040672</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1916226798838054</v>
+        <v>-0.2209733890664936</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.748765417566261</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.041782493676353</v>
+        <v>-8.115159266633073</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2523255860089333</v>
+        <v>-0.2816762951916214</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.728444501657704</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.01755385728738</v>
+        <v>-8.090930630244101</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2513481177068226</v>
+        <v>-0.2806988268895108</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.704215865268731</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.97400545051669</v>
+        <v>-8.047382223473409</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2408893670936396</v>
+        <v>-0.2702400762763273</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.704215865268731</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.821490268122914</v>
+        <v>-7.805233830019551</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.165420939754986</v>
+        <v>-0.1589183645136409</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.704215865268731</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.758260896354566</v>
+        <v>-7.742004458251203</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1455970705884519</v>
+        <v>-0.1390944953471065</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.704215865268731</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262046</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.634969761537435</v>
+        <v>-7.618713323434072</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.09878252265102239</v>
+        <v>-0.09227994740967738</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.580924730451601</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.613820562633991</v>
+        <v>-7.597564124530629</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.08262186485232004</v>
+        <v>-0.07611928961097503</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.559775531548158</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.370055120650547</v>
+        <v>-7.353798682547184</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.01066502028810845</v>
+        <v>0.01716759552945346</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.559775531548158</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.106027053457288</v>
+        <v>-7.089770615353924</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1184005610854282</v>
+        <v>0.1249031363267736</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.357910132732204</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.856176659508213</v>
+        <v>-6.839920221404849</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2110827936487603</v>
+        <v>0.2175853688901057</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.357910132732204</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.680284567040781</v>
+        <v>-6.664028128937417</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2850387541563819</v>
+        <v>0.2915413293977274</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.357910132732204</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.508838104018317</v>
+        <v>-6.492581665914954</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3669448454199209</v>
+        <v>0.3734474206612663</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.186463669709741</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.283805104349494</v>
+        <v>-6.267548666246131</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.455978522903747</v>
+        <v>0.4624810981450924</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.961430670040918</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.069170726713088</v>
+        <v>-6.052914288609724</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.546527075012627</v>
+        <v>0.5530296502539724</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7467962924045112</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.976170685507189</v>
+        <v>-5.959914247403826</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.564921350278782</v>
+        <v>0.5714239255201274</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7467962924045112</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.735740188702329</v>
+        <v>-5.719483750598966</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6628366256256033</v>
+        <v>0.6693392008669488</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5063657955996509</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.663497620531134</v>
+        <v>-5.647241182427771</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6956629667289014</v>
+        <v>0.7021655419702468</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5063657955996509</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.547557770905949</v>
+        <v>-5.531301332802586</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7427174904963159</v>
+        <v>0.7492200657376613</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.429544064583527</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.304902182482786</v>
+        <v>-5.288645744379423</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8367777970855741</v>
+        <v>0.8432803723269195</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.429544064583527</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.084881384445776</v>
+        <v>-5.068624946342412</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9263651533109925</v>
+        <v>0.9328677285523379</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2883242195155468</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.952013695382498</v>
+        <v>-4.935757257279135</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9954064117381269</v>
+        <v>1.001908986979472</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2883242195155468</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.792498591863128</v>
+        <v>-4.776242153759765</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.060358297586177</v>
+        <v>1.066860872827522</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1288091159961768</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.647826446763391</v>
+        <v>-4.631570008660027</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.128315258187512</v>
+        <v>1.134817833428857</v>
       </c>
       <c r="F1932" t="n">
         <v>0.01586302910356058</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.707701274121083</v>
+        <v>-4.69144483601772</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.090402818645861</v>
+        <v>1.096905393887206</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.04401179825413154</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.620901776342075</v>
+        <v>-4.604645338238711</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.14752311108003</v>
+        <v>1.154025686321375</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.04401179825413154</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.623371482803881</v>
+        <v>-4.607115044700517</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.14660762986872</v>
+        <v>1.153110205110065</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.0464815047159377</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.691741669127891</v>
+        <v>-4.675485231024528</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.130266477813818</v>
+        <v>1.136769053055163</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.03720580567972276</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.570325239501415</v>
+        <v>-4.554068801398051</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.169269758296299</v>
+        <v>1.175772333537645</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.03720580567972276</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.60131839883012</v>
+        <v>-4.585061960726756</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9815820596052043</v>
+        <v>0.9880846348465497</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.03720580567972276</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.42584413903765</v>
+        <v>-4.409587700934287</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.05633899551398</v>
+        <v>1.062841570755325</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.03720580567972276</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.536780391678899</v>
+        <v>-4.520523953575536</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9877065232186872</v>
+        <v>0.9942090984600327</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.03720580567972276</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581288</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.739806969222133</v>
+        <v>-4.723550531118769</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9096272774212997</v>
+        <v>0.9161298526626451</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2402323832229561</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.58188137028684</v>
+        <v>-4.565624932183476</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9829699034275492</v>
+        <v>0.9894724786688947</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2402323832229561</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.495637907260462</v>
+        <v>-4.479381469157098</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.012413559211961</v>
+        <v>1.018916134453306</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2402323832229561</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.496820991911523</v>
+        <v>-4.48056455380816</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.003716100796062</v>
+        <v>1.010218676037407</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2458754316894677</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273188</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.37369328491744</v>
+        <v>-4.357436846814077</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.053519056626796</v>
+        <v>1.060021631868142</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2458754316894677</v>
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.28088280346658</v>
+        <v>-4.304257644743862</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.019915941098506</v>
+        <v>1.010566004587593</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1530649502386083</v>
+        <v>-0.1926962296192527</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.640786516655721</v>
+        <v>2.617007749027334</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.232319751245551</v>
+        <v>-4.255694592522832</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.041214637911519</v>
+        <v>1.031864701400606</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1045018980175781</v>
+        <v>-0.1441331773982225</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.671797823912939</v>
+        <v>2.648019056284553</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.1196485330093</v>
+        <v>-4.143023374286582</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.081358833717742</v>
+        <v>1.072008897206829</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.00816932021867206</v>
+        <v>-0.03146195916197231</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.734476263366413</v>
+        <v>2.710697495738026</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.007271531826628</v>
+        <v>-4.030646373103909</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.131800930021478</v>
+        <v>1.122450993510566</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.00816932021867206</v>
+        <v>-0.03146195916197231</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.73996755919708</v>
+        <v>2.716188791568693</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968859</v>
+        <v>3.689594264968858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.205506100713359</v>
+        <v>-4.228880941990639</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.064004304235325</v>
+        <v>1.054654367724412</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1900652486680585</v>
+        <v>-0.2296965280487029</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.632524019633581</v>
+        <v>2.608745252005194</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306604617532</v>
+        <v>3.643066046175319</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.288507381738638</v>
+        <v>-4.311882223015918</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8691595118258666</v>
+        <v>0.8598095753149542</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2086361331952323</v>
+        <v>-0.2482674125758766</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.45973720891793</v>
+        <v>2.435958441289543</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.129313109682061</v>
+        <v>-4.152687950959342</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.052986881367703</v>
+        <v>1.04363694485679</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2086361331952323</v>
+        <v>-0.2482674125758766</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.579886869637135</v>
+        <v>2.556108102008749</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.215911692663164</v>
+        <v>-4.239286533940445</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.032860474277585</v>
+        <v>1.023510537766672</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2086361331952323</v>
+        <v>-0.2482674125758766</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.594399895739458</v>
+        <v>2.570621128111072</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.74117049438342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.177528030105013</v>
+        <v>-4.200902871382294</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.045633380643214</v>
+        <v>1.036283444132301</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1702524706370811</v>
+        <v>-0.2098837500177255</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.614849534616718</v>
+        <v>2.591070766988331</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.000411700069847</v>
+        <v>-4.023786541347127</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.113208941502582</v>
+        <v>1.10385900499167</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1702524706370811</v>
+        <v>-0.2098837500177255</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.611578563462019</v>
+        <v>2.587799795833633</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.970709576093554</v>
+        <v>-3.994084417370834</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.125773182855013</v>
+        <v>1.1164232463441</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1747225958523945</v>
+        <v>-0.2143538752330388</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.609579880094745</v>
+        <v>2.585801112466358</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.791334154854786</v>
+        <v>-3.814708996132066</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.191310326656934</v>
+        <v>1.181960390146022</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01794583768167579</v>
+        <v>-0.05757711706232016</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.69743291030359</v>
+        <v>2.673654142675204</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.836348368375392</v>
+        <v>-3.859723209652672</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.154112096580281</v>
+        <v>1.144762160069369</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0482947329962804</v>
+        <v>-0.08792601237692477</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.660031028446417</v>
+        <v>2.636252260818031</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.103352878647827</v>
+        <v>-4.126727719925108</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.053001854810253</v>
+        <v>1.04365191829934</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.242657771039229</v>
+        <v>-0.2822890504198733</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.549104767959594</v>
+        <v>2.525326000331207</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230804</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.392140099106743</v>
+        <v>-4.415514940384023</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9366908885231884</v>
+        <v>0.9273409520122757</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3437438911382293</v>
+        <v>-0.3833751705188737</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.487657017796695</v>
+        <v>2.463878250168309</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.359664512935971</v>
+        <v>-4.383039354213251</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9472810845458139</v>
+        <v>0.9379311480349015</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3437438911382293</v>
+        <v>-0.3833751705188737</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.485256979351012</v>
+        <v>2.461478211722625</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.340626385228673</v>
+        <v>-4.364001226505954</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9514210548369777</v>
+        <v>0.9420711183260653</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4019275024694239</v>
+        <v>-0.4415587818500682</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.44687153176054</v>
+        <v>2.423092764132153</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.806719880762929</v>
+        <v>3.477056974109338</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.773465375508851</v>
+        <v>2.583475150789387</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.340626385228673</v>
+        <v>-4.364001226505954</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9514210548369777</v>
+        <v>0.9420711183260653</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4019275024694239</v>
+        <v>-0.4415587818500682</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.766529172495218</v>
+        <v>2.576538947775755</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-45.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.4%</t>
+          <t>133.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-698.4%</t>
+          <t>-704.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.4%</t>
+          <t>-53.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.0%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-598.0%</t>
+          <t>-600.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-279.7%</t>
+          <t>-282.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-40.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.0%</t>
+          <t>-282.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-312.6%</t>
+          <t>-318.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-84.4%</t>
+          <t>-124.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.1%</t>
+          <t>-270.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-188.0%</t>
+          <t>-191.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-188.4%</t>
+          <t>-180.4%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.1087228009644963</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.165702868184994</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.657162997990651</v>
+        <v>1.596388246213587</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.116867970907334</v>
+        <v>4.080403119841095</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>-0.1284086908852988</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.105791355942618</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.657162997990651</v>
+        <v>1.596388246213587</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.151809055404875</v>
+        <v>4.115344204338637</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>-0.1233711001577123</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.10638383241899</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.712807454256969</v>
+        <v>1.652032702479904</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.147308318283764</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.2859971801223509</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.044389682767698</v>
+        <v>3.020079782056872</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.55018137429233</v>
+        <v>1.489406622515265</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.064943902994957</v>
+        <v>4.028479051928719</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.3517645701717629</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.019100335878403</v>
+        <v>2.994790435167577</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.55018137429233</v>
+        <v>1.489406622515265</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.065961512125428</v>
+        <v>4.029496661059189</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5079986410624522</v>
+        <v>-0.5687733928395171</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.922924838799057</v>
+        <v>2.898614938088231</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.55018137429233</v>
+        <v>1.489406622515265</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.056589544113184</v>
+        <v>4.020124693046944</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5897705414902039</v>
+        <v>-0.6505452932672688</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.880298804583195</v>
+        <v>2.855988903872369</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.577216947698467</v>
+        <v>1.516442195921402</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.062893614112104</v>
+        <v>4.026428763045865</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6569796493620816</v>
+        <v>-0.7177544011391466</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.858180478268146</v>
+        <v>2.83387057755732</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.577216947698467</v>
+        <v>1.516442195921402</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.067658930945806</v>
+        <v>4.031194079879567</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8645454337536935</v>
+        <v>-0.9253201855307585</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.772978960630741</v>
+        <v>2.748669059919916</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.369651163306855</v>
+        <v>1.30887641152979</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940944256430079</v>
+        <v>3.904479405363841</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.282299457300531</v>
+        <v>-1.343074209077596</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.60380424271707</v>
+        <v>2.579494342006244</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9518971397600179</v>
+        <v>0.891122387982953</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.68821873380704</v>
+        <v>3.651753882740802</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.503921390858648</v>
+        <v>-1.564696142635713</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.515021685892745</v>
+        <v>2.490711785181919</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9143710060726489</v>
+        <v>0.8535962542955839</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.665569270193541</v>
+        <v>3.629104419127302</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.711925449211725</v>
+        <v>-1.77270020098879</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.436712207105439</v>
+        <v>2.412402306394613</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9143710060726489</v>
+        <v>0.8535962542955839</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.670461414747466</v>
+        <v>3.633996563681227</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.9233378700997</v>
+        <v>-1.984112621876765</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.347228695088237</v>
+        <v>2.322918794377411</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7029585851846738</v>
+        <v>0.6421838334076089</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.538695418552669</v>
+        <v>3.50223056748643</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.262496247688222</v>
+        <v>-2.323270999465287</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.204649643359277</v>
+        <v>2.180339742648451</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3638002075961517</v>
+        <v>0.3030254558190868</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.328284691306005</v>
+        <v>3.291819840239766</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.470987029139907</v>
+        <v>-2.531761780916972</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.141591620517372</v>
+        <v>2.117281719806546</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1553094261444673</v>
+        <v>0.09453467436740237</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.223528512173762</v>
+        <v>3.187063661107524</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.964311900675085</v>
+        <v>-3.02508665245215</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.952360422311869</v>
+        <v>1.928050521601043</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.05032331190484857</v>
+        <v>-0.01045143987221636</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.16863559403856</v>
+        <v>3.132170742972321</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.456696928699182</v>
+        <v>-3.517471680476247</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.756512803145962</v>
+        <v>1.732202902435137</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4420617161192482</v>
+        <v>-0.5028364678963131</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.874310969267834</v>
+        <v>2.837846118201595</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.841877319629254</v>
+        <v>-3.902652071406319</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.600983185586797</v>
+        <v>1.576673284875971</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4420617161192482</v>
+        <v>-0.5028364678963131</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.872853508080697</v>
+        <v>2.836388657014458</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.185560092855917</v>
+        <v>-4.246334844632982</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.465279199750748</v>
+        <v>1.440969299039922</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5499677681464663</v>
+        <v>-0.6107425199235312</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.809879000318983</v>
+        <v>2.773414149252744</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.392071869742939</v>
+        <v>-4.452846621520004</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.378780547652197</v>
+        <v>1.354470646941371</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7564795450334878</v>
+        <v>-0.8172542968105527</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.682077992843027</v>
+        <v>2.645613141776789</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.701305972738989</v>
+        <v>-4.762080724516054</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.256859833154036</v>
+        <v>1.23254993244321</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7564795450334878</v>
+        <v>-0.8172542968105527</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.683850919543287</v>
+        <v>2.647386068477048</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.133111765888777</v>
+        <v>-5.193886517665842</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.070470403361526</v>
+        <v>1.0461605026507</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8928970414747548</v>
+        <v>-0.9536717932518197</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.588333309145932</v>
+        <v>2.551868458079692</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.367805760021329</v>
+        <v>-5.428580511798394</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9648775807105956</v>
+        <v>0.9405676799997695</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8865607742454996</v>
+        <v>-0.9473355260225645</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.580419844485575</v>
+        <v>2.543954993419336</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.703468407251782</v>
+        <v>-5.764243159028847</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8291931134743797</v>
+        <v>0.8048832127635537</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8865607742454996</v>
+        <v>-0.9473355260225645</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.57900043614154</v>
+        <v>2.542535585075301</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.067094652152095</v>
+        <v>-6.12786940392916</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6902301757484959</v>
+        <v>0.6659202750376698</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9847824111126254</v>
+        <v>-1.04555716288969</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.526555014255506</v>
+        <v>2.490090163189267</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.432222034790842</v>
+        <v>-6.492996786567907</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5434337376988285</v>
+        <v>0.5191238369880025</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.281093195411638</v>
+        <v>-1.341867947188703</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.34802305868193</v>
+        <v>2.311558207615692</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.840810811971521</v>
+        <v>-6.901585563748585</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3787597708413162</v>
+        <v>0.3544498701304906</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.750456724369381</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.101631336388282</v>
+        <v>2.065166485322043</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.253793296112614</v>
+        <v>-7.314568047889678</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.208752209656339</v>
+        <v>0.1844423089455134</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.750456724369381</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.096816768859743</v>
+        <v>2.060351917793504</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.670185170399612</v>
+        <v>-7.730959922176676</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.04018951055041775</v>
+        <v>0.01587960983959213</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.750456724369381</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.09481081946862</v>
+        <v>2.058345968402381</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.046862180929455</v>
+        <v>-8.107636932706519</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.100222602992841</v>
+        <v>-0.1245325037036666</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.750456724369381</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.105069510137299</v>
+        <v>2.068604659071061</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.392737002914265</v>
+        <v>-8.453511754691329</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2424729666410692</v>
+        <v>-0.2667828673518948</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.750456724369381</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.101169075282995</v>
+        <v>2.064704224216755</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.556316881098649</v>
+        <v>-8.617091632875713</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3094999978598221</v>
+        <v>-0.3338098985706477</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.750456724369381</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.099573995337995</v>
+        <v>2.063109144271756</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.852978222908847</v>
+        <v>-8.913752974685911</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4243855586546932</v>
+        <v>-0.4486954593655188</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.81919986010326</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.062107089826876</v>
+        <v>2.025642238760637</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.976222612124277</v>
+        <v>-9.036997363901341</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4777096188752683</v>
+        <v>-0.5020195195860939</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.81919986010326</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.058080785292473</v>
+        <v>2.021615934226234</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.359224000866908</v>
+        <v>-9.419998752643972</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6310122756939047</v>
+        <v>-0.6553221764047303</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.81919986010326</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.057978683970889</v>
+        <v>2.02151383290465</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.516622881080028</v>
+        <v>-9.577397632857092</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.691400311807723</v>
+        <v>-0.7157102125185486</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.915823988539316</v>
+        <v>-1.976598740316381</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.966110871814446</v>
+        <v>1.929646020748208</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.87615320358403</v>
+        <v>-9.936927955361094</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8298621375112734</v>
+        <v>-0.854172038222099</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.915823988539316</v>
+        <v>-1.976598740316381</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.971461175112497</v>
+        <v>1.934996324046258</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.926502267038252</v>
+        <v>-9.987277018815316</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8420857429357844</v>
+        <v>-0.86639564364661</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.966173051993538</v>
+        <v>-2.026947803770603</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.949167756997141</v>
+        <v>1.912702905930902</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.14565123511245</v>
+        <v>-10.20642598688951</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9267035795436951</v>
+        <v>-0.9510134802545207</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.185322020067736</v>
+        <v>-2.2460967718448</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.820720126774391</v>
+        <v>1.784255275708153</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.14196031015604</v>
+        <v>-10.2027350619331</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9252272095611302</v>
+        <v>-0.9495371102719559</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.185322020067736</v>
+        <v>-2.2460967718448</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.820720126774391</v>
+        <v>1.784255275708153</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.3462184854859</v>
+        <v>-10.40699323726297</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.001417282574433</v>
+        <v>-1.025727183285259</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.312960964681725</v>
+        <v>-2.373735716458789</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.74964995712464</v>
+        <v>1.713185106058402</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.56425625711708</v>
+        <v>-10.62503100889414</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.084149836742469</v>
+        <v>-1.108459737453294</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.487731732777624</v>
+        <v>-2.548506484554688</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.649270050751537</v>
+        <v>1.612805199685298</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.49078642544963</v>
+        <v>-10.5515611772267</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.039390202582068</v>
+        <v>-1.063700103292893</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.414261901110175</v>
+        <v>-2.47503665288724</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.708723651245427</v>
+        <v>1.672258800179188</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.66591084283617</v>
+        <v>-10.72668559461324</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.094884748789168</v>
+        <v>-1.119194649499994</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.589386318496719</v>
+        <v>-2.650161070273783</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.618204221561018</v>
+        <v>1.581739370494779</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.90036293685066</v>
+        <v>-10.96113768862773</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.19588475129656</v>
+        <v>-1.220194652007386</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.589386318496719</v>
+        <v>-2.650161070273783</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.610985056659422</v>
+        <v>1.574520205593183</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.1881667813879</v>
+        <v>-11.24894153316497</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.317678479885432</v>
+        <v>-1.341988380596258</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.877190163033957</v>
+        <v>-2.937964914811022</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.431630559163103</v>
+        <v>1.395165708096864</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.41799122855173</v>
+        <v>-11.47876598032879</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.408492468912406</v>
+        <v>-1.432802369623231</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.039837700104118</v>
+        <v>-3.100612451881182</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.335157826759563</v>
+        <v>1.298692975693324</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.65002014828799</v>
+        <v>-11.71079490006505</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.498610308177796</v>
+        <v>-1.522920208888622</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.101850397292541</v>
+        <v>-3.162625149069605</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.300643937075623</v>
+        <v>1.264179086009385</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.59800463431918</v>
+        <v>-11.65877938609624</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.473813766903869</v>
+        <v>-1.498123667614695</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.101850397292541</v>
+        <v>-3.162625149069605</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.304634272762024</v>
+        <v>1.268169421695786</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.7396764760433</v>
+        <v>-11.80045122782036</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.531957730492259</v>
+        <v>-1.556267631203085</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.101850397292541</v>
+        <v>-3.162625149069605</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.303159045863282</v>
+        <v>1.266694194797044</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.69008563161846</v>
+        <v>-11.75086038339553</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.497067982557453</v>
+        <v>-1.521377883268279</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.052259552867707</v>
+        <v>-3.113034304644771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.347966962683055</v>
+        <v>1.311502111616816</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.49093352438136</v>
+        <v>-11.55170827615843</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.430458273309296</v>
+        <v>-1.454768174020122</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.886937026917894</v>
+        <v>-2.947711778694958</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.43410934460626</v>
+        <v>1.397644493540021</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.26508837166195</v>
+        <v>-11.32586312343902</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.330541139185324</v>
+        <v>-1.35485103989615</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.84501035133073</v>
+        <v>-2.905785103107795</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.468844422994767</v>
+        <v>1.432379571928528</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.14050971532436</v>
+        <v>-11.20128446710143</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.279570532094228</v>
+        <v>-1.303880432805054</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.84501035133073</v>
+        <v>-2.905785103107795</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.469983567550826</v>
+        <v>1.433518716484587</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.19340500336865</v>
+        <v>-11.25417975514571</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.298094873149835</v>
+        <v>-1.322404773860661</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.840055005242284</v>
+        <v>-2.900829757019348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.475590549366001</v>
+        <v>1.439125698299762</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.9094962724399</v>
+        <v>-10.97027102421696</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.178797676539699</v>
+        <v>-1.203107577250525</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.840055005242284</v>
+        <v>-2.900829757019348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.481324253604638</v>
+        <v>1.444859402538399</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.83812987983025</v>
+        <v>-10.89890463160732</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.159988381889706</v>
+        <v>-1.184298282600531</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.768688612632636</v>
+        <v>-2.829463364409701</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.514406826776561</v>
+        <v>1.477941975710322</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.57429301262618</v>
+        <v>-10.63506776440325</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.064337116320985</v>
+        <v>-1.088647017031811</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.768688612632636</v>
+        <v>-2.829463364409701</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.504523345463654</v>
+        <v>1.468058494397415</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.30705121175778</v>
+        <v>-10.36782596353485</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9592749564729997</v>
+        <v>-0.9835848571838253</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.768688612632636</v>
+        <v>-2.829463364409701</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.50268878496428</v>
+        <v>1.466223933898041</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.20914417308129</v>
+        <v>-10.26991892485836</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9204124559758644</v>
+        <v>-0.94472235668669</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.700702862772079</v>
+        <v>-2.761477614549144</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.543179919907153</v>
+        <v>1.506715068840914</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.18519063210534</v>
+        <v>-10.2459653838824</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9101625334399874</v>
+        <v>-0.934472434150813</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.676749321796122</v>
+        <v>-2.737524073573187</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.558220550638221</v>
+        <v>1.521755699571982</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.921130693782539</v>
+        <v>-9.981905445559603</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8177988742726212</v>
+        <v>-0.8421087749834468</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.412689383473326</v>
+        <v>-2.473464135250391</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.703396197470147</v>
+        <v>1.666931346403908</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.214051070277701</v>
+        <v>-9.274825822054765</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5377540585309868</v>
+        <v>-0.5620639592418124</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.412689383473326</v>
+        <v>-2.473464135250391</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.700609163809846</v>
+        <v>1.664144312743607</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.173866771911511</v>
+        <v>-9.234641523688575</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5213367152966693</v>
+        <v>-0.5456466160074949</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.372505085107135</v>
+        <v>-2.4332798368842</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.725063366717402</v>
+        <v>1.688598515651163</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.093796976373707</v>
+        <v>-9.154571728150771</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4899419758607908</v>
+        <v>-0.5142518765716164</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.292435289569331</v>
+        <v>-2.353210041346396</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.772472065260841</v>
+        <v>1.736007214194602</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.860315754144107</v>
+        <v>-8.921090505921171</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3886250581310984</v>
+        <v>-0.412934958841924</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.058954067339732</v>
+        <v>-2.119728819116797</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.920485227436453</v>
+        <v>1.884020376370213</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.710649363136593</v>
+        <v>-8.771424114913657</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3316507120410521</v>
+        <v>-0.3559606127518777</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.966050576097196</v>
+        <v>-2.026825327874261</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.973335111869015</v>
+        <v>1.936870260802776</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.578373889505706</v>
+        <v>-8.63914864128277</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2833730358416702</v>
+        <v>-0.3076829365524958</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.83377510246631</v>
+        <v>-1.894549854243375</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.048067882794574</v>
+        <v>2.011603031728335</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.387774214832552</v>
+        <v>-8.448548966609616</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2043181052847718</v>
+        <v>-0.2286280059955974</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.643175427793157</v>
+        <v>-1.703950179570222</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.165242748286103</v>
+        <v>2.128777897219863</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.138774416148971</v>
+        <v>-8.199549167926035</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.09181184458768099</v>
+        <v>-0.1161217452985066</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.643175427793157</v>
+        <v>-1.703950179570222</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.178149089509761</v>
+        <v>2.141684238443522</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.244364405922076</v>
+        <v>-8.30513915769914</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2620237700961412</v>
+        <v>-0.2863336708069668</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.748765417566261</v>
+        <v>-1.809540169343326</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.98681916604668</v>
+        <v>1.950354314980441</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.263099308040672</v>
+        <v>-8.323874059817737</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2209733890664936</v>
+        <v>-0.2452832897773192</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.748765417566261</v>
+        <v>-1.809540169343326</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.035363507923766</v>
+        <v>1.998898656857527</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.115159266633073</v>
+        <v>-8.175934018410137</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2816762951916214</v>
+        <v>-0.305986195902447</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.728444501657704</v>
+        <v>-1.789219253434768</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.927677134780733</v>
+        <v>1.891212283714494</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.090930630244101</v>
+        <v>-8.151705382021165</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2806988268895108</v>
+        <v>-0.3050087276003364</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.704215865268731</v>
+        <v>-1.764990617045796</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.933500330360638</v>
+        <v>1.897035479294399</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.047382223473409</v>
+        <v>-8.108156975250473</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2702400762763273</v>
+        <v>-0.2945499769871529</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.704215865268731</v>
+        <v>-1.764990617045796</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.926539718265545</v>
+        <v>1.890074867199306</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.805233830019551</v>
+        <v>-7.866008581796615</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1589183645136409</v>
+        <v>-0.1832282652244666</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.704215865268731</v>
+        <v>-1.764990617045796</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.941002072646688</v>
+        <v>1.904537221580449</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.742004458251203</v>
+        <v>-7.802779210028267</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1390944953471065</v>
+        <v>-0.1634043960579321</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.704215865268731</v>
+        <v>-1.764990617045796</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.935534193105883</v>
+        <v>1.899069342039644</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.618713323434072</v>
+        <v>-7.679488075211136</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.09227994740967738</v>
+        <v>-0.116589848120503</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.580924730451601</v>
+        <v>-1.641699482228666</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.007006968006738</v>
+        <v>1.9705421169405</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.597564124530629</v>
+        <v>-7.658338876307693</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.07611928961097503</v>
+        <v>-0.1004291903218006</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.559775531548158</v>
+        <v>-1.620550283325223</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.02739746558613</v>
+        <v>1.990932614519891</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.353798682547184</v>
+        <v>-7.414573434324248</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.01716759552945346</v>
+        <v>-0.007142305181372155</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.559775531548158</v>
+        <v>-1.620550283325223</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.02317817393318</v>
+        <v>1.986713322866941</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.089770615353924</v>
+        <v>-7.150545367130988</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1249031363267736</v>
+        <v>0.100593235615948</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.357910132732204</v>
+        <v>-1.418684884509269</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.146421727142768</v>
+        <v>2.109956876076529</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.839920221404849</v>
+        <v>-6.900694973181913</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2175853688901057</v>
+        <v>0.1932754681792801</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.357910132732204</v>
+        <v>-1.418684884509269</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.139163802126471</v>
+        <v>2.102698951060232</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.664028128937417</v>
+        <v>-6.724802880714481</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2915413293977274</v>
+        <v>0.2672314286869018</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.357910132732204</v>
+        <v>-1.418684884509269</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.142762925647119</v>
+        <v>2.10629807458088</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.492581665914954</v>
+        <v>-6.553356417692018</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3734474206612663</v>
+        <v>0.3491375199504407</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.186463669709741</v>
+        <v>-1.247238421486806</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.258958309515151</v>
+        <v>2.222493458448912</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.267548666246131</v>
+        <v>-6.328323418023195</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4624810981450924</v>
+        <v>0.4381711974342668</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.961430670040918</v>
+        <v>-1.022205421817983</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.392998586932741</v>
+        <v>2.356533735866503</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.052914288609724</v>
+        <v>-6.113689040386788</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5530296502539724</v>
+        <v>0.5287197495431468</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7467962924045112</v>
+        <v>-0.807571044181576</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.526474014568903</v>
+        <v>2.490009163502664</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.959914247403826</v>
+        <v>-6.02068899918089</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5714239255201274</v>
+        <v>0.5471140248093018</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7467962924045112</v>
+        <v>-0.807571044181576</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.507668273352698</v>
+        <v>2.47120342228646</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.719483750598966</v>
+        <v>-5.78025850237603</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6693392008669488</v>
+        <v>0.6450293001561231</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5063657955996509</v>
+        <v>-0.5671405473767157</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.653669648060492</v>
+        <v>2.617204796994253</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.647241182427771</v>
+        <v>-5.708015934204835</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7021655419702468</v>
+        <v>0.6778556412594212</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5063657955996509</v>
+        <v>-0.5671405473767157</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.657598961895312</v>
+        <v>2.621134110829074</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.531301332802586</v>
+        <v>-5.59207608457965</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7492200657376613</v>
+        <v>0.7249101650268357</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.429544064583527</v>
+        <v>-0.4903188163605918</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.704370584422326</v>
+        <v>2.667905733356088</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288645744379423</v>
+        <v>-5.349420496156487</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8432803723269195</v>
+        <v>0.8189704716160939</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.429544064583527</v>
+        <v>-0.4903188163605918</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.70136865564232</v>
+        <v>2.664903804576081</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068624946342412</v>
+        <v>-5.129399698119476</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9328677285523379</v>
+        <v>0.9085578278415123</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2883242195155468</v>
+        <v>-0.3490989712926116</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.787679599693722</v>
+        <v>2.751214748627484</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935757257279135</v>
+        <v>-4.996532009056199</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001908986979472</v>
+        <v>0.9775990862686468</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2883242195155468</v>
+        <v>-0.3490989712926116</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.803573782495546</v>
+        <v>2.767108931429307</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.776242153759765</v>
+        <v>-4.837016905536829</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.066860872827522</v>
+        <v>1.042550972116697</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1288091159961768</v>
+        <v>-0.1895838677732417</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.90042868904747</v>
+        <v>2.863963837981231</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.631570008660027</v>
+        <v>-4.692344760437091</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.134817833428857</v>
+        <v>1.110507932718031</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.01586302910356058</v>
+        <v>-0.04491172267350424</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.997320078668752</v>
+        <v>2.960855227602513</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.69144483601772</v>
+        <v>-4.752219587794784</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.096905393887206</v>
+        <v>1.07259549317638</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.04401179825413154</v>
+        <v>-0.1047865500311964</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.947432673655562</v>
+        <v>2.910967822589324</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.604645338238711</v>
+        <v>-4.665420090015775</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.154025686321375</v>
+        <v>1.12971578561055</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.04401179825413154</v>
+        <v>-0.1047865500311964</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.969833166978129</v>
+        <v>2.93336831591189</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.607115044700517</v>
+        <v>-4.667889796477581</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.153110205110065</v>
+        <v>1.12880030439924</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.0464815047159377</v>
+        <v>-0.1072562564930025</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.968423744474457</v>
+        <v>2.931958893408218</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.675485231024528</v>
+        <v>-4.736259982801592</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.136769053055163</v>
+        <v>1.112459152344337</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.03720580567972276</v>
+        <v>-0.09798055745678758</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.984996086370888</v>
+        <v>2.948531235304649</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.554068801398051</v>
+        <v>-4.614843553175115</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.175772333537645</v>
+        <v>1.151462432826819</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.03720580567972276</v>
+        <v>-0.09798055745678758</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.975432795002779</v>
+        <v>2.93896794393654</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.585061960726756</v>
+        <v>-4.64583671250382</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9880846348465497</v>
+        <v>0.9637747341357241</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.03720580567972276</v>
+        <v>-0.09798055745678758</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.800142360043166</v>
+        <v>2.763677508976927</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.409587700934287</v>
+        <v>-4.470362452711351</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.062841570755325</v>
+        <v>1.0385316700445</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.03720580567972276</v>
+        <v>-0.09798055745678758</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.804709592034954</v>
+        <v>2.768244740968715</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.520523953575536</v>
+        <v>-4.5812987053526</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9942090984600327</v>
+        <v>0.9698991977492071</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.03720580567972276</v>
+        <v>-0.09798055745678758</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.780451620796161</v>
+        <v>2.743986769729922</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.723550531118769</v>
+        <v>-4.784325282895833</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9161298526626451</v>
+        <v>0.8918199519518195</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2402323832229561</v>
+        <v>-0.301007135000021</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.661767059490126</v>
+        <v>2.625302208423888</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.565624932183476</v>
+        <v>-4.62639968396054</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9894724786688947</v>
+        <v>0.965162577958069</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2402323832229561</v>
+        <v>-0.301007135000021</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.671939445922259</v>
+        <v>2.63547459485602</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.479381469157098</v>
+        <v>-4.540156220934162</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.018916134453306</v>
+        <v>0.9946062337424804</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2402323832229561</v>
+        <v>-0.301007135000021</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.666885716496119</v>
+        <v>2.63042086542988</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.48056455380816</v>
+        <v>-4.541339305585224</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.010218676037407</v>
+        <v>0.9859087753265814</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2458754316894677</v>
+        <v>-0.3066501834665325</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.655275662860738</v>
+        <v>2.618810811794499</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.357436846814077</v>
+        <v>-4.418211598591141</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.060021631868142</v>
+        <v>1.035711731157316</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2458754316894677</v>
+        <v>-0.3066501834665325</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.655827535893839</v>
+        <v>2.619362684827601</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.304257644743862</v>
+        <v>-4.325401117140281</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.010566004587593</v>
+        <v>1.002108615629026</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1926962296192527</v>
+        <v>-0.2138397020156731</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.617007749027334</v>
+        <v>2.604321665589482</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.255694592522832</v>
+        <v>-4.276838064919251</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.031864701400606</v>
+        <v>1.023407312442038</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1441331773982225</v>
+        <v>-0.165276649794643</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.648019056284553</v>
+        <v>2.635332972846701</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.143023374286582</v>
+        <v>-4.164166846683001</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.072008897206829</v>
+        <v>1.063551508248262</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03146195916197231</v>
+        <v>-0.05260543155839276</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.710697495738026</v>
+        <v>2.698011412300174</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.030646373103909</v>
+        <v>-4.051789845500328</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.122450993510566</v>
+        <v>1.113993604551998</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03146195916197231</v>
+        <v>-0.05260543155839276</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.716188791568693</v>
+        <v>2.703502708130841</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.228880941990639</v>
+        <v>-4.250024414387059</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.054654367724412</v>
+        <v>1.046196978765845</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2296965280487029</v>
+        <v>-0.2508400004451233</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608745252005194</v>
+        <v>2.596059168567342</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.311882223015918</v>
+        <v>-4.333025695412338</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8598095753149542</v>
+        <v>0.8513521863563864</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2482674125758766</v>
+        <v>-0.2694108849722971</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.435958441289543</v>
+        <v>2.423272357851691</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.152687950959342</v>
+        <v>-4.173831423355761</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.04363694485679</v>
+        <v>1.035179555898223</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2482674125758766</v>
+        <v>-0.2694108849722971</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556108102008749</v>
+        <v>2.543422018570896</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.239286533940445</v>
+        <v>-4.260430006336864</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.023510537766672</v>
+        <v>1.015053148808104</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2482674125758766</v>
+        <v>-0.2694108849722971</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570621128111072</v>
+        <v>2.557935044673219</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.200902871382294</v>
+        <v>-4.222046343778713</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.036283444132301</v>
+        <v>1.027826055173734</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2098837500177255</v>
+        <v>-0.2310272224141459</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.591070766988331</v>
+        <v>2.578384683550479</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.023786541347127</v>
+        <v>-4.044930013743547</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.10385900499167</v>
+        <v>1.095401616033102</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2098837500177255</v>
+        <v>-0.2310272224141459</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587799795833633</v>
+        <v>2.575113712395781</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.994084417370834</v>
+        <v>-4.015227889767253</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.1164232463441</v>
+        <v>1.107965857385532</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2143538752330388</v>
+        <v>-0.2354973476294593</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.585801112466358</v>
+        <v>2.573115029028506</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.814708996132066</v>
+        <v>-3.835852468528485</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.181960390146022</v>
+        <v>1.173503001187454</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05757711706232016</v>
+        <v>-0.07872058945874061</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.673654142675204</v>
+        <v>2.660968059237351</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.859723209652672</v>
+        <v>-3.880866682049092</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.144762160069369</v>
+        <v>1.136304771110801</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08792601237692477</v>
+        <v>-0.1090694847733452</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.636252260818031</v>
+        <v>2.623566177380178</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.126727719925108</v>
+        <v>-4.147871192321527</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.04365191829934</v>
+        <v>1.035194529340773</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2822890504198733</v>
+        <v>-0.3034325228162938</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.525326000331207</v>
+        <v>2.512639916893355</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.415514940384023</v>
+        <v>-4.436658412780442</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9273409520122757</v>
+        <v>0.9188835630537082</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3833751705188737</v>
+        <v>-0.4045186429152942</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.463878250168309</v>
+        <v>2.451192166730456</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.383039354213251</v>
+        <v>-4.40418282660967</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9379311480349015</v>
+        <v>0.9294737590763338</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3833751705188737</v>
+        <v>-0.4045186429152942</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.461478211722625</v>
+        <v>2.448792128284773</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.364001226505954</v>
+        <v>-4.385144698902373</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9420711183260653</v>
+        <v>0.9336137293674975</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4415587818500682</v>
+        <v>-0.4627022542464887</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.423092764132153</v>
+        <v>2.410406680694301</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.477056974109338</v>
+        <v>3.557134463074516</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.583475150789387</v>
+        <v>2.663090847585436</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.364001226505954</v>
+        <v>-4.385144698902373</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9420711183260653</v>
+        <v>0.9336137293674975</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4415587818500682</v>
+        <v>-0.4627022542464887</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.576538947775755</v>
+        <v>2.656154644571804</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-49.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.6%</t>
+          <t>132.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-704.4%</t>
+          <t>-680.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.6%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.9%</t>
+          <t>425.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-600.1%</t>
+          <t>-569.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-282.2%</t>
+          <t>-272.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.8%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.9%</t>
+          <t>-270.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-318.7%</t>
+          <t>-312.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.2%</t>
+          <t>-105.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270.3%</t>
+          <t>-268.4%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-191.6%</t>
+          <t>-188.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.4%</t>
+          <t>-184.1%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1087228009644963</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.165702868184994</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.596388246213587</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.080403119841095</v>
+        <v>4.116867970907334</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1284086908852988</v>
+        <v>0.1133650073075221</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.105791355942618</v>
+        <v>3.202500835219746</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.596388246213587</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.115344204338637</v>
+        <v>4.151809055404875</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1233711001577123</v>
+        <v>0.1184025980351086</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.10638383241899</v>
+        <v>3.203093311696119</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.652032702479904</v>
+        <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.147308318283764</v>
+        <v>4.183773169350004</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2859971801223509</v>
+        <v>-0.04422348192952996</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.020079782056872</v>
+        <v>3.116789261334</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.489406622515265</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.028479051928719</v>
+        <v>4.064943902994957</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3517645701717629</v>
+        <v>-0.109990871978942</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.994790435167577</v>
+        <v>3.091499914444706</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.489406622515265</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.029496661059189</v>
+        <v>4.065961512125428</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5687733928395171</v>
+        <v>-0.3269996946466961</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.898614938088231</v>
+        <v>2.99532441736536</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.489406622515265</v>
+        <v>1.55018137429233</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.020124693046944</v>
+        <v>4.056589544113184</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6505452932672688</v>
+        <v>-0.4087715950744478</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.855988903872369</v>
+        <v>2.952698383149497</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.516442195921402</v>
+        <v>1.577216947698467</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.026428763045865</v>
+        <v>4.062893614112104</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7177544011391466</v>
+        <v>-0.4759807029463255</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.83387057755732</v>
+        <v>2.930580056834448</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.516442195921402</v>
+        <v>1.577216947698467</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.031194079879567</v>
+        <v>4.067658930945806</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9253201855307585</v>
+        <v>-0.6835464873379373</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.748669059919916</v>
+        <v>2.845378539197044</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.30887641152979</v>
+        <v>1.369651163306855</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.904479405363841</v>
+        <v>3.940944256430079</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.343074209077596</v>
+        <v>-1.101300510884774</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.579494342006244</v>
+        <v>2.676203821283372</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.891122387982953</v>
+        <v>0.9518971397600179</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.651753882740802</v>
+        <v>3.68821873380704</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.564696142635713</v>
+        <v>-1.322922444442892</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.490711785181919</v>
+        <v>2.587421264459047</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8535962542955839</v>
+        <v>0.9143710060726489</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.629104419127302</v>
+        <v>3.665569270193541</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.77270020098879</v>
+        <v>-1.530926502795969</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.412402306394613</v>
+        <v>2.509111785671741</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8535962542955839</v>
+        <v>0.9143710060726489</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.633996563681227</v>
+        <v>3.670461414747466</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.984112621876765</v>
+        <v>-1.742338923683944</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.322918794377411</v>
+        <v>2.419628273654539</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6421838334076089</v>
+        <v>0.7029585851846738</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.50223056748643</v>
+        <v>3.538695418552669</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.323270999465287</v>
+        <v>-2.081497301272466</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.180339742648451</v>
+        <v>2.27704922192558</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3030254558190868</v>
+        <v>0.3638002075961517</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.291819840239766</v>
+        <v>3.328284691306005</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.531761780916972</v>
+        <v>-2.289988082724151</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.117281719806546</v>
+        <v>2.213991199083674</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.09453467436740237</v>
+        <v>0.1553094261444673</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.187063661107524</v>
+        <v>3.223528512173762</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.02508665245215</v>
+        <v>-2.783312954259329</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.928050521601043</v>
+        <v>2.024760000878172</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.01045143987221636</v>
+        <v>0.05032331190484857</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.132170742972321</v>
+        <v>3.16863559403856</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.517471680476247</v>
+        <v>-3.275697982283426</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.732202902435137</v>
+        <v>1.828912381712265</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.5028364678963131</v>
+        <v>-0.4420617161192482</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.837846118201595</v>
+        <v>2.874310969267834</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.902652071406319</v>
+        <v>-3.660878373213498</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.576673284875971</v>
+        <v>1.673382764153099</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.5028364678963131</v>
+        <v>-0.4420617161192482</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.836388657014458</v>
+        <v>2.872853508080697</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.246334844632982</v>
+        <v>-4.004561146440161</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.440969299039922</v>
+        <v>1.53767877831705</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.6107425199235312</v>
+        <v>-0.5499677681464663</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.773414149252744</v>
+        <v>2.809879000318983</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.452846621520004</v>
+        <v>-4.211072923327182</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.354470646941371</v>
+        <v>1.4511801262185</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8172542968105527</v>
+        <v>-0.7564795450334878</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.645613141776789</v>
+        <v>2.682077992843027</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.762080724516054</v>
+        <v>-4.520307026323233</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.23254993244321</v>
+        <v>1.329259411720339</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8172542968105527</v>
+        <v>-0.7564795450334878</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.647386068477048</v>
+        <v>2.683850919543287</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.193886517665842</v>
+        <v>-4.952112819473021</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.0461605026507</v>
+        <v>1.142869981927828</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9536717932518197</v>
+        <v>-0.8928970414747548</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.551868458079692</v>
+        <v>2.588333309145932</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.428580511798394</v>
+        <v>-5.186806813605573</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9405676799997695</v>
+        <v>1.037277159276898</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9473355260225645</v>
+        <v>-0.8865607742454996</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.543954993419336</v>
+        <v>2.580419844485575</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.764243159028847</v>
+        <v>-5.522469460836025</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8048832127635537</v>
+        <v>0.901592692040682</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9473355260225645</v>
+        <v>-0.8865607742454996</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.542535585075301</v>
+        <v>2.57900043614154</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.12786940392916</v>
+        <v>-5.886095705736339</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6659202750376698</v>
+        <v>0.7626297543147986</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.04555716288969</v>
+        <v>-0.9847824111126254</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.490090163189267</v>
+        <v>2.526555014255506</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.492996786567907</v>
+        <v>-6.251223088375085</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5191238369880025</v>
+        <v>0.6158333162651313</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.341867947188703</v>
+        <v>-1.281093195411638</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.311558207615692</v>
+        <v>2.34802305868193</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.901585563748585</v>
+        <v>-6.659811865555763</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3544498701304906</v>
+        <v>0.4511593494076189</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.750456724369381</v>
+        <v>-1.689681972592316</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.065166485322043</v>
+        <v>2.101631336388282</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.314568047889678</v>
+        <v>-7.072794349696857</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1844423089455134</v>
+        <v>0.2811517882226422</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.750456724369381</v>
+        <v>-1.689681972592316</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.060351917793504</v>
+        <v>2.096816768859743</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.730959922176676</v>
+        <v>-7.489186223983855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.01587960983959213</v>
+        <v>0.1125890891167205</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.750456724369381</v>
+        <v>-1.689681972592316</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.058345968402381</v>
+        <v>2.09481081946862</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.107636932706519</v>
+        <v>-7.865863234513699</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1245325037036666</v>
+        <v>-0.02782302442653828</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.750456724369381</v>
+        <v>-1.689681972592316</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.068604659071061</v>
+        <v>2.105069510137299</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.453511754691329</v>
+        <v>-8.211738056498508</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2667828673518948</v>
+        <v>-0.1700733880747665</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.750456724369381</v>
+        <v>-1.689681972592316</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.064704224216755</v>
+        <v>2.101169075282995</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.617091632875713</v>
+        <v>-8.375317934682892</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3338098985706477</v>
+        <v>-0.2371004192935193</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.750456724369381</v>
+        <v>-1.689681972592316</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.063109144271756</v>
+        <v>2.099573995337995</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.913752974685911</v>
+        <v>-8.67197927649309</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4486954593655188</v>
+        <v>-0.3519859800883904</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.81919986010326</v>
+        <v>-1.758425108326195</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.025642238760637</v>
+        <v>2.062107089826876</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.036997363901341</v>
+        <v>-8.795223665708519</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5020195195860939</v>
+        <v>-0.4053100403089651</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.81919986010326</v>
+        <v>-1.758425108326195</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.021615934226234</v>
+        <v>2.058080785292473</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.419998752643972</v>
+        <v>-9.178225054451151</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6553221764047303</v>
+        <v>-0.558612697127602</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.81919986010326</v>
+        <v>-1.758425108326195</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.02151383290465</v>
+        <v>2.057978683970889</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.577397632857092</v>
+        <v>-9.335623934664271</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7157102125185486</v>
+        <v>-0.6190007332414198</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.976598740316381</v>
+        <v>-1.915823988539316</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.929646020748208</v>
+        <v>1.966110871814446</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.936927955361094</v>
+        <v>-9.695154257168273</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.854172038222099</v>
+        <v>-0.7574625589449706</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.976598740316381</v>
+        <v>-1.915823988539316</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.934996324046258</v>
+        <v>1.971461175112497</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.987277018815316</v>
+        <v>-9.745503320622495</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.86639564364661</v>
+        <v>-0.7696861643694817</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.026947803770603</v>
+        <v>-1.966173051993538</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.912702905930902</v>
+        <v>1.949167756997141</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.20642598688951</v>
+        <v>-9.964652288696692</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9510134802545207</v>
+        <v>-0.8543040009773919</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.2460967718448</v>
+        <v>-2.185322020067736</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.784255275708153</v>
+        <v>1.820720126774391</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.2027350619331</v>
+        <v>-9.960961363740282</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9495371102719559</v>
+        <v>-0.8528276309948275</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.2460967718448</v>
+        <v>-2.185322020067736</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.784255275708153</v>
+        <v>1.820720126774391</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.40699323726297</v>
+        <v>-10.16521953907015</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.025727183285259</v>
+        <v>-0.9290177040081309</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.373735716458789</v>
+        <v>-2.312960964681725</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.713185106058402</v>
+        <v>1.74964995712464</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.62503100889414</v>
+        <v>-10.38325731070132</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.108459737453294</v>
+        <v>-1.011750258176165</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.548506484554688</v>
+        <v>-2.487731732777624</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.612805199685298</v>
+        <v>1.649270050751537</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.5515611772267</v>
+        <v>-10.30978747903387</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.063700103292893</v>
+        <v>-0.9669906240157653</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.47503665288724</v>
+        <v>-2.414261901110175</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.672258800179188</v>
+        <v>1.708723651245427</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.72668559461324</v>
+        <v>-10.48491189642042</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.119194649499994</v>
+        <v>-1.022485170222866</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.650161070273783</v>
+        <v>-2.589386318496719</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.581739370494779</v>
+        <v>1.618204221561018</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.96113768862773</v>
+        <v>-10.71936399043491</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.220194652007386</v>
+        <v>-1.123485172730258</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.650161070273783</v>
+        <v>-2.589386318496719</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.574520205593183</v>
+        <v>1.610985056659422</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.24894153316497</v>
+        <v>-11.00716783497215</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.341988380596258</v>
+        <v>-1.245278901319129</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.937964914811022</v>
+        <v>-2.877190163033957</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.395165708096864</v>
+        <v>1.431630559163103</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.47876598032879</v>
+        <v>-11.23699228213597</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.432802369623231</v>
+        <v>-1.336092890346102</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.100612451881182</v>
+        <v>-3.039837700104118</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.298692975693324</v>
+        <v>1.335157826759563</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.71079490006505</v>
+        <v>-11.46902120187223</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.522920208888622</v>
+        <v>-1.426210729611493</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.162625149069605</v>
+        <v>-3.101850397292541</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.264179086009385</v>
+        <v>1.300643937075623</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.65877938609624</v>
+        <v>-11.41700568790342</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.498123667614695</v>
+        <v>-1.401414188337567</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.162625149069605</v>
+        <v>-3.101850397292541</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.268169421695786</v>
+        <v>1.304634272762024</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.80045122782036</v>
+        <v>-11.55867752962754</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.556267631203085</v>
+        <v>-1.459558151925957</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.162625149069605</v>
+        <v>-3.101850397292541</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.266694194797044</v>
+        <v>1.303159045863282</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.75086038339553</v>
+        <v>-11.50908668520271</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.521377883268279</v>
+        <v>-1.424668403991151</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.113034304644771</v>
+        <v>-3.052259552867707</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.311502111616816</v>
+        <v>1.347966962683055</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.55170827615843</v>
+        <v>-11.30993457796561</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.454768174020122</v>
+        <v>-1.358058694742994</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.947711778694958</v>
+        <v>-2.886937026917894</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.397644493540021</v>
+        <v>1.43410934460626</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.32586312343902</v>
+        <v>-11.08408942524619</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.35485103989615</v>
+        <v>-1.25814156061902</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.905785103107795</v>
+        <v>-2.84501035133073</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.432379571928528</v>
+        <v>1.468844422994767</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.20128446710143</v>
+        <v>-10.9595107689086</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.303880432805054</v>
+        <v>-1.207170953527925</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.905785103107795</v>
+        <v>-2.84501035133073</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.433518716484587</v>
+        <v>1.469983567550826</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.25417975514571</v>
+        <v>-11.01240605695289</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.322404773860661</v>
+        <v>-1.225695294583532</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.900829757019348</v>
+        <v>-2.840055005242284</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.439125698299762</v>
+        <v>1.475590549366001</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.97027102421696</v>
+        <v>-10.72849732602414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.203107577250525</v>
+        <v>-1.106398097973396</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.900829757019348</v>
+        <v>-2.840055005242284</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.444859402538399</v>
+        <v>1.481324253604638</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.89890463160732</v>
+        <v>-10.65713093341449</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.184298282600531</v>
+        <v>-1.087588803323402</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.829463364409701</v>
+        <v>-2.768688612632636</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.477941975710322</v>
+        <v>1.514406826776561</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.63506776440325</v>
+        <v>-10.39329406621042</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.088647017031811</v>
+        <v>-0.9919375377546813</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.829463364409701</v>
+        <v>-2.768688612632636</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.468058494397415</v>
+        <v>1.504523345463654</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.36782596353485</v>
+        <v>-10.12605226534203</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9835848571838253</v>
+        <v>-0.8868753779066965</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.829463364409701</v>
+        <v>-2.768688612632636</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.466223933898041</v>
+        <v>1.50268878496428</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.26991892485836</v>
+        <v>-10.02814522666553</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.94472235668669</v>
+        <v>-0.8480128774095612</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.761477614549144</v>
+        <v>-2.700702862772079</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.506715068840914</v>
+        <v>1.543179919907153</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.2459653838824</v>
+        <v>-10.00419168568958</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.934472434150813</v>
+        <v>-0.8377629548736842</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.737524073573187</v>
+        <v>-2.676749321796122</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.521755699571982</v>
+        <v>1.558220550638221</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.981905445559603</v>
+        <v>-9.74013174736678</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8421087749834468</v>
+        <v>-0.7453992957063176</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.473464135250391</v>
+        <v>-2.412689383473326</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.666931346403908</v>
+        <v>1.703396197470147</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.274825822054765</v>
+        <v>-9.033052123861943</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5620639592418124</v>
+        <v>-0.4653544799646836</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.473464135250391</v>
+        <v>-2.412689383473326</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.664144312743607</v>
+        <v>1.700609163809846</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.234641523688575</v>
+        <v>-8.992867825495752</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5456466160074949</v>
+        <v>-0.4489371367303661</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.4332798368842</v>
+        <v>-2.372505085107135</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.688598515651163</v>
+        <v>1.725063366717402</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.154571728150771</v>
+        <v>-8.912798029957948</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5142518765716164</v>
+        <v>-0.4175423972944872</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.353210041346396</v>
+        <v>-2.292435289569331</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.736007214194602</v>
+        <v>1.772472065260841</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.921090505921171</v>
+        <v>-8.679316807728348</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.412934958841924</v>
+        <v>-0.3162254795647952</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.119728819116797</v>
+        <v>-2.058954067339732</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.884020376370213</v>
+        <v>1.920485227436453</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.771424114913657</v>
+        <v>-8.529650416720834</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3559606127518777</v>
+        <v>-0.2592511334747485</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.026825327874261</v>
+        <v>-1.966050576097196</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.936870260802776</v>
+        <v>1.973335111869015</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.63914864128277</v>
+        <v>-8.397374943089947</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3076829365524958</v>
+        <v>-0.2109734572753665</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.894549854243375</v>
+        <v>-1.83377510246631</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.011603031728335</v>
+        <v>2.048067882794574</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.448548966609616</v>
+        <v>-8.249372988213615</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2286280059955974</v>
+        <v>-0.1489576146371974</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.703950179570222</v>
+        <v>-1.685773147589978</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.128777897219863</v>
+        <v>2.13968411640801</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.199549167926035</v>
+        <v>-8.000373189530034</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1161217452985066</v>
+        <v>-0.03645135394010612</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.703950179570222</v>
+        <v>-1.685773147589978</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.141684238443522</v>
+        <v>2.152590457631669</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.30513915769914</v>
+        <v>-8.105963179303139</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2863336708069668</v>
+        <v>-0.2066632794485663</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.809540169343326</v>
+        <v>-1.791363137363082</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.950354314980441</v>
+        <v>1.961260534168587</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.323874059817737</v>
+        <v>-8.124698081421736</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2452832897773192</v>
+        <v>-0.1656128984189191</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.809540169343326</v>
+        <v>-1.791363137363082</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.998898656857527</v>
+        <v>2.009804876045674</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.175934018410137</v>
+        <v>-7.976758040014136</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.305986195902447</v>
+        <v>-0.226315804544047</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.789219253434768</v>
+        <v>-1.771042221454525</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.891212283714494</v>
+        <v>1.902118502902641</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.151705382021165</v>
+        <v>-7.952529403625164</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3050087276003364</v>
+        <v>-0.2253383362419359</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.764990617045796</v>
+        <v>-1.746813585065552</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.897035479294399</v>
+        <v>1.907941698482546</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.108156975250473</v>
+        <v>-7.908980996854473</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2945499769871529</v>
+        <v>-0.2148795856287529</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.764990617045796</v>
+        <v>-1.746813585065552</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.890074867199306</v>
+        <v>1.900981086387453</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.866008581796615</v>
+        <v>-7.666832603400615</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1832282652244666</v>
+        <v>-0.1035578738660665</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.764990617045796</v>
+        <v>-1.746813585065552</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.904537221580449</v>
+        <v>1.915443440768596</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.802779210028267</v>
+        <v>-7.495628485653234</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1634043960579321</v>
+        <v>-0.04054410630791905</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.764990617045796</v>
+        <v>-1.746813585065552</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.899069342039644</v>
+        <v>1.909975561227791</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.679488075211136</v>
+        <v>-7.372337350836103</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.116589848120503</v>
+        <v>0.006270441629510071</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.641699482228666</v>
+        <v>-1.623522450248422</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.9705421169405</v>
+        <v>1.981448336128646</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.658338876307693</v>
+        <v>-7.35118815193266</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1004291903218006</v>
+        <v>0.02243109942821242</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.620550283325223</v>
+        <v>-1.602373251344979</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.990932614519891</v>
+        <v>2.001838833708037</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.414573434324248</v>
+        <v>-7.107422709949216</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.007142305181372155</v>
+        <v>0.1157179845686409</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.620550283325223</v>
+        <v>-1.602373251344979</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.986713322866941</v>
+        <v>1.997619542055088</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.150545367130988</v>
+        <v>-6.843394642755955</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.100593235615948</v>
+        <v>0.2234535253659611</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.418684884509269</v>
+        <v>-1.400507852529025</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.109956876076529</v>
+        <v>2.120863095264676</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.900694973181913</v>
+        <v>-6.593544248806881</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1932754681792801</v>
+        <v>0.3161357579292932</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.418684884509269</v>
+        <v>-1.400507852529025</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.102698951060232</v>
+        <v>2.113605170248378</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.724802880714481</v>
+        <v>-6.417652156339448</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2672314286869018</v>
+        <v>0.3900917184369148</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.418684884509269</v>
+        <v>-1.400507852529025</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.10629807458088</v>
+        <v>2.117204293769027</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.553356417692018</v>
+        <v>-6.246205693316985</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3491375199504407</v>
+        <v>0.4719978097004538</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.247238421486806</v>
+        <v>-1.229061389506562</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.222493458448912</v>
+        <v>2.233399677637058</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.328323418023195</v>
+        <v>-6.021172693648162</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4381711974342668</v>
+        <v>0.5610314871842799</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.022205421817983</v>
+        <v>-1.004028389837739</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.356533735866503</v>
+        <v>2.367439955054649</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.113689040386788</v>
+        <v>-5.806538316011755</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5287197495431468</v>
+        <v>0.6515800392931599</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.807571044181576</v>
+        <v>-0.7893940122013321</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.490009163502664</v>
+        <v>2.500915382690811</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.02068899918089</v>
+        <v>-5.713538274805857</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5471140248093018</v>
+        <v>0.6699743145593149</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.807571044181576</v>
+        <v>-0.7893940122013321</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.47120342228646</v>
+        <v>2.482109641474606</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.78025850237603</v>
+        <v>-5.473107778000997</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6450293001561231</v>
+        <v>0.7678895899061366</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5671405473767157</v>
+        <v>-0.5489635153964718</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.617204796994253</v>
+        <v>2.6281110161824</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.708015934204835</v>
+        <v>-5.400865209829802</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6778556412594212</v>
+        <v>0.8007159310094347</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5671405473767157</v>
+        <v>-0.5489635153964718</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.621134110829074</v>
+        <v>2.63204033001722</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.59207608457965</v>
+        <v>-5.284925360204617</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7249101650268357</v>
+        <v>0.8477704547768488</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4903188163605918</v>
+        <v>-0.4721417843803479</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.667905733356088</v>
+        <v>2.678811952544234</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.349420496156487</v>
+        <v>-5.042269771781454</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8189704716160939</v>
+        <v>0.9418307613661074</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4903188163605918</v>
+        <v>-0.4721417843803479</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.664903804576081</v>
+        <v>2.675810023764228</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.129399698119476</v>
+        <v>-4.822248973744443</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9085578278415123</v>
+        <v>1.031418117591526</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3490989712926116</v>
+        <v>-0.3309219393123677</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.751214748627484</v>
+        <v>2.76212096781563</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.996532009056199</v>
+        <v>-4.689381284681166</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9775990862686468</v>
+        <v>1.10045937601866</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3490989712926116</v>
+        <v>-0.3309219393123677</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.767108931429307</v>
+        <v>2.778015150617453</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.837016905536829</v>
+        <v>-4.529866181161796</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.042550972116697</v>
+        <v>1.16541126186671</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1895838677732417</v>
+        <v>-0.1714068357929978</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.863963837981231</v>
+        <v>2.874870057169377</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.692344760437091</v>
+        <v>-4.385194036062058</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.110507932718031</v>
+        <v>1.233368222468045</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.04491172267350424</v>
+        <v>-0.02673469069326034</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.960855227602513</v>
+        <v>2.971761446790659</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.752219587794784</v>
+        <v>-4.445068863419751</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.07259549317638</v>
+        <v>1.195455782926393</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1047865500311964</v>
+        <v>-0.08660951805095246</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.910967822589324</v>
+        <v>2.92187404177747</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.665420090015775</v>
+        <v>-4.358269365640743</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.12971578561055</v>
+        <v>1.252576075360563</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1047865500311964</v>
+        <v>-0.08660951805095246</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.93336831591189</v>
+        <v>2.944274535100036</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.667889796477581</v>
+        <v>-4.360739072102549</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.12880030439924</v>
+        <v>1.251660594149253</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1072562564930025</v>
+        <v>-0.08907922451275863</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.931958893408218</v>
+        <v>2.942865112596365</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.736259982801592</v>
+        <v>-4.429109258426559</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.112459152344337</v>
+        <v>1.235319442094351</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.09798055745678758</v>
+        <v>-0.07980352547654368</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.948531235304649</v>
+        <v>2.959437454492795</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.614843553175115</v>
+        <v>-4.307692828800082</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.151462432826819</v>
+        <v>1.274322722576833</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.09798055745678758</v>
+        <v>-0.07980352547654368</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.93896794393654</v>
+        <v>2.949874163124687</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.64583671250382</v>
+        <v>-4.338685988128788</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9637747341357241</v>
+        <v>1.086635023885737</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.09798055745678758</v>
+        <v>-0.07980352547654368</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.763677508976927</v>
+        <v>2.774583728165073</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.470362452711351</v>
+        <v>-4.163211728336318</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.0385316700445</v>
+        <v>1.161391959794513</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.09798055745678758</v>
+        <v>-0.07980352547654368</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.768244740968715</v>
+        <v>2.779150960156861</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.5812987053526</v>
+        <v>-4.274147980977567</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9698991977492071</v>
+        <v>1.09275948749922</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.09798055745678758</v>
+        <v>-0.07980352547654368</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.743986769729922</v>
+        <v>2.754892988918068</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581288</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.784325282895833</v>
+        <v>-4.4771745585208</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8918199519518195</v>
+        <v>1.014680241701833</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.301007135000021</v>
+        <v>-0.2828301030197771</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.625302208423888</v>
+        <v>2.636208427612034</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.62639968396054</v>
+        <v>-4.319248959585507</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.965162577958069</v>
+        <v>1.088022867708082</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.301007135000021</v>
+        <v>-0.2828301030197771</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.63547459485602</v>
+        <v>2.646380814044166</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.540156220934162</v>
+        <v>-4.233005496559129</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9946062337424804</v>
+        <v>1.117466523492494</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.301007135000021</v>
+        <v>-0.2828301030197771</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.63042086542988</v>
+        <v>2.641327084618026</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.541339305585224</v>
+        <v>-4.234188581210191</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9859087753265814</v>
+        <v>1.108769065076594</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3066501834665325</v>
+        <v>-0.2884731514862886</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.618810811794499</v>
+        <v>2.629717030982645</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.418211598591141</v>
+        <v>-4.111060874216108</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.035711731157316</v>
+        <v>1.158572020907329</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3066501834665325</v>
+        <v>-0.2884731514862886</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.619362684827601</v>
+        <v>2.630268904015747</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.325401117140281</v>
+        <v>-4.018250392765248</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.002108615629026</v>
+        <v>1.124968905379039</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2138397020156731</v>
+        <v>-0.1956626700354293</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.604321665589482</v>
+        <v>2.615227884777628</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.276838064919251</v>
+        <v>-3.969687340544218</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.023407312442038</v>
+        <v>1.146267602192052</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.165276649794643</v>
+        <v>-0.1470996178143991</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.635332972846701</v>
+        <v>2.646239192034847</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.164166846683001</v>
+        <v>-3.857016122307968</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.063551508248262</v>
+        <v>1.186411797998275</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05260543155839276</v>
+        <v>-0.03442839957814886</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.698011412300174</v>
+        <v>2.70891763148832</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.051789845500328</v>
+        <v>-3.744639121125295</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.113993604551998</v>
+        <v>1.236853894302011</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05260543155839276</v>
+        <v>-0.03442839957814886</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.703502708130841</v>
+        <v>2.714408927318987</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.689594264968859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.250024414387059</v>
+        <v>-3.942873690012025</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.046196978765845</v>
+        <v>1.169057268515858</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2508400004451233</v>
+        <v>-0.2326629684648794</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.596059168567342</v>
+        <v>2.606965387755488</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.333025695412338</v>
+        <v>-4.025874971037304</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8513521863563864</v>
+        <v>0.9742124761063999</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2694108849722971</v>
+        <v>-0.2512338529920532</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.423272357851691</v>
+        <v>2.434178577039837</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199265</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.173831423355761</v>
+        <v>-3.866680698980728</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.035179555898223</v>
+        <v>1.158039845648236</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2694108849722971</v>
+        <v>-0.2512338529920532</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.543422018570896</v>
+        <v>2.554328237759043</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660764</v>
+        <v>3.733008865660765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.260430006336864</v>
+        <v>-3.953279281961831</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.015053148808104</v>
+        <v>1.137913438558118</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2694108849722971</v>
+        <v>-0.2512338529920532</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.557935044673219</v>
+        <v>2.568841263861366</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117049438342</v>
+        <v>3.741170494383421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.222046343778713</v>
+        <v>-3.914895619403679</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.027826055173734</v>
+        <v>1.150686344923747</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2310272224141459</v>
+        <v>-0.212850190433902</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.578384683550479</v>
+        <v>2.589290902738625</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.044930013743547</v>
+        <v>-3.737779289368513</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.095401616033102</v>
+        <v>1.218261905783115</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2310272224141459</v>
+        <v>-0.212850190433902</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.575113712395781</v>
+        <v>2.586019931583927</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263898</v>
+        <v>3.741324873263899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.015227889767253</v>
+        <v>-3.70807716539222</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.107965857385532</v>
+        <v>1.230826147135546</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2354973476294593</v>
+        <v>-0.2173203156492154</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.573115029028506</v>
+        <v>2.584021248216652</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.835852468528485</v>
+        <v>-3.528701744153452</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.173503001187454</v>
+        <v>1.296363290937467</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07872058945874061</v>
+        <v>-0.06054355747849671</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.660968059237351</v>
+        <v>2.671874278425498</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.880866682049092</v>
+        <v>-3.573715957674058</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.136304771110801</v>
+        <v>1.259165060860815</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1090694847733452</v>
+        <v>-0.09089245279310132</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.623566177380178</v>
+        <v>2.634472396568325</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>3.737023032979535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.147871192321527</v>
+        <v>-3.840720467946493</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.035194529340773</v>
+        <v>1.158054819090786</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3034325228162938</v>
+        <v>-0.2852554908360499</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.512639916893355</v>
+        <v>2.523546136081501</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230804</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.436658412780442</v>
+        <v>-4.129507688405408</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9188835630537082</v>
+        <v>1.041743852803722</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4045186429152942</v>
+        <v>-0.3863416109350503</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.451192166730456</v>
+        <v>2.462098385918603</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285449</v>
+        <v>3.70556808628545</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.40418282660967</v>
+        <v>-4.097032102234636</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9294737590763338</v>
+        <v>1.052334048826347</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4045186429152942</v>
+        <v>-0.3863416109350503</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.448792128284773</v>
+        <v>2.459698347472919</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.385144698902373</v>
+        <v>-4.077993974527339</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9336137293674975</v>
+        <v>1.056474019117511</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4627022542464887</v>
+        <v>-0.4445252222662448</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.410406680694301</v>
+        <v>2.421312899882447</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.557134463074516</v>
+        <v>3.472200998958121</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.663090847585436</v>
+        <v>2.626046759054874</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.385144698902373</v>
+        <v>-4.077993974527339</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9336137293674975</v>
+        <v>1.056474019117511</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4627022542464887</v>
+        <v>-0.4445252222662448</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.656154644571804</v>
+        <v>2.619110556041242</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-34.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.7%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-680.3%</t>
+          <t>-698.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-54.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>425.0%</t>
+          <t>446.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-569.4%</t>
+          <t>-561.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.5%</t>
+          <t>-271.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>1152.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.6%</t>
+          <t>-259.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>-215.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-105.1%</t>
+          <t>-181.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.4%</t>
+          <t>-265.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,42 +1451,42 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-188.0%</t>
+          <t>-179.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-193.6%</t>
         </is>
       </c>
     </row>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1133650073075221</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.202500835219746</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43868,19 +43868,19 @@
         <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.156088696795822</v>
+        <v>3.239996511172742</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1184025980351086</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.203093311696119</v>
+        <v>3.214601547506736</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.267680983726923</v>
       </c>
     </row>
     <row r="1841">
@@ -43891,19 +43891,19 @@
         <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.13483507841956</v>
+        <v>3.218742892796479</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.04422348192952996</v>
+        <v>-0.2252224283452861</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.116789261334</v>
+        <v>3.128297497144617</v>
       </c>
       <c r="F1841" t="n">
         <v>1.55018137429233</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.064943902994957</v>
+        <v>4.148851717371877</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.13585268755003</v>
+        <v>3.219760501926949</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.109990871978942</v>
+        <v>-0.2909898183946981</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.091499914444706</v>
+        <v>3.103008150255323</v>
       </c>
       <c r="F1842" t="n">
         <v>1.55018137429233</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.065961512125428</v>
+        <v>4.149869326502348</v>
       </c>
     </row>
     <row r="1843">
@@ -43937,19 +43937,19 @@
         <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.126480719537785</v>
+        <v>3.210388533914705</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3269996946466961</v>
+        <v>-0.5079986410624522</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.99532441736536</v>
+        <v>3.006832653175977</v>
       </c>
       <c r="F1843" t="n">
         <v>1.55018137429233</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.056589544113184</v>
+        <v>4.140497358490103</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.116563445493024</v>
+        <v>3.200471259869943</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4087715950744478</v>
+        <v>-0.5897705414902039</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.952698383149497</v>
+        <v>2.964206618960114</v>
       </c>
       <c r="F1844" t="n">
         <v>1.577216947698467</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.062893614112104</v>
+        <v>4.146801428489024</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.121328762326726</v>
+        <v>3.205236576703645</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4759807029463255</v>
+        <v>-0.6569796493620816</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.930580056834448</v>
+        <v>2.942088292645066</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.067658930945806</v>
+        <v>4.151566745322726</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.119153558445966</v>
+        <v>3.203061372822886</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6835464873379373</v>
+        <v>-0.8645454337536935</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.845378539197044</v>
+        <v>2.856886775007661</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940944256430079</v>
+        <v>4.024852070806999</v>
       </c>
     </row>
     <row r="1847">
@@ -44029,19 +44029,19 @@
         <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.117080449951029</v>
+        <v>3.200988264327949</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.101300510884774</v>
+        <v>-1.282299457300531</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.676203821283372</v>
+        <v>2.687712057093989</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.68821873380704</v>
+        <v>3.77212654818396</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.116946666549951</v>
+        <v>3.200854480926871</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.322922444442892</v>
+        <v>-1.503921390858648</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.587421264459047</v>
+        <v>2.598929500269664</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.665569270193541</v>
+        <v>3.749477084570461</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.121838811103876</v>
+        <v>3.205746625480796</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.530926502795969</v>
+        <v>-1.711925449211725</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.509111785671741</v>
+        <v>2.520620021482359</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.670461414747466</v>
+        <v>3.754369229124386</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.116920267441865</v>
+        <v>3.200828081818784</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.742338923683944</v>
+        <v>-1.9233378700997</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.419628273654539</v>
+        <v>2.431136509465157</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.538695418552669</v>
+        <v>3.622603232929589</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.110004566748314</v>
+        <v>3.193912381125233</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.081497301272466</v>
+        <v>-2.262496247688222</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.27704922192558</v>
+        <v>2.288557457736197</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.328284691306005</v>
+        <v>3.412192505682925</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.130342856487082</v>
+        <v>3.214250670864002</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.289988082724151</v>
+        <v>-2.470987029139907</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.213991199083674</v>
+        <v>2.225499434894291</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.223528512173762</v>
+        <v>3.307436326550682</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.13844160689565</v>
+        <v>3.22234942127257</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.783312954259329</v>
+        <v>-2.964311900675085</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.024760000878172</v>
+        <v>2.036268236688789</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.16863559403856</v>
+        <v>3.252543408415479</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.139547998939383</v>
+        <v>3.223455813316302</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.275697982283426</v>
+        <v>-3.456696928699182</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.828912381712265</v>
+        <v>1.840420617522882</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.874310969267834</v>
+        <v>2.958218783644754</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.138090537752246</v>
+        <v>3.221998352129166</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.660878373213498</v>
+        <v>-3.841877319629254</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.673382764153099</v>
+        <v>1.684890999963716</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.872853508080697</v>
+        <v>2.956761322457617</v>
       </c>
     </row>
     <row r="1856">
@@ -44236,19 +44236,19 @@
         <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.223767475583782</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.004561146440161</v>
+        <v>-4.185560092855917</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.53767877831705</v>
+        <v>1.549187014127668</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.809879000318983</v>
+        <v>2.893786814695902</v>
       </c>
     </row>
     <row r="1857">
@@ -44259,19 +44259,19 @@
         <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.21987353424004</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.211072923327182</v>
+        <v>-4.392071869742939</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.4511801262185</v>
+        <v>1.462688362029117</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.682077992843027</v>
+        <v>2.765985807219947</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.221646460940299</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.520307026323233</v>
+        <v>-4.701305972738989</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.329259411720339</v>
+        <v>1.340767647530956</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.683850919543287</v>
+        <v>2.767758733920207</v>
       </c>
     </row>
     <row r="1859">
@@ -44305,19 +44305,19 @@
         <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.207979348407703</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.952112819473021</v>
+        <v>-5.133111765888777</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.142869981927828</v>
+        <v>1.154378217738445</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.588333309145932</v>
+        <v>2.672241123522851</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.196264123409794</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.186806813605573</v>
+        <v>-5.367805760021329</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.037277159276898</v>
+        <v>1.048785395087515</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.580419844485575</v>
+        <v>2.664327658862494</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.194844715065759</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.522469460836025</v>
+        <v>-5.703468407251782</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.901592692040682</v>
+        <v>0.9131009278512994</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.57900043614154</v>
+        <v>2.66290825051846</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.201332275300001</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.886095705736339</v>
+        <v>-6.067094652152095</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7626297543147986</v>
+        <v>0.7741379901254155</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.526555014255506</v>
+        <v>2.610462828632426</v>
       </c>
     </row>
     <row r="1863">
@@ -44397,19 +44397,19 @@
         <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.200586790305832</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.251223088375085</v>
+        <v>-6.432222034790842</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6158333162651313</v>
+        <v>0.6273415520757482</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.34802305868193</v>
+        <v>2.43193087305885</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.199348334320591</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.659811865555763</v>
+        <v>-6.840810811971521</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4511593494076189</v>
+        <v>0.4626675852182358</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.101631336388282</v>
+        <v>2.185539150765202</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.194533766792052</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.072794349696857</v>
+        <v>-7.253793296112614</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2811517882226422</v>
+        <v>0.2926600240332586</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.096816768859743</v>
+        <v>2.180724583236662</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.192527817400929</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.489186223983855</v>
+        <v>-7.670185170399612</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1125890891167205</v>
+        <v>0.1240973249273374</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.09481081946862</v>
+        <v>2.17871863384554</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.202786508069608</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.865863234513699</v>
+        <v>-8.046862180929455</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.02782302442653828</v>
+        <v>-0.01631478861592139</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.105069510137299</v>
+        <v>2.188977324514219</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.198886073215303</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.211738056498508</v>
+        <v>-8.392737002914265</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1700733880747665</v>
+        <v>-0.1585651522641496</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.101169075282995</v>
+        <v>2.185076889659914</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.197290993270304</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.375317934682892</v>
+        <v>-8.556316881098649</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2371004192935193</v>
+        <v>-0.2255921834829024</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.099573995337995</v>
+        <v>2.183481809714915</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.201069969199513</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.67197927649309</v>
+        <v>-8.852978222908847</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3519859800883904</v>
+        <v>-0.3404777442777736</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.062107089826876</v>
+        <v>2.146014904203796</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.197043664665109</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.795223665708519</v>
+        <v>-8.976222612124277</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4053100403089651</v>
+        <v>-0.3938018044983487</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.058080785292473</v>
+        <v>2.141988599669393</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.196941563343525</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.178225054451151</v>
+        <v>-9.359224000866908</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.558612697127602</v>
+        <v>-0.5471044613169851</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.057978683970889</v>
+        <v>2.141886498347809</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.199513079314956</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.335623934664271</v>
+        <v>-9.516622881080028</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6190007332414198</v>
+        <v>-0.6074924974308034</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.966110871814446</v>
+        <v>2.050018686191366</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.204863382613006</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.695154257168273</v>
+        <v>-9.87615320358403</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7574625589449706</v>
+        <v>-0.7459543231343537</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.971461175112497</v>
+        <v>2.055368989489416</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.212779402570183</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.745503320622495</v>
+        <v>-9.926502267038252</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7696861643694817</v>
+        <v>-0.7581779285588648</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.949167756997141</v>
+        <v>2.03307557137406</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.215821153191952</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.964652288696692</v>
+        <v>-10.14565123511245</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8543040009773919</v>
+        <v>-0.8427957651667755</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.820720126774391</v>
+        <v>1.904627941151311</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.131913338815032</v>
+        <v>3.215821153191952</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.960961363740282</v>
+        <v>-10.14196031015604</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8528276309948275</v>
+        <v>-0.8413193951842106</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.820720126774391</v>
+        <v>1.904627941151311</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.137426535933675</v>
+        <v>3.221334350310594</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16521953907015</v>
+        <v>-10.3462184854859</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9290177040081309</v>
+        <v>-0.9175094681975136</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.74964995712464</v>
+        <v>1.83355777150156</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.141909090418111</v>
+        <v>3.22581690479503</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.38325731070132</v>
+        <v>-10.56425625711708</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.011750258176165</v>
+        <v>-1.000242022365549</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.649270050751537</v>
+        <v>1.733177865128457</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.157280791911532</v>
+        <v>3.241188606288452</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.30978747903387</v>
+        <v>-10.49078642544963</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9669906240157653</v>
+        <v>-0.955482388205148</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.708723651245427</v>
+        <v>1.792631465622347</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.171836012659049</v>
+        <v>3.255743827035968</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.48491189642042</v>
+        <v>-10.66591084283617</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.022485170222866</v>
+        <v>-1.010976934412248</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.618204221561018</v>
+        <v>1.702112035937937</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.164616847757453</v>
+        <v>3.248524662134372</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.71936399043491</v>
+        <v>-10.90036293685066</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.123485172730258</v>
+        <v>-1.11197693691964</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.610985056659422</v>
+        <v>1.694892871036341</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.157944656983477</v>
+        <v>3.241852471360396</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.00716783497215</v>
+        <v>-10.96562008074148</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.245278901319129</v>
+        <v>-1.144751985249942</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.877190163033957</v>
+        <v>-2.654643462387532</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.431630559163103</v>
+        <v>1.649066393927877</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.159060446822033</v>
+        <v>3.242968261198953</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.23699228213597</v>
+        <v>-11.1954445279053</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.336092890346102</v>
+        <v>-1.235565974276915</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.039837700104118</v>
+        <v>-2.817290999457692</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.335157826759563</v>
+        <v>1.552593661524337</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.161754175451148</v>
+        <v>3.245661989828067</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.46902120187223</v>
+        <v>-11.42747344764156</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.426210729611493</v>
+        <v>-1.325683813542306</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.101850397292541</v>
+        <v>-2.879303696646116</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.300643937075623</v>
+        <v>1.518079771840398</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.165744511137548</v>
+        <v>3.249652325514468</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.41700568790342</v>
+        <v>-11.37545793367275</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.401414188337567</v>
+        <v>-1.30088727226838</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.101850397292541</v>
+        <v>-2.879303696646116</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.304634272762024</v>
+        <v>1.522070107526799</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.164269284238807</v>
+        <v>3.248177098615726</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.55867752962754</v>
+        <v>-11.51712977539687</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.459558151925957</v>
+        <v>-1.35903123585677</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.101850397292541</v>
+        <v>-2.879303696646116</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.303159045863282</v>
+        <v>1.520594880628057</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.179322694403679</v>
+        <v>3.263230508780599</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.50908668520271</v>
+        <v>-11.46753893097204</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.424668403991151</v>
+        <v>-1.324141487921964</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.052259552867707</v>
+        <v>-2.829712852221282</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.347966962683055</v>
+        <v>1.56540279744783</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.166271560756996</v>
+        <v>3.250179375133916</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.30993457796561</v>
+        <v>-11.26838682373494</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.358058694742994</v>
+        <v>-1.257531778673807</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.886937026917894</v>
+        <v>-2.664390326271469</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.43410934460626</v>
+        <v>1.651545179371035</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.175850633793205</v>
+        <v>3.259758448170124</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.08408942524619</v>
+        <v>-11.04254167101553</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.25814156061902</v>
+        <v>-1.157614644549834</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.84501035133073</v>
+        <v>-2.622463650684305</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.468844422994767</v>
+        <v>1.686280257759542</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.176989778349264</v>
+        <v>3.260897592726183</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.9595107689086</v>
+        <v>-10.91796301467794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.207170953527925</v>
+        <v>-1.106644037458738</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.84501035133073</v>
+        <v>-2.622463650684305</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.469983567550826</v>
+        <v>1.687419402315601</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.179623552511371</v>
+        <v>3.263531366888291</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.01240605695289</v>
+        <v>-10.97085830272222</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.225695294583532</v>
+        <v>-1.125168378514346</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.840055005242284</v>
+        <v>-2.617508304595859</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.475590549366001</v>
+        <v>1.693026384130776</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.185357256750008</v>
+        <v>3.269265071126927</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.72849732602414</v>
+        <v>-10.68694957179347</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.106398097973396</v>
+        <v>-1.005871181904209</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.840055005242284</v>
+        <v>-2.617508304595859</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.481324253604638</v>
+        <v>1.698760088369413</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.175619994356143</v>
+        <v>3.259527808733062</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.65713093341449</v>
+        <v>-10.61558317918383</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.087588803323402</v>
+        <v>-0.9870618872542156</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.768688612632636</v>
+        <v>-2.546141911986211</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.514406826776561</v>
+        <v>1.731842661541336</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.165736513043235</v>
+        <v>3.249644327420155</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.39329406621042</v>
+        <v>-10.35174631197976</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9919375377546813</v>
+        <v>-0.8914106216854951</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.768688612632636</v>
+        <v>-2.546141911986211</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.504523345463654</v>
+        <v>1.721959180228428</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.163901952543861</v>
+        <v>3.247809766920781</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.12605226534203</v>
+        <v>-10.08450451111136</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8868753779066965</v>
+        <v>-0.7863484618375103</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.768688612632636</v>
+        <v>-2.546141911986211</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.50268878496428</v>
+        <v>1.720124619729055</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.1636016375704</v>
+        <v>3.24750945194732</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.02814522666553</v>
+        <v>-9.986597472434868</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8480128774095612</v>
+        <v>-0.7474859613403746</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.700702862772079</v>
+        <v>-2.478156162125654</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.543179919907153</v>
+        <v>1.760615754671928</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.164270143715894</v>
+        <v>3.248177958092814</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.00419168568958</v>
+        <v>-9.96264393145891</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8377629548736842</v>
+        <v>-0.7372360388044976</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.676749321796122</v>
+        <v>-2.454202621149697</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.558220550638221</v>
+        <v>1.775656385402996</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.151009827554142</v>
+        <v>3.234917641931061</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.74013174736678</v>
+        <v>-9.698583993136113</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7453992957063176</v>
+        <v>-0.644872379637131</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.412689383473326</v>
+        <v>-2.190142682826901</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.703396197470147</v>
+        <v>1.920832032234921</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.148222793893841</v>
+        <v>3.232130608270761</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.033052123861943</v>
+        <v>-8.991504369631276</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4653544799646836</v>
+        <v>-0.364827563895497</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.412689383473326</v>
+        <v>-2.190142682826901</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.700609163809846</v>
+        <v>1.91804499857462</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.148566417781682</v>
+        <v>3.232474232158602</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.992867825495752</v>
+        <v>-8.951320071265085</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4489371367303661</v>
+        <v>-0.3484102206611794</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.372505085107135</v>
+        <v>-2.14995838446071</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.725063366717402</v>
+        <v>1.942499201482176</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.147933239002439</v>
+        <v>3.231841053379359</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.912798029957948</v>
+        <v>-8.871250275727281</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4175423972944872</v>
+        <v>-0.317015481225301</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.292435289569331</v>
+        <v>-2.069888588922906</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.772472065260841</v>
+        <v>1.989907900025615</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.155857667840292</v>
+        <v>3.239765482217211</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.679316807728348</v>
+        <v>-8.637769053497681</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3162254795647952</v>
+        <v>-0.2156985634956086</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.058954067339732</v>
+        <v>-1.836407366693308</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.920485227436453</v>
+        <v>2.137921062201227</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.236873271904252</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.529650416720834</v>
+        <v>-8.488102662490167</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2592511334747485</v>
+        <v>-0.1587242174055623</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.966050576097196</v>
+        <v>-1.743503875450772</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.973335111869015</v>
+        <v>2.19077094663379</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.232240758651279</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.397374943089947</v>
+        <v>-8.35582718885928</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2109734572753665</v>
+        <v>-0.1104465412061804</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.83377510246631</v>
+        <v>-1.611228401819885</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.048067882794574</v>
+        <v>2.265503717559349</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.235055819338916</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.249372988213615</v>
+        <v>-8.192569338489962</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1489576146371974</v>
+        <v>-0.04232834037081634</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.685773147589978</v>
+        <v>-1.447970551450567</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.13968411640801</v>
+        <v>2.366273488468575</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.247962160562575</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.000373189530034</v>
+        <v>-7.943569539806381</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.03645135394010612</v>
+        <v>0.0701779203262749</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.685773147589978</v>
+        <v>-1.447970551450567</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.152590457631669</v>
+        <v>2.379179829692235</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.119986230963356</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.105963179303139</v>
+        <v>-8.049159529579486</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2066632794485663</v>
+        <v>-0.1000340051821857</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.791363137363082</v>
+        <v>-1.553560541223672</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.961260534168587</v>
+        <v>2.187849906229153</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.168530572840442</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.124698081421736</v>
+        <v>-8.067894431698083</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1656128984189191</v>
+        <v>-0.05898362415253811</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.791363137363082</v>
+        <v>-1.553560541223672</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009804876045674</v>
+        <v>2.236394248106239</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>3.048651650152275</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.976758040014136</v>
+        <v>-7.919954390290483</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.226315804544047</v>
+        <v>-0.119686530277666</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.771042221454525</v>
+        <v>-1.533239625315114</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902118502902641</v>
+        <v>2.128707874963206</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>3.039937663898796</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.952529403625164</v>
+        <v>-7.895725753901511</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2253383362419359</v>
+        <v>-0.1187090619755553</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.746813585065552</v>
+        <v>-1.509010988926142</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.907941698482546</v>
+        <v>2.134531070543112</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>3.032977051803703</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.908980996854473</v>
+        <v>-7.85217734713082</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2148795856287529</v>
+        <v>-0.1082503113623723</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.746813585065552</v>
+        <v>-1.509010988926142</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.900981086387453</v>
+        <v>2.127570458448019</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>3.047439406184846</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.666832603400615</v>
+        <v>-7.610028953676962</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1035578738660665</v>
+        <v>0.003071400400314062</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.746813585065552</v>
+        <v>-1.509010988926142</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.915443440768596</v>
+        <v>2.142032812829162</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>3.041971526644041</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.495628485653234</v>
+        <v>-7.546799581908614</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.04054410630791905</v>
+        <v>0.02289526956684851</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.746813585065552</v>
+        <v>-1.509010988926142</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.909975561227791</v>
+        <v>2.136564933288357</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>3.039469620654618</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.372337350836103</v>
+        <v>-7.423508447091483</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.006270441629510071</v>
+        <v>0.06970981750427763</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.623522450248422</v>
+        <v>-1.385719854109011</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.981448336128646</v>
+        <v>2.208037708189212</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>3.047170598891944</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.35118815193266</v>
+        <v>-7.40235924818804</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.02243109942821242</v>
+        <v>0.08587047530298042</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.602373251344979</v>
+        <v>-1.364570655205568</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.001838833708037</v>
+        <v>2.228428205768603</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>3.042951307238994</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.107422709949216</v>
+        <v>-7.158593806204595</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1157179845686409</v>
+        <v>0.1791573604434089</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.602373251344979</v>
+        <v>-1.364570655205568</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.997619542055088</v>
+        <v>2.224208914115654</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>3.04507562115901</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.843394642755955</v>
+        <v>-6.894565739011336</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2234535253659611</v>
+        <v>0.2868929012407286</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.400507852529025</v>
+        <v>-1.162705256389615</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.120863095264676</v>
+        <v>2.347452467325242</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>3.037817696142712</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.593544248806881</v>
+        <v>-6.644715345062261</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3161357579292932</v>
+        <v>0.3795751338040607</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.400507852529025</v>
+        <v>-1.162705256389615</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.113605170248378</v>
+        <v>2.340194542308944</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>3.041416819663361</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.417652156339448</v>
+        <v>-6.468823252594829</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3900917184369148</v>
+        <v>0.4535310943116819</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.400507852529025</v>
+        <v>-1.162705256389615</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.117204293769027</v>
+        <v>2.343793665829593</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>3.054744325717915</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.246205693316985</v>
+        <v>-6.297376789572366</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4719978097004538</v>
+        <v>0.5354371855752214</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.229061389506562</v>
+        <v>-0.9912587933671514</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.233399677637058</v>
+        <v>2.459989049697624</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>3.053764803334212</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.021172693648162</v>
+        <v>-6.072343789903543</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5610314871842799</v>
+        <v>0.6244708630590474</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.004028389837739</v>
+        <v>-0.7662257936983286</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.367439955054649</v>
+        <v>2.594029327115215</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>3.058459604388529</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.806538316011755</v>
+        <v>-5.857709412267136</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6515800392931599</v>
+        <v>0.7150194151679274</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7893940122013321</v>
+        <v>-0.5515914160619217</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.500915382690811</v>
+        <v>2.727504754751376</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>3.039653863172325</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.713538274805857</v>
+        <v>-5.764709371061238</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6699743145593149</v>
+        <v>0.7334136904340824</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7893940122013321</v>
+        <v>-0.5515914160619217</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.482109641474606</v>
+        <v>2.708699013535172</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>3.041396939797202</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.473107778000997</v>
+        <v>-5.524278874256377</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7678895899061366</v>
+        <v>0.8313289657809038</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5489635153964718</v>
+        <v>-0.3111609192570615</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.6281110161824</v>
+        <v>2.854700388242966</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>3.045326253632022</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.400865209829802</v>
+        <v>-5.452036306085183</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8007159310094347</v>
+        <v>0.8641553068842018</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5489635153964718</v>
+        <v>-0.3111609192570615</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.63204033001722</v>
+        <v>2.858629702077786</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>3.046004837549362</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.284925360204617</v>
+        <v>-5.336096456459997</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8477704547768488</v>
+        <v>0.9112098306516159</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4721417843803479</v>
+        <v>-0.2343391882409376</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.678811952544234</v>
+        <v>2.9054013246048</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>3.043002908769356</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.042269771781454</v>
+        <v>-5.093440868036835</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9418307613661074</v>
+        <v>1.005270137240875</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4721417843803479</v>
+        <v>-0.2343391882409376</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.675810023764228</v>
+        <v>2.902399395824793</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>3.04458194577997</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.822248973744443</v>
+        <v>-4.873420069999824</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.031418117591526</v>
+        <v>1.094857493466293</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3309219393123677</v>
+        <v>-0.09311934317295734</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.76212096781563</v>
+        <v>2.988710339876196</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>3.060476128581793</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.689381284681166</v>
+        <v>-4.740552380936546</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.10045937601866</v>
+        <v>1.163898751893427</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3309219393123677</v>
+        <v>-0.09311934317295734</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.778015150617453</v>
+        <v>3.004604522678019</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>3.061621973022095</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.529866181161796</v>
+        <v>-4.581037277417177</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.16541126186671</v>
+        <v>1.228850637741477</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1714068357929978</v>
+        <v>0.06639576034641259</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.874870057169377</v>
+        <v>3.101459429229943</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>3.071710075583535</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.385194036062058</v>
+        <v>-4.436365132317439</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.233368222468045</v>
+        <v>1.296807598342812</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02673469069326034</v>
+        <v>0.21106790544615</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.971761446790659</v>
+        <v>3.198350818851225</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.973839752608041</v>
+        <v>3.057747566984961</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.445068863419751</v>
+        <v>-4.496239959675131</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.195455782926393</v>
+        <v>1.258895158801161</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08660951805095246</v>
+        <v>0.1511930780884579</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.92187404177747</v>
+        <v>3.148463413838036</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>3.080148060307527</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.358269365640743</v>
+        <v>-4.409440461896123</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.252576075360563</v>
+        <v>1.31601545123533</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08660951805095246</v>
+        <v>0.1511930780884579</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.944274535100036</v>
+        <v>3.170863907160602</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>3.080220461680939</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.360739072102549</v>
+        <v>-4.411910168357929</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.251660594149253</v>
+        <v>1.31509997002402</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08907922451275863</v>
+        <v>0.1487233716266517</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.942865112596365</v>
+        <v>3.16945448465693</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.091227384155641</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.429109258426559</v>
+        <v>-4.480280354681939</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.235319442094351</v>
+        <v>1.298758817969118</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.07980352547654368</v>
+        <v>0.1579990706628667</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.959437454492795</v>
+        <v>3.186026826553361</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>3.081664092787532</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.307692828800082</v>
+        <v>-4.358863925055463</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.274322722576833</v>
+        <v>1.3377620984516</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.07980352547654368</v>
+        <v>0.1579990706628667</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.949874163124687</v>
+        <v>3.176463535185253</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.906373657827919</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.338685988128788</v>
+        <v>-4.389857084384168</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.086635023885737</v>
+        <v>1.150074399760505</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.07980352547654368</v>
+        <v>0.1579990706628667</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.774583728165073</v>
+        <v>3.001173100225639</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.910940889819707</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.163211728336318</v>
+        <v>-4.214382824591699</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.161391959794513</v>
+        <v>1.22483133566928</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.07980352547654368</v>
+        <v>0.1579990706628667</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.779150960156861</v>
+        <v>3.005740332217427</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>2.886682918580914</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.274147980977567</v>
+        <v>-4.325319077232948</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.09275948749922</v>
+        <v>1.156198863373988</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.07980352547654368</v>
+        <v>0.1579990706628667</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.754892988918068</v>
+        <v>2.981482360978634</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>2.889814303800819</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.4771745585208</v>
+        <v>-4.528345654776181</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.014680241701833</v>
+        <v>1.0781196175766</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2828301030197771</v>
+        <v>-0.04502750688036672</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.636208427612034</v>
+        <v>2.8627977996726</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>2.899986690232952</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.319248959585507</v>
+        <v>-4.370420055840888</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.088022867708082</v>
+        <v>1.151462243582849</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2828301030197771</v>
+        <v>-0.04502750688036672</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.646380814044166</v>
+        <v>2.872970186104732</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>2.894932960806812</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.233005496559129</v>
+        <v>-4.28417659281451</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.117466523492494</v>
+        <v>1.180905899367261</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2828301030197771</v>
+        <v>-0.04502750688036672</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.641327084618026</v>
+        <v>2.867916456678592</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>2.886708736251338</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.234188581210191</v>
+        <v>-4.285359677465571</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.108769065076594</v>
+        <v>1.172208440951362</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2884731514862886</v>
+        <v>-0.05067055534687825</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.629717030982645</v>
+        <v>2.856306403043211</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>2.887260609284439</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.111060874216108</v>
+        <v>-4.162231970471488</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158572020907329</v>
+        <v>1.222011396782097</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2884731514862886</v>
+        <v>-0.05067055534687825</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.630268904015747</v>
+        <v>2.856858276076313</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.816533301175805</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.018250392765248</v>
+        <v>-4.069421489020629</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124968905379039</v>
+        <v>1.188408281253806</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1956626700354293</v>
+        <v>0.0421399261039811</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.615227884777628</v>
+        <v>2.841817256838194</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.818406777100406</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.969687340544218</v>
+        <v>-4.059327955155637</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.146267602192052</v>
+        <v>1.194319170724404</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1470996178143991</v>
+        <v>0.05223345996897277</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.646239192034847</v>
+        <v>2.84974685308179</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.813482485612129</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.857016122307968</v>
+        <v>-3.946656736919387</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.186411797998275</v>
+        <v>1.234463366530627</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03442839957814886</v>
+        <v>0.164904678205223</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.70891763148832</v>
+        <v>2.912425292535263</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.818973781442796</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.744639121125295</v>
+        <v>-3.834279735736714</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.236853894302011</v>
+        <v>1.284905462834363</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03442839957814886</v>
+        <v>0.164904678205223</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.714408927318987</v>
+        <v>2.91791658836593</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968859</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.830470983211335</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.942873690012025</v>
+        <v>-4.032514304623445</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.169057268515858</v>
+        <v>1.21710883704821</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2326629684648794</v>
+        <v>-0.0333298906815076</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.606965387755488</v>
+        <v>2.810473048802431</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175319</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.668826703211988</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.025874971037304</v>
+        <v>-4.115515585648724</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9742124761063999</v>
+        <v>1.022264044638752</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2512338529920532</v>
+        <v>-0.05190077520868136</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.434178577039837</v>
+        <v>2.63768623808678</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.788976363931194</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.866680698980728</v>
+        <v>-3.956321313592147</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.158039845648236</v>
+        <v>1.206091414180588</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2512338529920532</v>
+        <v>-0.05190077520868136</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.554328237759043</v>
+        <v>2.757835898805985</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660765</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.803489390033517</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.953279281961831</v>
+        <v>-4.042919896573251</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.137913438558118</v>
+        <v>1.185965007090469</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2512338529920532</v>
+        <v>-0.05190077520868136</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.568841263861366</v>
+        <v>2.772348924908308</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383421</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.800908831375886</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.914895619403679</v>
+        <v>-4.0045362340151</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.150686344923747</v>
+        <v>1.198737913456098</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.212850190433902</v>
+        <v>-0.01351711265053018</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.589290902738625</v>
+        <v>2.792798563785568</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.797637860221188</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.737779289368513</v>
+        <v>-3.827419903979933</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.218261905783115</v>
+        <v>1.266313474315467</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.212850190433902</v>
+        <v>-0.01351711265053018</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.586019931583927</v>
+        <v>2.78952759263087</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263899</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.798321251983101</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.70807716539222</v>
+        <v>-3.79771778000364</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.230826147135546</v>
+        <v>1.278877715667897</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2173203156492154</v>
+        <v>-0.01798723786584355</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.584021248216652</v>
+        <v>2.787528909263595</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481233</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.792108227289515</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.528701744153452</v>
+        <v>-3.618342358764872</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.296363290937467</v>
+        <v>1.344414859469819</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.06054355747849671</v>
+        <v>0.1387895203048751</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.671874278425498</v>
+        <v>2.87538193947244</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.772915682621105</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.573715957674058</v>
+        <v>-3.663356572285478</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.259165060860815</v>
+        <v>1.307216629393166</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.09089245279310132</v>
+        <v>0.1084406249902705</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.634472396568325</v>
+        <v>2.837980057615267</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979535</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.778607244960051</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.840720467946493</v>
+        <v>-3.930361082557914</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.158054819090786</v>
+        <v>1.206106387623138</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2852554908360499</v>
+        <v>-0.08592241305267806</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.523546136081501</v>
+        <v>2.727053797128444</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>2.777811166856552</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.129507688405408</v>
+        <v>-4.219148303016829</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.041743852803722</v>
+        <v>1.089795421336073</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3863416109350503</v>
+        <v>-0.1870085331516784</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.462098385918603</v>
+        <v>2.665606046965545</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.691503314033949</v>
+        <v>2.775411128410869</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.097032102234636</v>
+        <v>-4.186672716846057</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.052334048826347</v>
+        <v>1.100385617358699</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3863416109350503</v>
+        <v>-0.1870085331516784</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.459698347472919</v>
+        <v>2.663206008519862</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.688028033242194</v>
+        <v>2.771935847619114</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.077993974527339</v>
+        <v>-4.028904772143104</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.056474019117511</v>
+        <v>1.160017514448125</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4445252222662448</v>
+        <v>-0.4125521621592376</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.421312899882447</v>
+        <v>2.524404550323571</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.472200998958121</v>
+        <v>3.467054031490409</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.626046759054874</v>
+        <v>2.771554898820841</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.077993974527339</v>
+        <v>-3.996241101867553</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.056474019117511</v>
+        <v>1.172702033760073</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4445252222662448</v>
+        <v>-0.4125521621592376</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.619110556041242</v>
+        <v>2.524023601525299</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240513.xlsx
+++ b/tame_output/ON/bt/strategyON_20240513.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-45.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.4%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-698.4%</t>
+          <t>-697.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.7%</t>
+          <t>446.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-561.2%</t>
+          <t>-592.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-271.3%</t>
+          <t>-279.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1152.8%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.0%</t>
+          <t>-282.6%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-312.6%</t>
+          <t>-311.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-215.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-181.3%</t>
+          <t>-189.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.2%</t>
+          <t>-263.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-179.6%</t>
+          <t>-187.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-193.6%</t>
+          <t>-203.3%</t>
         </is>
       </c>
     </row>
@@ -43868,19 +43868,19 @@
         <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.239996511172742</v>
+        <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
         <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.214601547506736</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.267680983726923</v>
+        <v>4.183773169350004</v>
       </c>
     </row>
     <row r="1841">
@@ -43891,19 +43891,19 @@
         <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.218742892796479</v>
+        <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2252224283452861</v>
+        <v>-0.2145341394007469</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.128297497144617</v>
+        <v>3.048664998345513</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.55018137429233</v>
+        <v>1.560869663236869</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.148851717371877</v>
+        <v>4.071356876361682</v>
       </c>
     </row>
     <row r="1842">
@@ -43914,19 +43914,19 @@
         <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.219760501926949</v>
+        <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2909898183946981</v>
+        <v>-0.280301529450159</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.103008150255323</v>
+        <v>3.023375651456219</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.55018137429233</v>
+        <v>1.560869663236869</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.149869326502348</v>
+        <v>4.072374485492151</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760745</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.210388533914705</v>
+        <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5079986410624522</v>
+        <v>-0.4973103521179131</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.006832653175977</v>
+        <v>2.927200154376873</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.55018137429233</v>
+        <v>1.560869663236869</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.140497358490103</v>
+        <v>4.063002517479907</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.200471259869943</v>
+        <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5897705414902039</v>
+        <v>-0.5790822525456648</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.964206618960114</v>
+        <v>2.88457412016101</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.577216947698467</v>
+        <v>1.587905236643006</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.146801428489024</v>
+        <v>4.069306587478827</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.205236576703645</v>
+        <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6569796493620816</v>
+        <v>-0.6462913604175424</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.942088292645066</v>
+        <v>2.862455793845962</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.577216947698467</v>
+        <v>1.587905236643006</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.151566745322726</v>
+        <v>4.07407190431253</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.203061372822886</v>
+        <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8645454337536935</v>
+        <v>-0.8538571448091543</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.856886775007661</v>
+        <v>2.777254276208557</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.369651163306855</v>
+        <v>1.380339452251394</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.024852070806999</v>
+        <v>3.947357229796803</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.200988264327949</v>
+        <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.282299457300531</v>
+        <v>-1.271611168355991</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.687712057093989</v>
+        <v>2.608079558294885</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9518971397600179</v>
+        <v>0.9625854287045569</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.77212654818396</v>
+        <v>3.694631707173764</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.200854480926871</v>
+        <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.503921390858648</v>
+        <v>-1.493233101914109</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.598929500269664</v>
+        <v>2.51929700147056</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9143710060726489</v>
+        <v>0.9250592950171879</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.749477084570461</v>
+        <v>3.671982243560264</v>
       </c>
     </row>
     <row r="1849">
@@ -44075,19 +44075,19 @@
         <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.205746625480796</v>
+        <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.711925449211725</v>
+        <v>-1.701237160267186</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.520620021482359</v>
+        <v>2.440987522683255</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9143710060726489</v>
+        <v>0.9250592950171879</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.754369229124386</v>
+        <v>3.676874388114189</v>
       </c>
     </row>
     <row r="1850">
@@ -44098,19 +44098,19 @@
         <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.200828081818784</v>
+        <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.9233378700997</v>
+        <v>-1.912649581155161</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.431136509465157</v>
+        <v>2.351504010666053</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7029585851846738</v>
+        <v>0.7136468741292128</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.622603232929589</v>
+        <v>3.545108391919392</v>
       </c>
     </row>
     <row r="1851">
@@ -44121,19 +44121,19 @@
         <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.193912381125233</v>
+        <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.262496247688222</v>
+        <v>-2.251807958743683</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.288557457736197</v>
+        <v>2.208924958937093</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3638002075961517</v>
+        <v>0.3744884965406907</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.412192505682925</v>
+        <v>3.334697664672728</v>
       </c>
     </row>
     <row r="1852">
@@ -44144,19 +44144,19 @@
         <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.214250670864002</v>
+        <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.470987029139907</v>
+        <v>-2.460298740195368</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.225499434894291</v>
+        <v>2.145866936095188</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1553094261444673</v>
+        <v>0.1659977150890063</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.307436326550682</v>
+        <v>3.229941485540486</v>
       </c>
     </row>
     <row r="1853">
@@ -44167,19 +44167,19 @@
         <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.22234942127257</v>
+        <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.964311900675085</v>
+        <v>-2.953623611730546</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.036268236688789</v>
+        <v>1.956635737889685</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.05032331190484857</v>
+        <v>0.06101160084938756</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.252543408415479</v>
+        <v>3.175048567405283</v>
       </c>
     </row>
     <row r="1854">
@@ -44190,19 +44190,19 @@
         <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.223455813316302</v>
+        <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.456696928699182</v>
+        <v>-3.446008639754643</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.840420617522882</v>
+        <v>1.760788118723778</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4420617161192482</v>
+        <v>-0.4313734271747092</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.958218783644754</v>
+        <v>2.880723942634557</v>
       </c>
     </row>
     <row r="1855">
@@ -44213,19 +44213,19 @@
         <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.221998352129166</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.841877319629254</v>
+        <v>-3.831189030684715</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.684890999963716</v>
+        <v>1.605258501164613</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4420617161192482</v>
+        <v>-0.4313734271747092</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.956761322457617</v>
+        <v>2.87926648144742</v>
       </c>
     </row>
     <row r="1856">
@@ -44236,19 +44236,19 @@
         <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.223767475583782</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.185560092855917</v>
+        <v>-4.174871803911378</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.549187014127668</v>
+        <v>1.469554515328564</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5499677681464663</v>
+        <v>-0.5392794792019273</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.893786814695902</v>
+        <v>2.816291973685706</v>
       </c>
     </row>
     <row r="1857">
@@ -44259,19 +44259,19 @@
         <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.21987353424004</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.392071869742939</v>
+        <v>-4.381383580798399</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.462688362029117</v>
+        <v>1.383055863230013</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7564795450334878</v>
+        <v>-0.7457912560889488</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.765985807219947</v>
+        <v>2.688490966209751</v>
       </c>
     </row>
     <row r="1858">
@@ -44282,19 +44282,19 @@
         <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.221646460940299</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.701305972738989</v>
+        <v>-4.69061768379445</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.340767647530956</v>
+        <v>1.261135148731852</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7564795450334878</v>
+        <v>-0.7457912560889488</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.767758733920207</v>
+        <v>2.69026389291001</v>
       </c>
     </row>
     <row r="1859">
@@ -44305,19 +44305,19 @@
         <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.207979348407703</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.133111765888777</v>
+        <v>-5.122423476944237</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.154378217738445</v>
+        <v>1.074745718939341</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8928970414747548</v>
+        <v>-0.8822087525302158</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.672241123522851</v>
+        <v>2.594746282512655</v>
       </c>
     </row>
     <row r="1860">
@@ -44328,19 +44328,19 @@
         <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.196264123409794</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.367805760021329</v>
+        <v>-5.35711747107679</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.048785395087515</v>
+        <v>0.9691528962884113</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8865607742454996</v>
+        <v>-0.8758724853009606</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.664327658862494</v>
+        <v>2.586832817852299</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.194844715065759</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.703468407251782</v>
+        <v>-5.692780118307242</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9131009278512994</v>
+        <v>0.8334684290521954</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8865607742454996</v>
+        <v>-0.8758724853009606</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.66290825051846</v>
+        <v>2.585413409508264</v>
       </c>
     </row>
     <row r="1862">
@@ -44374,19 +44374,19 @@
         <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.201332275300001</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.067094652152095</v>
+        <v>-6.056406363207556</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7741379901254155</v>
+        <v>0.6945054913263116</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9847824111126254</v>
+        <v>-0.9740941221680864</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.610462828632426</v>
+        <v>2.53296798762223</v>
       </c>
     </row>
     <row r="1863">
@@ -44397,19 +44397,19 @@
         <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.200586790305832</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.432222034790842</v>
+        <v>-6.421533745846302</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6273415520757482</v>
+        <v>0.5477090532766442</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.281093195411638</v>
+        <v>-1.270404906467099</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.43193087305885</v>
+        <v>2.354436032048653</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.199348334320591</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.840810811971521</v>
+        <v>-6.830122523026981</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4626675852182358</v>
+        <v>0.3830350864191319</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.678993683647777</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.185539150765202</v>
+        <v>2.108044309755005</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.194533766792052</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.253793296112614</v>
+        <v>-7.243105007168075</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2926600240332586</v>
+        <v>0.2130275252341551</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.678993683647777</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.180724583236662</v>
+        <v>2.103229742226466</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.192527817400929</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.670185170399612</v>
+        <v>-7.659496881455072</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1240973249273374</v>
+        <v>0.04446482612823344</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.678993683647777</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.17871863384554</v>
+        <v>2.101223792835343</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.202786508069608</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.046862180929455</v>
+        <v>-8.036173891984916</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.01631478861592139</v>
+        <v>-0.0959472874150249</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.678993683647777</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.188977324514219</v>
+        <v>2.111482483504022</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.198886073215303</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.392737002914265</v>
+        <v>-8.382048713969725</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1585651522641496</v>
+        <v>-0.2381976510632535</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.678993683647777</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.185076889659914</v>
+        <v>2.107582048649718</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.197290993270304</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.556316881098649</v>
+        <v>-8.54562859215411</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2255921834829024</v>
+        <v>-0.3052246822820064</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.678993683647777</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.183481809714915</v>
+        <v>2.105986968704719</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.201069969199513</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.852978222908847</v>
+        <v>-8.842289933964308</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3404777442777736</v>
+        <v>-0.4201102430768775</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.747736819381656</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.146014904203796</v>
+        <v>2.0685200631936</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.197043664665109</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.976222612124277</v>
+        <v>-8.965534323179737</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3938018044983487</v>
+        <v>-0.4734343032974522</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.747736819381656</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.141988599669393</v>
+        <v>2.064493758659196</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.196941563343525</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.359224000866908</v>
+        <v>-9.348535711922368</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5471044613169851</v>
+        <v>-0.626736960116089</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.747736819381656</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.141886498347809</v>
+        <v>2.064391657337612</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.199513079314956</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.516622881080028</v>
+        <v>-9.505934592135489</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6074924974308034</v>
+        <v>-0.6871249962299069</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.915823988539316</v>
+        <v>-1.905135699594777</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.050018686191366</v>
+        <v>1.97252384518117</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.204863382613006</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.87615320358403</v>
+        <v>-9.865464914639491</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7459543231343537</v>
+        <v>-0.8255868219334577</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.915823988539316</v>
+        <v>-1.905135699594777</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.055368989489416</v>
+        <v>1.97787414847922</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.212779402570183</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.926502267038252</v>
+        <v>-9.915813978093713</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7581779285588648</v>
+        <v>-0.8378104273579687</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.966173051993538</v>
+        <v>-1.955484763048999</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.03307557137406</v>
+        <v>1.955580730363864</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.215821153191952</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.14565123511245</v>
+        <v>-10.13496294616791</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8427957651667755</v>
+        <v>-0.922428263965879</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.185322020067736</v>
+        <v>-2.174633731123197</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.904627941151311</v>
+        <v>1.827133100141115</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.215821153191952</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.14196031015604</v>
+        <v>-10.1312720212115</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8413193951842106</v>
+        <v>-0.920951893983315</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.185322020067736</v>
+        <v>-2.174633731123197</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.904627941151311</v>
+        <v>1.827133100141115</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.221334350310594</v>
+        <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.3462184854859</v>
+        <v>-10.33553019654136</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9175094681975136</v>
+        <v>-0.9971419669966179</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.312960964681725</v>
+        <v>-2.302272675737186</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.83355777150156</v>
+        <v>1.756062930491364</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.22581690479503</v>
+        <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.56425625711708</v>
+        <v>-10.55356796817254</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.000242022365549</v>
+        <v>-1.079874521164653</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.487731732777624</v>
+        <v>-2.477043443833085</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.733177865128457</v>
+        <v>1.65568302411826</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.241188606288452</v>
+        <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.49078642544963</v>
+        <v>-10.48009813650509</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.955482388205148</v>
+        <v>-1.035114887004252</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.414261901110175</v>
+        <v>-2.403573612165636</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.792631465622347</v>
+        <v>1.715136624612151</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.255743827035968</v>
+        <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.66591084283617</v>
+        <v>-10.65522255389163</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.010976934412248</v>
+        <v>-1.090609433211353</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.589386318496719</v>
+        <v>-2.57869802955218</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.702112035937937</v>
+        <v>1.624617194927741</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.248524662134372</v>
+        <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.90036293685066</v>
+        <v>-10.88967464790612</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.11197693691964</v>
+        <v>-1.191609435718745</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.589386318496719</v>
+        <v>-2.57869802955218</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.694892871036341</v>
+        <v>1.617398030026145</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.241852471360396</v>
+        <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.96562008074148</v>
+        <v>-11.17747849244336</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.144751985249942</v>
+        <v>-1.313403164307616</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.654643462387532</v>
+        <v>-2.866501874089418</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.649066393927877</v>
+        <v>1.438043532529826</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.242968261198953</v>
+        <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.1954445279053</v>
+        <v>-11.40730293960719</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.235565974276915</v>
+        <v>-1.40421715333459</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.817290999457692</v>
+        <v>-3.029149411159579</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.552593661524337</v>
+        <v>1.341570800126286</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.245661989828067</v>
+        <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.42747344764156</v>
+        <v>-11.63933185934345</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.325683813542306</v>
+        <v>-1.49433499259998</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.879303696646116</v>
+        <v>-3.091162108348002</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.518079771840398</v>
+        <v>1.307056910442347</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.249652325514468</v>
+        <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.37545793367275</v>
+        <v>-11.58731634537464</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.30088727226838</v>
+        <v>-1.469538451326054</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.879303696646116</v>
+        <v>-3.091162108348002</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.522070107526799</v>
+        <v>1.311047246128748</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.248177098615726</v>
+        <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.51712977539687</v>
+        <v>-11.72898818709876</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.35903123585677</v>
+        <v>-1.527682414914444</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.879303696646116</v>
+        <v>-3.091162108348002</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.520594880628057</v>
+        <v>1.309572019230006</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.263230508780599</v>
+        <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.46753893097204</v>
+        <v>-11.67939734267392</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.324141487921964</v>
+        <v>-1.492792666979638</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.829712852221282</v>
+        <v>-3.041571263923168</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.56540279744783</v>
+        <v>1.354379936049779</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.250179375133916</v>
+        <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.26838682373494</v>
+        <v>-11.48024523543682</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.257531778673807</v>
+        <v>-1.426182957731481</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.664390326271469</v>
+        <v>-2.876248737973355</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.651545179371035</v>
+        <v>1.440522317972983</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.259758448170124</v>
+        <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.04254167101553</v>
+        <v>-11.25440008271741</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.157614644549834</v>
+        <v>-1.326265823607508</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.622463650684305</v>
+        <v>-2.834322062386191</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.686280257759542</v>
+        <v>1.47525739636149</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.260897592726183</v>
+        <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.91796301467794</v>
+        <v>-11.12982142637982</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.106644037458738</v>
+        <v>-1.275295216516412</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.622463650684305</v>
+        <v>-2.834322062386191</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.687419402315601</v>
+        <v>1.476396540917549</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.263531366888291</v>
+        <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.97085830272222</v>
+        <v>-11.18271671442411</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.125168378514346</v>
+        <v>-1.29381955757202</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.617508304595859</v>
+        <v>-2.829366716297745</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.693026384130776</v>
+        <v>1.482003522732725</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.269265071126927</v>
+        <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.68694957179347</v>
+        <v>-10.89880798349536</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.005871181904209</v>
+        <v>-1.174522360961883</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.617508304595859</v>
+        <v>-2.829366716297745</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.698760088369413</v>
+        <v>1.487737226971361</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.259527808733062</v>
+        <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.61558317918383</v>
+        <v>-10.82744159088571</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9870618872542156</v>
+        <v>-1.15571306631189</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.546141911986211</v>
+        <v>-2.758000323688097</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.731842661541336</v>
+        <v>1.520819800143284</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.249644327420155</v>
+        <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.35174631197976</v>
+        <v>-10.56360472368164</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8914106216854951</v>
+        <v>-1.060061800743169</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.546141911986211</v>
+        <v>-2.758000323688097</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.721959180228428</v>
+        <v>1.510936318830377</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.247809766920781</v>
+        <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.08450451111136</v>
+        <v>-10.29636292281324</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7863484618375103</v>
+        <v>-0.9549996408951844</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.546141911986211</v>
+        <v>-2.758000323688097</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.720124619729055</v>
+        <v>1.509101758331003</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.24750945194732</v>
+        <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.986597472434868</v>
+        <v>-10.19845588413675</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7474859613403746</v>
+        <v>-0.9161371403980483</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.478156162125654</v>
+        <v>-2.690014573827541</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.760615754671928</v>
+        <v>1.549592893273876</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.248177958092814</v>
+        <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.96264393145891</v>
+        <v>-10.1745023431608</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7372360388044976</v>
+        <v>-0.9058872178621722</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.454202621149697</v>
+        <v>-2.666061032851583</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.775656385402996</v>
+        <v>1.564633524004944</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.234917641931061</v>
+        <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.698583993136113</v>
+        <v>-9.910442404837999</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.644872379637131</v>
+        <v>-0.8135235586948051</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.190142682826901</v>
+        <v>-2.402001094528787</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.920832032234921</v>
+        <v>1.70980917083687</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.232130608270761</v>
+        <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.991504369631276</v>
+        <v>-9.203362781333162</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.364827563895497</v>
+        <v>-0.5334787429531711</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.190142682826901</v>
+        <v>-2.402001094528787</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.91804499857462</v>
+        <v>1.707022137176569</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.232474232158602</v>
+        <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.951320071265085</v>
+        <v>-9.163178482966972</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3484102206611794</v>
+        <v>-0.5170613997188536</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.14995838446071</v>
+        <v>-2.361816796162596</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.942499201482176</v>
+        <v>1.731476340084125</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.231841053379359</v>
+        <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.871250275727281</v>
+        <v>-9.083108687429167</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.317015481225301</v>
+        <v>-0.4856666602829751</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.069888588922906</v>
+        <v>-2.281747000624792</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.989907900025615</v>
+        <v>1.778885038627564</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.239765482217211</v>
+        <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.637769053497681</v>
+        <v>-8.849627465199568</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2156985634956086</v>
+        <v>-0.3843497425532827</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.836407366693308</v>
+        <v>-2.048265778395194</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.137921062201227</v>
+        <v>1.926898200803175</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.236873271904252</v>
+        <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.488102662490167</v>
+        <v>-8.699961074192053</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1587242174055623</v>
+        <v>-0.3273753964632364</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.743503875450772</v>
+        <v>-1.955362287152658</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.19077094663379</v>
+        <v>1.979748085235738</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.232240758651279</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.35582718885928</v>
+        <v>-8.567685600561166</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1104465412061804</v>
+        <v>-0.2790977202638545</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.611228401819885</v>
+        <v>-1.823086813521771</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.265503717559349</v>
+        <v>2.054480856161297</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.235055819338916</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.192569338489962</v>
+        <v>-8.377085925888013</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.04232834037081634</v>
+        <v>-0.2000427897069561</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.447970551450567</v>
+        <v>-1.632487138848618</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.366273488468575</v>
+        <v>2.171655721652825</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.247962160562575</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.943569539806381</v>
+        <v>-8.128086127204432</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0701779203262749</v>
+        <v>-0.08753652900986486</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.447970551450567</v>
+        <v>-1.632487138848618</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.379179829692235</v>
+        <v>2.184562062876484</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.119986230963356</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.049159529579486</v>
+        <v>-8.233676116977536</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1000340051821857</v>
+        <v>-0.2577484545183255</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.553560541223672</v>
+        <v>-1.738077128621723</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.187849906229153</v>
+        <v>1.993232139413403</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.168530572840442</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.067894431698083</v>
+        <v>-8.252411019096133</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05898362415253811</v>
+        <v>-0.2166980734886779</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.553560541223672</v>
+        <v>-1.738077128621723</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.236394248106239</v>
+        <v>2.041776481290489</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.048651650152275</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.919954390290483</v>
+        <v>-8.104470977688534</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.119686530277666</v>
+        <v>-0.2774009796138057</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.533239625315114</v>
+        <v>-1.717756212713165</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.128707874963206</v>
+        <v>1.934090108147456</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.039937663898796</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.895725753901511</v>
+        <v>-8.080242341299561</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1187090619755553</v>
+        <v>-0.2764235113116951</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.509010988926142</v>
+        <v>-1.693527576324193</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.134531070543112</v>
+        <v>1.939913303727361</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.032977051803703</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.85217734713082</v>
+        <v>-8.03669393452887</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1082503113623723</v>
+        <v>-0.2659647606985116</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.509010988926142</v>
+        <v>-1.693527576324193</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.127570458448019</v>
+        <v>1.932952691632268</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.047439406184846</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.610028953676962</v>
+        <v>-7.794545541075012</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.003071400400314062</v>
+        <v>-0.1546430489358253</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.509010988926142</v>
+        <v>-1.693527576324193</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.142032812829162</v>
+        <v>1.947415046013411</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.041971526644041</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.546799581908614</v>
+        <v>-7.731316169306663</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02289526956684851</v>
+        <v>-0.1348191797692908</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.509010988926142</v>
+        <v>-1.693527576324193</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.136564933288357</v>
+        <v>1.941947166472606</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.039469620654618</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.423508447091483</v>
+        <v>-7.608025034489533</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06970981750427763</v>
+        <v>-0.08800463183186169</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.385719854109011</v>
+        <v>-1.570236441507062</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.208037708189212</v>
+        <v>2.013419941373462</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.047170598891944</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.40235924818804</v>
+        <v>-7.586875835586089</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08587047530298042</v>
+        <v>-0.07184397403315934</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.364570655205568</v>
+        <v>-1.549087242603619</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.228428205768603</v>
+        <v>2.033810438952853</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.042951307238994</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.158593806204595</v>
+        <v>-7.343110393602645</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1791573604434089</v>
+        <v>0.02144291110726915</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.364570655205568</v>
+        <v>-1.549087242603619</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.224208914115654</v>
+        <v>2.029591147299903</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.04507562115901</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.894565739011336</v>
+        <v>-7.079082326409385</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2868929012407286</v>
+        <v>0.1291784519045893</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.162705256389615</v>
+        <v>-1.347221843787666</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.347452467325242</v>
+        <v>2.152834700509492</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.037817696142712</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.644715345062261</v>
+        <v>-6.82923193246031</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3795751338040607</v>
+        <v>0.2218606844679214</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.162705256389615</v>
+        <v>-1.347221843787666</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.340194542308944</v>
+        <v>2.145576775493194</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.041416819663361</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.468823252594829</v>
+        <v>-6.653339839992878</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4535310943116819</v>
+        <v>0.2958166449755431</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.162705256389615</v>
+        <v>-1.347221843787666</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.343793665829593</v>
+        <v>2.149175899013843</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.054744325717915</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.297376789572366</v>
+        <v>-6.481893376970414</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5354371855752214</v>
+        <v>0.377722736239082</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9912587933671514</v>
+        <v>-1.175775380765202</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.459989049697624</v>
+        <v>2.265371282881874</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.053764803334212</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.072343789903543</v>
+        <v>-6.256860377301591</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6244708630590474</v>
+        <v>0.4667564137229081</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7662257936983286</v>
+        <v>-0.9507423810963794</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.594029327115215</v>
+        <v>2.399411560299465</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.058459604388529</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.857709412267136</v>
+        <v>-6.042225999665185</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7150194151679274</v>
+        <v>0.5573049658317881</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5515914160619217</v>
+        <v>-0.7361080034599726</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.727504754751376</v>
+        <v>2.532886987935626</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.039653863172325</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.764709371061238</v>
+        <v>-5.949225958459286</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7334136904340824</v>
+        <v>0.5756992410979431</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5515914160619217</v>
+        <v>-0.7361080034599726</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.708699013535172</v>
+        <v>2.514081246719422</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.041396939797202</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.524278874256377</v>
+        <v>-5.708795461654426</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8313289657809038</v>
+        <v>0.6736145164447649</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3111609192570615</v>
+        <v>-0.4956775066551123</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.854700388242966</v>
+        <v>2.660082621427216</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.045326253632022</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.452036306085183</v>
+        <v>-5.636552893483231</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8641553068842018</v>
+        <v>0.706440857548063</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3111609192570615</v>
+        <v>-0.4956775066551123</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.858629702077786</v>
+        <v>2.664011935262035</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.046004837549362</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.336096456459997</v>
+        <v>-5.520613043858046</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9112098306516159</v>
+        <v>0.753495381315477</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2343391882409376</v>
+        <v>-0.4188557756389885</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.9054013246048</v>
+        <v>2.71078355778905</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.043002908769356</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.093440868036835</v>
+        <v>-5.277957455434883</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.005270137240875</v>
+        <v>0.8475556879047357</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2343391882409376</v>
+        <v>-0.4188557756389885</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.902399395824793</v>
+        <v>2.707781629009043</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.04458194577997</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.873420069999824</v>
+        <v>-5.057936657397873</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.094857493466293</v>
+        <v>0.937143044130154</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.09311934317295734</v>
+        <v>-0.2776359305710082</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.988710339876196</v>
+        <v>2.794092573060446</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.060476128581793</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.740552380936546</v>
+        <v>-4.925068968334595</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.163898751893427</v>
+        <v>1.006184302557288</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.09311934317295734</v>
+        <v>-0.2776359305710082</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.004604522678019</v>
+        <v>2.809986755862269</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.061621973022095</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.581037277417177</v>
+        <v>-4.765553864815225</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.228850637741477</v>
+        <v>1.071136188405338</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.06639576034641259</v>
+        <v>-0.1181208270516383</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101459429229943</v>
+        <v>2.906841662414193</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.071710075583535</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.436365132317439</v>
+        <v>-4.620881719715488</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.296807598342812</v>
+        <v>1.139093149006673</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.21106790544615</v>
+        <v>0.02655131804809913</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.198350818851225</v>
+        <v>3.003733052035475</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.057747566984961</v>
+        <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.496239959675131</v>
+        <v>-4.68075654707318</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.258895158801161</v>
+        <v>1.101180709465022</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1511930780884579</v>
+        <v>-0.03332350930959299</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.148463413838036</v>
+        <v>2.953845647022286</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.080148060307527</v>
+        <v>2.965121781512536</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.409440461896123</v>
+        <v>-4.658136576805768</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.31601545123533</v>
+        <v>1.101510726476481</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1511930780884579</v>
+        <v>-0.03332350930959299</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.170863907160602</v>
+        <v>2.945127675926781</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.080220461680939</v>
+        <v>2.965194182885948</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.411910168357929</v>
+        <v>-4.660606283267574</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.31509997002402</v>
+        <v>1.100595245265171</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1487233716266517</v>
+        <v>-0.03579321577139916</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.16945448465693</v>
+        <v>2.943718253423109</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.091227384155641</v>
+        <v>2.97620110536065</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.480280354681939</v>
+        <v>-4.728976469591585</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.298758817969118</v>
+        <v>1.084254093210269</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1579990706628667</v>
+        <v>-0.02651751673518421</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186026826553361</v>
+        <v>2.96029059531954</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.081664092787532</v>
+        <v>2.966637813992541</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.358863925055463</v>
+        <v>-4.607560039965108</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.3377620984516</v>
+        <v>1.123257373692751</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1579990706628667</v>
+        <v>-0.02651751673518421</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176463535185253</v>
+        <v>2.950727303951431</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.906373657827919</v>
+        <v>2.791347379032928</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.389857084384168</v>
+        <v>-4.638553199293813</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.150074399760505</v>
+        <v>0.9355696750016556</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1579990706628667</v>
+        <v>-0.02651751673518421</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.001173100225639</v>
+        <v>2.775436868991818</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.910940889819707</v>
+        <v>2.795914611024716</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.214382824591699</v>
+        <v>-4.463078939501344</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.22483133566928</v>
+        <v>1.010326610910431</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1579990706628667</v>
+        <v>-0.02651751673518421</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.005740332217427</v>
+        <v>2.780004100983606</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.886682918580914</v>
+        <v>2.771656639785923</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.325319077232948</v>
+        <v>-4.574015192142593</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.156198863373988</v>
+        <v>0.9416941386151387</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1579990706628667</v>
+        <v>-0.02651751673518421</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.981482360978634</v>
+        <v>2.755746129744813</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.889814303800819</v>
+        <v>2.774788025005829</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.528345654776181</v>
+        <v>-4.777041769685826</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.0781196175766</v>
+        <v>0.8636148928177509</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.04502750688036672</v>
+        <v>-0.2295440942784176</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.8627977996726</v>
+        <v>2.637061568438778</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.899986690232952</v>
+        <v>2.784960411437961</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.370420055840888</v>
+        <v>-4.619116170750533</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.151462243582849</v>
+        <v>0.9369575188240005</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.04502750688036672</v>
+        <v>-0.2295440942784176</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.872970186104732</v>
+        <v>2.647233954870911</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.894932960806812</v>
+        <v>2.779906682011821</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.28417659281451</v>
+        <v>-4.532872707724155</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.180905899367261</v>
+        <v>0.966401174608412</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.04502750688036672</v>
+        <v>-0.2295440942784176</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.867916456678592</v>
+        <v>2.642180225444771</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.886708736251338</v>
+        <v>2.771682457456347</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.285359677465571</v>
+        <v>-4.534055792375216</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.172208440951362</v>
+        <v>0.9577037161925128</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.05067055534687825</v>
+        <v>-0.2351871427449291</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.856306403043211</v>
+        <v>2.630570171809389</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.887260609284439</v>
+        <v>2.772234330489448</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.162231970471488</v>
+        <v>-4.410928085381133</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.222011396782097</v>
+        <v>1.007506672023248</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.05067055534687825</v>
+        <v>-0.2351871427449291</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.856858276076313</v>
+        <v>2.631122044842491</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279497</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.816533301175805</v>
+        <v>2.701507022380814</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.069421489020629</v>
+        <v>-4.318117603930274</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.188408281253806</v>
+        <v>0.9739035564949572</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.0421399261039811</v>
+        <v>-0.1423766612940698</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.841817256838194</v>
+        <v>2.616081025604372</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.818406777100406</v>
+        <v>2.703380498305415</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.059327955155637</v>
+        <v>-4.269554551709244</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.194319170724404</v>
+        <v>0.9952022533079701</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.05223345996897277</v>
+        <v>-0.09381360907303959</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.84974685308179</v>
+        <v>2.647092332861591</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.813482485612129</v>
+        <v>2.698456206817138</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.946656736919387</v>
+        <v>-4.156883333472994</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.234463366530627</v>
+        <v>1.035346449114193</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.164904678205223</v>
+        <v>0.01885760916321061</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.912425292535263</v>
+        <v>2.709770772315065</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.818973781442796</v>
+        <v>2.703947502647805</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.834279735736714</v>
+        <v>-4.044506332290321</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.284905462834363</v>
+        <v>1.085788545417929</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.164904678205223</v>
+        <v>0.01885760916321061</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.91791658836593</v>
+        <v>2.715262068145732</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.830470983211335</v>
+        <v>2.715444704416344</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.032514304623445</v>
+        <v>-4.242740901177052</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.21710883704821</v>
+        <v>1.017991919631776</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.0333298906815076</v>
+        <v>-0.17937695972352</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.810473048802431</v>
+        <v>2.607818528582232</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.668826703211988</v>
+        <v>2.553800424416997</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.115515585648724</v>
+        <v>-4.325742182202331</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.022264044638752</v>
+        <v>0.8231471272223179</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.05190077520868136</v>
+        <v>-0.1979478442506937</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.63768623808678</v>
+        <v>2.435031717866581</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.788976363931194</v>
+        <v>2.673950085136203</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.956321313592147</v>
+        <v>-4.166547910145754</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.206091414180588</v>
+        <v>1.006974496764154</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.05190077520868136</v>
+        <v>-0.1979478442506937</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.757835898805985</v>
+        <v>2.555181378585787</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.803489390033517</v>
+        <v>2.688463111238526</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.042919896573251</v>
+        <v>-4.253146493126857</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.185965007090469</v>
+        <v>0.9868480896740359</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.05190077520868136</v>
+        <v>-0.1979478442506937</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.772348924908308</v>
+        <v>2.56969440468811</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.800908831375886</v>
+        <v>2.685882552580895</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.0045362340151</v>
+        <v>-4.214762830568706</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.198737913456098</v>
+        <v>0.9996209960396651</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.01351711265053018</v>
+        <v>-0.1595641816925426</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.792798563785568</v>
+        <v>2.59014404356537</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.797637860221188</v>
+        <v>2.682611581426197</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.827419903979933</v>
+        <v>-4.03764650053354</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.266313474315467</v>
+        <v>1.067196556899034</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.01351711265053018</v>
+        <v>-0.1595641816925426</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.78952759263087</v>
+        <v>2.586873072410671</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.798321251983101</v>
+        <v>2.68329497318811</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.79771778000364</v>
+        <v>-4.007944376557246</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.278877715667897</v>
+        <v>1.079760798251464</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.01798723786584355</v>
+        <v>-0.1640343069078559</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.787528909263595</v>
+        <v>2.584874389043396</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.792108227289515</v>
+        <v>2.677081948494524</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.618342358764872</v>
+        <v>-3.828568955318478</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.344414859469819</v>
+        <v>1.145297942053386</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1387895203048751</v>
+        <v>-0.007257548737137243</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.87538193947244</v>
+        <v>2.672727419252242</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.772915682621105</v>
+        <v>2.657889403826114</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.663356572285478</v>
+        <v>-3.873583168839084</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.307216629393166</v>
+        <v>1.108099711976733</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1084406249902705</v>
+        <v>-0.03760644405174185</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.837980057615267</v>
+        <v>2.635325537395069</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.778607244960051</v>
+        <v>2.66358096616506</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.930361082557914</v>
+        <v>-4.14058767911152</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.206106387623138</v>
+        <v>1.006989470206704</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08592241305267806</v>
+        <v>-0.2319694820946904</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.727053797128444</v>
+        <v>2.524399276908246</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.777811166856552</v>
+        <v>2.662784888061561</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.219148303016829</v>
+        <v>-4.429374899570435</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.089795421336073</v>
+        <v>0.8906785039196397</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1870085331516784</v>
+        <v>-0.3330556021936908</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.665606046965545</v>
+        <v>2.462951526745347</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.775411128410869</v>
+        <v>2.660384849615878</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.186672716846057</v>
+        <v>-4.396899313399663</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.100385617358699</v>
+        <v>0.9012686999422652</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1870085331516784</v>
+        <v>-0.3330556021936908</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.663206008519862</v>
+        <v>2.460551488299664</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.771935847619114</v>
+        <v>2.656909568824123</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.028904772143104</v>
+        <v>-4.377861185692366</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.160017514448125</v>
+        <v>0.9054086702334292</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4125521621592376</v>
+        <v>-0.3912392135248853</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.524404550323571</v>
+        <v>2.422166040709192</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.467054031490409</v>
+        <v>3.539066292402619</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.771554898820841</v>
+        <v>2.662328641369611</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.996241101867553</v>
+        <v>-4.313172440472359</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.172702033760073</v>
+        <v>0.9367032408669205</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4125521621592376</v>
+        <v>-0.3912392135248853</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.524023601525299</v>
+        <v>2.42758511325468</v>
       </c>
     </row>
   </sheetData>
